--- a/context/card_data_demo.xlsx
+++ b/context/card_data_demo.xlsx
@@ -6,7 +6,7 @@
   </bookViews>
   <sheets>
     <sheet name="Affinity" sheetId="1" r:id="rId4"/>
-    <sheet name="Character" sheetId="2" r:id="rId5"/>
+    <sheet name="Unit" sheetId="2" r:id="rId5"/>
     <sheet name="Union" sheetId="3" r:id="rId6"/>
     <sheet name="Trap" sheetId="4" r:id="rId7"/>
     <sheet name="Tech" sheetId="5" r:id="rId8"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1412">
   <si>
     <t>Table 1</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Chaos</t>
   </si>
   <si>
-    <t>High cost, powerful characters</t>
+    <t>High cost, powerful units</t>
   </si>
   <si>
     <t>Arcane</t>
@@ -55,7 +55,7 @@
     <t>Bio</t>
   </si>
   <si>
-    <t>Few character, mutate to other or attack a lot of times, Tech heavy</t>
+    <t>Few unit, mutate to other or attack a lot of times, Tech heavy</t>
   </si>
   <si>
     <t>Cosmic</t>
@@ -118,7 +118,7 @@
     <t>Pyromancer</t>
   </si>
   <si>
-    <t>Character</t>
+    <t>Unit</t>
   </si>
   <si>
     <t>+30 ATK vs Nature Affinity</t>
@@ -211,13 +211,13 @@
     <t>Ironclad Sentinel</t>
   </si>
   <si>
-    <t>Immune to 0-cost Traps. This Character cannot be destroyed by Tech Cards.</t>
+    <t>Immune to 0-cost Traps. This Unit cannot be destroyed by Tech Cards.</t>
   </si>
   <si>
     <t>Tomb Bandit</t>
   </si>
   <si>
-    <t>This Character cannot be destroyed by Traps.</t>
+    <t>This Unit cannot be destroyed by Traps.</t>
   </si>
   <si>
     <t>Scout Probe</t>
@@ -235,19 +235,19 @@
     <t>Lab Bloater</t>
   </si>
   <si>
-    <t>With Mutagen Flag: destroy the attacker in Reckoning. Foe pay no cost.</t>
+    <t>With Mutagen Flag: you can destroy both units in Reckoning. No cost is paid.</t>
   </si>
   <si>
     <t>Lab Crawler</t>
   </si>
   <si>
-    <t>With Mutagen Flag: gain 1 more attack once per turn</t>
+    <t>With Mutagen Flag: this card can target 3 cards</t>
   </si>
   <si>
     <t>Pit Lord</t>
   </si>
   <si>
-    <t>his card is destroyed if battle with Divine Character. After this card attacked, halve its ATK&amp;DEF permanently</t>
+    <t>his card is destroyed if battle with Divine Unit. After this card attacked, halve its ATK&amp;DEF permanently</t>
   </si>
   <si>
     <t>Ancient Lich</t>
@@ -265,7 +265,7 @@
     <t>Mountain Sage</t>
   </si>
   <si>
-    <t>Double effect of Tech card apply to this character</t>
+    <t>Double effect of Tech card apply to this unit</t>
   </si>
   <si>
     <t xml:space="preserve">War Genie </t>
@@ -316,7 +316,7 @@
     <t>Leech Man</t>
   </si>
   <si>
-    <t>+20 DEF permanently each time it performed attack and survive</t>
+    <t>+20 DEF permanently each time it performed attack and survive. With mutagen flag : +45 ATK</t>
   </si>
   <si>
     <t>Immortal Vampire</t>
@@ -364,7 +364,7 @@
     <t>Ectoplasm</t>
   </si>
   <si>
-    <t>When your character card is destroy, you can copy ATK, DEF, Crystal Cost of the destroyed card to this card instead. Can be triggered face-down.</t>
+    <t>When your unit card is destroy, you can copy ATK, DEF, Crystal Cost of the destroyed card to this card instead. Can be triggered face-down.</t>
   </si>
   <si>
     <t>Death Stag</t>
@@ -373,7 +373,7 @@
     <t>Champion of the Valley</t>
   </si>
   <si>
-    <t>+10 ATK permanently if it destroyed a character. This bonus do not exceed maximum of 30</t>
+    <t>+10 ATK permanently if it destroyed a unit. This bonus do not exceed maximum of 30</t>
   </si>
   <si>
     <t>Magenta the Nightbloom</t>
@@ -553,7 +553,7 @@
     <t>Golden Senju</t>
   </si>
   <si>
-    <t>Once per turn, if attacked non-character card, this card : can attack 1 more times</t>
+    <t>Once per turn, if attacked non-unit card, this card : can attack 1 more times</t>
   </si>
   <si>
     <t>Cruel Angel</t>
@@ -649,7 +649,7 @@
     <t>Lady of the Sacred Pond</t>
   </si>
   <si>
-    <t>+20 ATK and DEF to Anima character</t>
+    <t>+20 ATK and DEF to Anima unit</t>
   </si>
   <si>
     <t>Unwavering Cleric</t>
@@ -1030,7 +1030,7 @@
     <t>Nostra the Necromancer</t>
   </si>
   <si>
-    <t>While this is face-up, whenever your card is destroyed, revive character with ATK and DEF not exceed 50 and place on any of your empty cell</t>
+    <t>While this is face-up, whenever your card is destroyed, revive unit with ATK and DEF not exceed 50 and place on any of your empty cell</t>
   </si>
   <si>
     <t>Bone Dragon</t>
@@ -1090,7 +1090,7 @@
     <t>Mad Raccoon</t>
   </si>
   <si>
-    <t>Armored Mokney</t>
+    <t>Armored Monkey</t>
   </si>
   <si>
     <t>+10 ATK if there is face-up Nature card</t>
@@ -1150,7 +1150,7 @@
     <t>Doctopus</t>
   </si>
   <si>
-    <t>Once, whenever your Nature card is destroyed, you can make this card ATK becomes 0, revive the character at the end of this turn. This effect can be used faced down.</t>
+    <t>Once, whenever your Nature card is destroyed, you can make this card ATK becomes 0, revive the unit at the end of this turn. This effect can be used faced down.</t>
   </si>
   <si>
     <t>White Tiger</t>
@@ -1246,7 +1246,7 @@
     <t>Wending the Wise Princess</t>
   </si>
   <si>
-    <t>Once, when this card is revealed, choose either reveal 1 card on opponent’s field or put 1 princes flag on your face-up character</t>
+    <t>Once, when this card is revealed, choose either reveal 1 card on opponent’s field or put 1 princes flag on your face-up unit</t>
   </si>
   <si>
     <t>Fern the Mermaid Princess</t>
@@ -1270,7 +1270,7 @@
     <t>Lindsy the Brave Princess</t>
   </si>
   <si>
-    <t>At the start of each turn, put 1 princess flag on your face-up character</t>
+    <t>At the start of each turn, put 1 princess flag on your face-up unit</t>
   </si>
   <si>
     <t>Rena the Space Princess</t>
@@ -1627,7 +1627,7 @@
     <t>Gluttonous Amoeba</t>
   </si>
   <si>
-    <t>If this card battles, opponent’s next attack must target a Dead End.</t>
+    <t>If this card battles, opponent’s next attack must target a face-down card</t>
   </si>
   <si>
     <t>Sticky Grappler</t>
@@ -1654,7 +1654,7 @@
     <t>Rotten Shrieker</t>
   </si>
   <si>
-    <t>-10 ATK permanently at your turn’s end</t>
+    <t>Without Mutagen Flag : -10 ATK permanently at your turn’s end</t>
   </si>
   <si>
     <t>Toxin Folk</t>
@@ -1702,7 +1702,7 @@
     <t>Epsilon The Wither</t>
   </si>
   <si>
-    <t>When this card battles, it gain +20 ATK and DEF until the end of turn, but all your other characters lose 20 ATK and DEF until the end of turn.</t>
+    <t>When this card battles, it gain +20 ATK and DEF until the end of turn, but all your other units lose 20 ATK and DEF until the end of turn.</t>
   </si>
   <si>
     <t>Plaguespreader</t>
@@ -1711,7 +1711,7 @@
     <t>Black Worms</t>
   </si>
   <si>
-    <t>At the end of your turn, -50 crystal for each mutagen flag on the field</t>
+    <t>At the end of your turn, your foe lose 300 crystals for each Mutagen flag on the field</t>
   </si>
   <si>
     <t>Special Bleacher Unit</t>
@@ -1966,7 +1966,7 @@
     <t>Leopard Jailer</t>
   </si>
   <si>
-    <t>If this card attacks a character card, the target is unable to attack until the end of their turn.</t>
+    <t>If this card attacks a unit card, the target is unable to attack until the end of their turn.</t>
   </si>
   <si>
     <t>Wild West Raccoon</t>
@@ -1999,10 +1999,10 @@
     <t>Union</t>
   </si>
   <si>
-    <t>1 ??? + 1 ??? + 1000 crystals</t>
-  </si>
-  <si>
-    <t>Gryphon + 1 Divine + 1000 crystals</t>
+    <t>1 ??? + 1 ??? + 1000 cost</t>
+  </si>
+  <si>
+    <t>Gryphon + 1 Divine + 1000 cost</t>
   </si>
   <si>
     <t>10000
@@ -2021,10 +2021,10 @@
     <t>Double ATK&amp;DEF against Chaos</t>
   </si>
   <si>
-    <t>1 ??? + 1 ??? + 1500 crystals</t>
-  </si>
-  <si>
-    <t>1 ‘Seraph’ name + 1 Divine (≥ 800 cost) + 1500 crystals</t>
+    <t>1 ??? + 1 ??? + 1500 cost</t>
+  </si>
+  <si>
+    <t>1 ‘Seraph’ unit + 1 Divine (≥ 800 cost) + 1500 cost</t>
   </si>
   <si>
     <t>11011
@@ -2037,10 +2037,10 @@
     <t>Gaia Turtle</t>
   </si>
   <si>
-    <t>2 ??? + 2000 crystals</t>
-  </si>
-  <si>
-    <t>2 cards (≥100 DEF) + 2000 crystals</t>
+    <t>2 ??? + 2000 cost</t>
+  </si>
+  <si>
+    <t>2 any units (≥100 DEF) + 2000 cost</t>
   </si>
   <si>
     <t>00000
@@ -2053,10 +2053,10 @@
     <t>Barros the Colossol</t>
   </si>
   <si>
-    <t>2 ???+ 1500 crystals</t>
-  </si>
-  <si>
-    <t>2 Nature (≥ 800 cost) + 1500 crystals</t>
+    <t>2 ???+ 1500 cost</t>
+  </si>
+  <si>
+    <t>2 Nature (≥ 800 cost) + 1500 cost</t>
   </si>
   <si>
     <t>00000
@@ -2075,10 +2075,10 @@
     <t>Can attack 3 times per turn</t>
   </si>
   <si>
-    <t>1 ??? + 2 ??? + 1500 crystals</t>
-  </si>
-  <si>
-    <t>Bio with mutagen flag + 2 Bio + 1500 crystals</t>
+    <t>1 ??? + 2 ??? + 1500 cost</t>
+  </si>
+  <si>
+    <t>1 Bio with mutagen flag + 2 Bio + 1500 cost</t>
   </si>
   <si>
     <t>00100
@@ -2097,10 +2097,10 @@
     <t>With another face-up Cosmic: this card cannot be destroyed</t>
   </si>
   <si>
-    <t>2 ??? + 1500 crystal</t>
-  </si>
-  <si>
-    <t>2 Cosmic (≥ 800 cost) + 1500 crystal</t>
+    <t>2 ??? + 1500 cost</t>
+  </si>
+  <si>
+    <t>2 Cosmic (≥ 800 cost) + 1500 cost</t>
   </si>
   <si>
     <t>00100
@@ -2113,16 +2113,16 @@
     <t>X-Death Squad</t>
   </si>
   <si>
-    <t>In Reckoning, pay ???, destroy foe’s character. They pay ???.</t>
-  </si>
-  <si>
-    <t>In Reckoning, pay 1000, destroy foe’s character. They pay no cost.</t>
-  </si>
-  <si>
-    <t>1 ??? + 2 ??? + 1000 crystals</t>
-  </si>
-  <si>
-    <t>1 Anima (≥ 800 cost) + 2 Anima + 1000 crystals</t>
+    <t>In Reckoning, pay ???, destroy foe’s unit. They pay ???.</t>
+  </si>
+  <si>
+    <t>In Reckoning, pay 1000, destroy foe’s unit. They pay no cost.</t>
+  </si>
+  <si>
+    <t>1 ??? + 2 ??? + 800 cost</t>
+  </si>
+  <si>
+    <t>1 Anima (≥ 800 cost) + 2 Anima + 800 cost</t>
   </si>
   <si>
     <t>10101
@@ -2141,7 +2141,7 @@
     <t>+100 ATK and DEF if 15 or more of your cells is revealed</t>
   </si>
   <si>
-    <t>1 Slim Gray + 1 Cosmic (≥ 800 cost) + 1000 crystals</t>
+    <t>1 Slim Gray + 1 Cosmic (≥ 800 cost) + 1000 cost</t>
   </si>
   <si>
     <t>00100
@@ -2160,7 +2160,7 @@
     <t>+100 ATK vs Cosmic</t>
   </si>
   <si>
-    <t>1 Cosmic (≥ 500 cost) + 1 Cosmic + 1500 crystals</t>
+    <t>1 Cosmic (≥ 500 cost) + 1 Cosmic + 1500 cost</t>
   </si>
   <si>
     <t>00100
@@ -2179,10 +2179,10 @@
     <t>Destroy this card after battle calculation</t>
   </si>
   <si>
-    <t>2 ??? + 1000 crystal</t>
-  </si>
-  <si>
-    <t>2 Bio cards (≥ 800 cost) + 1000 crystal</t>
+    <t>2 ??? + 1000 cost</t>
+  </si>
+  <si>
+    <t>2 Bio cards (≥ 800 cost) + 1000 cost</t>
   </si>
   <si>
     <t>10001
@@ -2201,7 +2201,7 @@
     <t>+30 ATK permanently at the end of your turn</t>
   </si>
   <si>
-    <t>1 Cleaver Saint + 1 Divine card + 1500 crystal</t>
+    <t>1 Cleaver Saint + 1 Divine card + 1500 cost</t>
   </si>
   <si>
     <t>00011
@@ -2211,13 +2211,10 @@
 00011</t>
   </si>
   <si>
-    <t>Rocket Tyrant</t>
-  </si>
-  <si>
-    <t>1 ??? + 1 ??? + 1000 crystal</t>
-  </si>
-  <si>
-    <t>1 Bio (≥ 800 cost) + 1 Anima (≥ 800 cost) + 1000 crystal</t>
+    <t>Rocket Marauder</t>
+  </si>
+  <si>
+    <t>1 Bio (≥ 800 cost) + 1 Anima (≥ 800 cost) + 1000 cost</t>
   </si>
   <si>
     <t>00000
@@ -2236,7 +2233,7 @@
     <t>-50 ATK if attacks dead end card</t>
   </si>
   <si>
-    <t>2 Chaos (≥ 800 cost) + 1000 crystal</t>
+    <t>1 Chaos (≥ 1000 cost) + 1 Chaos (≥ 800 cost) + 1000 cost</t>
   </si>
   <si>
     <t>00000
@@ -2255,7 +2252,10 @@
     <t>In Reckoning, pay 1000 crystal cost to +60 DEF</t>
   </si>
   <si>
-    <t>1 Armored Nature card + 1 Nature (≥ 800 cost) + 1000 crystals</t>
+    <t>1 ??? + 1 ??? + 800 cost</t>
+  </si>
+  <si>
+    <t>1 Armored Nature card + 1 Nature (≥ 800 cost) + 800 cost</t>
   </si>
   <si>
     <t>00000
@@ -2274,7 +2274,7 @@
     <t>Once, after Reckoning: +ATK&amp;DEF equal to half of that foe’s card</t>
   </si>
   <si>
-    <t>1 Succubus + 1 Chaos + 1000 crystals</t>
+    <t>1 Succubus + 1 Chaos + 800 cost</t>
   </si>
   <si>
     <t>00100
@@ -2293,7 +2293,10 @@
     <t>+5 ATK for each Divine cards on their own field</t>
   </si>
   <si>
-    <t>1 Tiny Pixie + 1 Divine card + 1000 crystal</t>
+    <t>1 ??? + 1 ??? + 300 cost</t>
+  </si>
+  <si>
+    <t>1 Tiny Pixie + 1 Divine+ 300 cost</t>
   </si>
   <si>
     <t>00100
@@ -2312,7 +2315,10 @@
     <t>+15 ATK until the end of this turn, once.</t>
   </si>
   <si>
-    <t>1 Ponycorn + 1 Divine card + 1000 crystals</t>
+    <t>1 ??? + 1 ??? + 500 cost</t>
+  </si>
+  <si>
+    <t>1 Ponycorn + 1 Divine card + 500 cost</t>
   </si>
   <si>
     <t>Choir Lead Amber</t>
@@ -2321,13 +2327,13 @@
     <t>+20 ATK to all ?????</t>
   </si>
   <si>
-    <t>+20 ATK to all Divine characters on their own field</t>
-  </si>
-  <si>
-    <t>3 ??? + 1000 crystals</t>
-  </si>
-  <si>
-    <t>3 Choir Lady cards + 1000 crystals</t>
+    <t>+20 ATK to all Divine units on their own field</t>
+  </si>
+  <si>
+    <t>3 ??? + 500 cost</t>
+  </si>
+  <si>
+    <t>3 Choir Lady cards + 500 cost</t>
   </si>
   <si>
     <t>01100
@@ -2346,7 +2352,7 @@
     <t>Once, destroy Divine or Anima card</t>
   </si>
   <si>
-    <t>1 Cruel Angel + 1 Anima Card + 1000 crystals</t>
+    <t>1 Cruel Angel + 1 Anima Card + 1000 cost</t>
   </si>
   <si>
     <t>11111
@@ -2365,10 +2371,10 @@
     <t>At battle calculation, flip a coin. If head, the attack does nothing</t>
   </si>
   <si>
-    <t>1 ??? + 1 ???+ 1000 crystals</t>
-  </si>
-  <si>
-    <t>1 Sphinx character + 1 Divine card + 1000 crystals</t>
+    <t>1 ??? + 1 ???+ 1000 cost</t>
+  </si>
+  <si>
+    <t>1 Sphinx unit + 1 Divine card + 1000 cost</t>
   </si>
   <si>
     <t>00000
@@ -2387,10 +2393,10 @@
     <t>This card cannot attack if there is card with affinity other than Divine or Anima on their own field</t>
   </si>
   <si>
-    <t>1 ???+ ??? + 1000 crystals</t>
-  </si>
-  <si>
-    <t>1 Sphinx character + 1 Anima + 1000 crystals</t>
+    <t>1 ???+ ??? + 1000 cost</t>
+  </si>
+  <si>
+    <t>1 Sphinx unit + 1 Anima + 1000 cost</t>
   </si>
   <si>
     <t>11111
@@ -2409,10 +2415,10 @@
     <t>+20 ATK vs Chaos and Arcane</t>
   </si>
   <si>
-    <t>2 ???+ 2000 crystals</t>
-  </si>
-  <si>
-    <t>2 Sphinx characters + 1000 crystals</t>
+    <t>2 ???+ 2000 cost</t>
+  </si>
+  <si>
+    <t>2 Sphinx units + 1000 cost</t>
   </si>
   <si>
     <t>10001
@@ -2431,7 +2437,7 @@
     <t>During the end of that turn, flip a coin. If head, +10 ATK. If tail, +10 DEF</t>
   </si>
   <si>
-    <t>1 Lucky Statue + 1 Divine card + 1000 crystals</t>
+    <t>1 Lucky Statue + 1 Divine card + 1000 cost</t>
   </si>
   <si>
     <t>00100
@@ -2444,7 +2450,7 @@
     <t>Raijin and Fujin</t>
   </si>
   <si>
-    <t>Raijin + Fujin + 1000 crystals</t>
+    <t>Raijin + Fujin + 800 cost</t>
   </si>
   <si>
     <t>10001
@@ -2463,7 +2469,7 @@
     <t>At the end of this turn, +5 ATK and DEF permanently.</t>
   </si>
   <si>
-    <t>Bloom Fairy + 1 Nature card + 1000 crystals</t>
+    <t>Bloom Fairy + 1 Nature card + 1000 cost</t>
   </si>
   <si>
     <t>11111
@@ -2482,7 +2488,10 @@
     <t>If this card defends, DEF becomes 50, ATK becomes 0. If this card performs attack, ATK becomes 50, DEF becomes 0.</t>
   </si>
   <si>
-    <t>Sunrise Lady + Moonrise Gentleman + 1000 crystals</t>
+    <t>1 ??? + 1 ??? + 400 cost</t>
+  </si>
+  <si>
+    <t>Sunrise Lady + Moonrise Gentleman + 400 cost</t>
   </si>
   <si>
     <t>11111
@@ -2501,10 +2510,10 @@
     <t>This card can attack twice per turn</t>
   </si>
   <si>
-    <t>1??? + 1 ??? + 1000 crystals</t>
-  </si>
-  <si>
-    <t>Lady of the Sacred Pond + 1 Anima + 1000 crystals</t>
+    <t>1??? + 1 ??? + 1000 cost</t>
+  </si>
+  <si>
+    <t>Lady of the Sacred Pond + 1 Anima + 1000 cost</t>
   </si>
   <si>
     <t>11011
@@ -2517,7 +2526,7 @@
     <t>Blast Beam Seraph</t>
   </si>
   <si>
-    <t>Gerald of the Heavenly Light + 1 Divine + 1000 crystals</t>
+    <t>Gerald of the Heavenly Light + 1 Divine + 1000 cost</t>
   </si>
   <si>
     <t>11111
@@ -2536,10 +2545,7 @@
     <t>+50 ATK and DEF for each Divine cards on the field. This bonus does not exceed maximum of 100</t>
   </si>
   <si>
-    <t>2 ??? + 1500 crystals</t>
-  </si>
-  <si>
-    <t>2 Divine (800 cost) + 1500 crystals</t>
+    <t>2 Divine (800 cost) + 1500 cost</t>
   </si>
   <si>
     <t>00100
@@ -2558,7 +2564,7 @@
     <t>If this card attacks a dead end card, you receive 200 crystals</t>
   </si>
   <si>
-    <t>1 Miner probe + 1 Cosmic + 1000 crystals</t>
+    <t>1 Miner probe + 1 Cosmic + 500 cost</t>
   </si>
   <si>
     <t>11111
@@ -2571,7 +2577,7 @@
     <t>Kitsune</t>
   </si>
   <si>
-    <t>Dark Monk + 1 Chaos + 1000 crystals</t>
+    <t>Dark Monk + 1 Chaos + 300 cost</t>
   </si>
   <si>
     <t>01100
@@ -2590,7 +2596,10 @@
     <t>This card can choose two attack targets. -5 ATK for each successful attack.</t>
   </si>
   <si>
-    <t>Yaksa + 1 Chaos + 1000 crystals</t>
+    <t>1 ??? + 1 ??? + 600 cost</t>
+  </si>
+  <si>
+    <t>Yaksa + 1 Chaos + 600 cost</t>
   </si>
   <si>
     <t>11011
@@ -2603,7 +2612,10 @@
     <t>Skeleton Overlord</t>
   </si>
   <si>
-    <t>3 Skeleton cards + 1000 crystals</t>
+    <t>3 ??? + 400 cost</t>
+  </si>
+  <si>
+    <t>3 Skeleton cards + 400 cost</t>
   </si>
   <si>
     <t>01110
@@ -2622,10 +2634,10 @@
     <t>When this card defends, halve its attack and increase DEF by that amount  permanently</t>
   </si>
   <si>
-    <t>4 ??? + 2000 crystals</t>
-  </si>
-  <si>
-    <t>4 Chaos card (500 cost) + 2000 crystals</t>
+    <t>4 ??? + 2000 cost</t>
+  </si>
+  <si>
+    <t>4 Chaos card (500 cost) + 2000 cost</t>
   </si>
   <si>
     <t>10001
@@ -2638,7 +2650,10 @@
     <t>Katana Shark</t>
   </si>
   <si>
-    <t>3 ‘Sharks’ name + 1000 crystals</t>
+    <t>3 ??? + 800 cost</t>
+  </si>
+  <si>
+    <t>3 ‘Sharks’ name + 800 cost</t>
   </si>
   <si>
     <t>11000
@@ -2679,7 +2694,7 @@
     <t>After this card battles, select 1 foe’s card, flip a coin. Head : destroy that card</t>
   </si>
   <si>
-    <t>Ostrich Cannon + 1 Nature + 1500 crystals</t>
+    <t>Ostrich Cannon + 1 Nature + 1500 cost</t>
   </si>
   <si>
     <t>10001
@@ -2698,10 +2713,10 @@
     <t>Once Union, put venom flag on all foe’s face-up card</t>
   </si>
   <si>
-    <t>2 ??? + 1000 crystals</t>
-  </si>
-  <si>
-    <t>2 Nature cards + 1000 crystals</t>
+    <t>2 ??? + 500 cost</t>
+  </si>
+  <si>
+    <t>2 Nature cards + 500 cost</t>
   </si>
   <si>
     <t>11111
@@ -2714,7 +2729,10 @@
     <t>Ancient Lizard</t>
   </si>
   <si>
-    <t>1 Flame Lizard + 1 Nature + 1000 crystals</t>
+    <t>1 ??? + 1 ???+ 800 cost</t>
+  </si>
+  <si>
+    <t>1 Flame Lizard + 1 Nature + 800 cost</t>
   </si>
   <si>
     <t>00000
@@ -2730,10 +2748,10 @@
     <t>+?? ATK when this card can destroy ???</t>
   </si>
   <si>
-    <t>+25 ATK when this card can destroy a character card</t>
-  </si>
-  <si>
-    <t>1 Kulu the Alpha Leader + 1 Anima + 1000 crystals</t>
+    <t>+25 ATK when this card can destroy a unit card</t>
+  </si>
+  <si>
+    <t>1 Kulu the Alpha Leader + 1 Anima + 1000 cost</t>
   </si>
   <si>
     <t>10101
@@ -2752,7 +2770,7 @@
     <t>At battle calculation, +40 ATK and +40 DEF vs Union cards</t>
   </si>
   <si>
-    <t>1 Dew the Frog Knight + 1 card including ‘princess’ name or card with princess flag + 1000 crystals</t>
+    <t>1 Dew the Frog Knight + 1 card including ‘princess’ name or card with princess flag + 1000 cost</t>
   </si>
   <si>
     <t>11011
@@ -2771,7 +2789,10 @@
     <t>Both player cannot use tech while this card is face-up. This card is unaffected by traps.</t>
   </si>
   <si>
-    <t>3 ‘Princess’ or card with princess flag + 1000 crystals</t>
+    <t>3 ??? + 1000 cost</t>
+  </si>
+  <si>
+    <t>3 ‘Princess’ or card with princess flag + 1000 cost</t>
   </si>
   <si>
     <t>01110
@@ -2790,10 +2811,10 @@
     <t>+20 ATK at the end of your turn. Whenever this card attacks, reset this bonus.</t>
   </si>
   <si>
-    <t>1 ??? + 1 ??? + 1 ??? + 1000 crystals</t>
-  </si>
-  <si>
-    <t>Wild Centaur + Wild Minotaur + Wild Pegasus + 1000 crystals</t>
+    <t>1 ??? + 1 ??? + 1 ??? + 1000 cost</t>
+  </si>
+  <si>
+    <t>Wild Centaur + Wild Minotaur + Wild Pegasus + 1000 cost</t>
   </si>
   <si>
     <t>00000
@@ -2812,7 +2833,10 @@
     <t>Cannot be destroyed by non-union cards. If targeted by tech, destroy this card.</t>
   </si>
   <si>
-    <t>1 Arcane (≥ 500 cost) + 1 Nature (≥ 500 cost) + 1 Divine (≥ 500 cost) + 1000 crystals</t>
+    <t>1 ??? + 1 ??? + 1 ??? + 800 cost</t>
+  </si>
+  <si>
+    <t>1 Arcane (≥ 500 cost) + 1 Nature (≥ 500 cost) + 1 Divine (≥ 500 cost) + 800 cost</t>
   </si>
   <si>
     <t>00100
@@ -2831,7 +2855,7 @@
     <t>This card is unaffected by trap effect</t>
   </si>
   <si>
-    <t>1 Steel Eagle + 1 Nature (≥ 800 cost) + 1000 crystals</t>
+    <t>1 Steel Eagle + 1 Nature (≥ 800 cost) + 1000 cost</t>
   </si>
   <si>
     <t>00000
@@ -2850,16 +2874,16 @@
     <t>During battle, you can choose to destroy 1 of your trap card to +60 ATK and DEF</t>
   </si>
   <si>
-    <t>1 Space Janitor + 1 Cosmic + 1000 crystals</t>
+    <t>1 Space Janitor + 1 Cosmic + 1000 cost</t>
   </si>
   <si>
     <t>Berserk Hyena</t>
   </si>
   <si>
-    <t>2 ???+ 1000 crystals</t>
-  </si>
-  <si>
-    <t>2 Nature + 1000 crystals</t>
+    <t>2 ???+ 500 cost</t>
+  </si>
+  <si>
+    <t>2 Nature + 500 cost</t>
   </si>
   <si>
     <t>00000
@@ -2878,7 +2902,7 @@
     <t>Defender is unable to attack on next opponent’s turn.</t>
   </si>
   <si>
-    <t>Drill Woodpecker + 1 Nature + 1000 crystals</t>
+    <t>Drill Woodpecker + 1 Nature + 1000 cost</t>
   </si>
   <si>
     <t>10100
@@ -2897,7 +2921,10 @@
     <t>Start of your turn: Reveal 1 foe’s cell. If it was a Dead End, destroy this card. Otherwise, gain 200 crystals.</t>
   </si>
   <si>
-    <t>2 Divine cards + 1000 crystals</t>
+    <t>2 ??? + 300 cost</t>
+  </si>
+  <si>
+    <t>2 Divine cards + 300 cost</t>
   </si>
   <si>
     <t>00100
@@ -2941,7 +2968,7 @@
     <t>1 ??? + 1 ??? + 1000</t>
   </si>
   <si>
-    <t>Cullan the Magic Swordsman + Red Mage + 1000 crystals</t>
+    <t>Cullan the Magic Swordsman + Red Mage + 1000 cost</t>
   </si>
   <si>
     <t>00001
@@ -2957,7 +2984,7 @@
     <t>Whenever an opponent destroys one of your cards, gain +15 ATK permanently (max +60).</t>
   </si>
   <si>
-    <t>Mad Doctor + 1 Chaos card + 1000 crystals</t>
+    <t>Mad Doctor + 1 Chaos card + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00000
@@ -2971,13 +2998,16 @@
     <t>Colorful Mage</t>
   </si>
   <si>
-    <t>-??? ATK&amp;DEF permanently if battles against non-Arcane card.</t>
-  </si>
-  <si>
-    <t>-10 ATK&amp;DEF permanently if battles against non-Arcane card.</t>
-  </si>
-  <si>
-    <t>Red Mage + Green Mage + Blue Mage + 1000 crystals</t>
+    <t>Foe’s non-Arcane get ??? in Reckoning with this card</t>
+  </si>
+  <si>
+    <t>Foe’s non-Arcane get -10 ATK&amp;DEF permanently in Reckoning with this card</t>
+  </si>
+  <si>
+    <t>??? + ???+ ??? + 500 cost</t>
+  </si>
+  <si>
+    <t>Red Mage + Green Mage + Blue Mage + 500 cost</t>
   </si>
   <si>
     <t>Ethereal Marquees</t>
@@ -2989,7 +3019,7 @@
     <t>-80 DEF if defends against Arcane card. If this card battles and survived, pay 500 crystal cost</t>
   </si>
   <si>
-    <t>Nobleman of Luminaso + 1 Arcane + 1500 crystals</t>
+    <t>Nobleman of Luminaso + 1 Arcane + 1500 cost</t>
   </si>
   <si>
     <t>00100
@@ -3005,7 +3035,7 @@
     <t>At the beginning of your opponent’s turn, flip a coin. If head, your opponent can only attack once.</t>
   </si>
   <si>
-    <t>Alluring Spellcaster + 1 Arcane + 1000 crystals</t>
+    <t>Alluring Spellcaster + 1 Arcane + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00000
@@ -3022,7 +3052,7 @@
     <t>When another of your Arcane card defends, you can swap this card with the defender. Flip a coin, if head, the attack is negated</t>
   </si>
   <si>
-    <t>Freya the Rift Walker + Bingo the Chrono Rabbit + 1000 crystals.</t>
+    <t>Freya the Rift Walker + Bingo the Chrono Rabbit + 1000 cost.</t>
   </si>
   <si>
     <t xml:space="preserve">00010
@@ -3039,7 +3069,7 @@
     <t>This card can only choose attack target in the same pattern as its union zone</t>
   </si>
   <si>
-    <t>Long Tongue + 1 Bio card + 1000 crystals.</t>
+    <t>Long Tongue + 1 Bio card + 1000 cost.</t>
   </si>
   <si>
     <t xml:space="preserve">10001
@@ -3053,7 +3083,7 @@
     <t>Diamond Elemental</t>
   </si>
   <si>
-    <t>Fire Elemental + Earth Elemental + 1000 crystals</t>
+    <t>Fire Elemental + Earth Elemental + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">01010
@@ -3070,7 +3100,7 @@
     <t>Card that battles this card cannot perform attack until the end of their next turn.</t>
   </si>
   <si>
-    <t>Water Elemental + Wind Elemental + 1000 crystals</t>
+    <t>Water Elemental + Wind Elemental + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00000
@@ -3084,7 +3114,7 @@
     <t>Cloud Elemental</t>
   </si>
   <si>
-    <t>Fire Elemental + Water Elemental + 1000 crystals</t>
+    <t>Fire Elemental + Water Elemental + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00100
@@ -3101,7 +3131,7 @@
     <t>After successful attack, reveal 1 of your opponent’s card</t>
   </si>
   <si>
-    <t>Fire Elemental + Wind Elemental + 1000 crystals</t>
+    <t>Fire Elemental + Wind Elemental + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00010
@@ -3118,7 +3148,7 @@
     <t>At the end of this turn, +10 DEF permanently</t>
   </si>
   <si>
-    <t>Water Elemental + Earth Elemental + 1000 crystals</t>
+    <t>Water Elemental + Earth Elemental + 1000 cost</t>
   </si>
   <si>
     <t>Sand Elemental</t>
@@ -3127,7 +3157,7 @@
     <t>+40 ATK and DEF vs Non-Arcane cards</t>
   </si>
   <si>
-    <t>Wind Elemental + Earth Elemental + 1000 crystals</t>
+    <t>Wind Elemental + Earth Elemental + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00000
@@ -3144,7 +3174,7 @@
     <t>At the end of this turn, +10 ATK permanently</t>
   </si>
   <si>
-    <t>Mind Elemental + Fire Elemental + 1500 crystals</t>
+    <t>Mind Elemental + Fire Elemental + 1500 cost</t>
   </si>
   <si>
     <t>Acid Elemental</t>
@@ -3153,13 +3183,13 @@
     <t xml:space="preserve">When this card is union summoned, put acid flag on all of your opponent’s face-up card. At the end of opponent’s turn, card with acid flag -10 DEF </t>
   </si>
   <si>
-    <t>Mind Elemental + Water Elemental + 1500 crystals</t>
+    <t>Mind Elemental + Water Elemental + 1500 cost</t>
   </si>
   <si>
     <t>Vacuum Elemental</t>
   </si>
   <si>
-    <t>Mind Elemental + Wind Elemental + 1500 crystals</t>
+    <t>Mind Elemental + Wind Elemental + 1500 cost</t>
   </si>
   <si>
     <t>Magnet Elemental</t>
@@ -3168,7 +3198,7 @@
     <t>Your opponent’s non-Arcane cards cannot target face-up card other than this card.</t>
   </si>
   <si>
-    <t>Mind Elemental + Earth Elemental + 1500 crystals</t>
+    <t>Mind Elemental + Earth Elemental + 1500 cost</t>
   </si>
   <si>
     <t>Dwarven Berserker</t>
@@ -3177,7 +3207,7 @@
     <t>This card can attack twice</t>
   </si>
   <si>
-    <t>1 Dwarven card + 1 Arcane or Anima card + 1500 crystals</t>
+    <t>1 Dwarven card + 1 Arcane or Anima card + 1500 cost</t>
   </si>
   <si>
     <t xml:space="preserve">01110
@@ -3191,7 +3221,7 @@
     <t>Grand Fort Captain</t>
   </si>
   <si>
-    <t>2 Grand Fort card + 1000 crystals</t>
+    <t>2 Grand Fort card + 500 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00000
@@ -3205,13 +3235,13 @@
     <t>Volatile Slasher</t>
   </si>
   <si>
-    <t>While this card attacking, it gain +??? ATK bonus vs target’s affinity ???</t>
-  </si>
-  <si>
-    <t>While this card attacking, it gain +50 ATK bonus vs target’s affinity permanently, once per affinity.</t>
-  </si>
-  <si>
-    <t>1 Bladeshifter + 1 Bio card + 1000 crystals</t>
+    <t>After Reckoning with non-Bio, it gain ???.</t>
+  </si>
+  <si>
+    <t>After Reckoning with non-Bio, it gain +50 ATK permanently.</t>
+  </si>
+  <si>
+    <t>1 Bladeshifter + 1 Bio card + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">10000
@@ -3231,7 +3261,7 @@
     <t>Upon union, revive 1 Moon non-Union card. Double its cost.</t>
   </si>
   <si>
-    <t>1 Moon card+ 1 Cosmic card + 1000 crystals</t>
+    <t>1 Moon card+ 1 Cosmic card + 500 cost</t>
   </si>
   <si>
     <t xml:space="preserve">10001
@@ -3245,13 +3275,16 @@
     <t>Rebel King</t>
   </si>
   <si>
-    <t>At foe’s turn ends: foe select ??? card and swap ATK&amp;DEF</t>
-  </si>
-  <si>
-    <t>At foe’s turn ends: foe select 1 own face-up card and swap ATK&amp;DEF</t>
-  </si>
-  <si>
-    <t>Jirayu the Rebellious Prince + 1 Anima card (≥ 500 cost) + 1000 crystals</t>
+    <t>At foe’s turn ends: ??? and swap ATK&amp;DEF</t>
+  </si>
+  <si>
+    <t>At foe’s turn ends: foe select 1 own unit and swap ATK&amp;DEF</t>
+  </si>
+  <si>
+    <t>??? + ??? + 800 cost</t>
+  </si>
+  <si>
+    <t>Jirayu the Rebellious Prince + 1 Anima card (≥ 500 cost) + 800 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00100
@@ -3271,7 +3304,10 @@
     <t>+30 ATK vs Union</t>
   </si>
   <si>
-    <t>Kiyoko the Death Whisper + Silver Spearman + 1000</t>
+    <t>??? + ??? + 1000 cost</t>
+  </si>
+  <si>
+    <t>Kiyoko the Death Whisper + Silver Spearman + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">01010
@@ -3285,13 +3321,13 @@
     <t>Moon Ninja Lady</t>
   </si>
   <si>
-    <t>Once, this card is not ???.</t>
+    <t>Once, this card is ???.</t>
   </si>
   <si>
     <t>Once, this card is not destroyed.</t>
   </si>
   <si>
-    <t>Kiyoko the Death Whisper + 1 Anima card + 1000</t>
+    <t>Kiyoko the Death Whisper + 1 Anima card + 800 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00100
@@ -3305,7 +3341,7 @@
     <t>Imperial Frame</t>
   </si>
   <si>
-    <t>Laser Walker + 1 Cosmic card + 1000</t>
+    <t>Laser Walker + 1 Cosmic card + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00000
@@ -3322,10 +3358,10 @@
     <t>Destroy it at turn’s end, then select all face-up ???.</t>
   </si>
   <si>
-    <t>Destroy it at turn’s end, then select all face-up foe’s card in adjacent cells, destroy them.</t>
-  </si>
-  <si>
-    <t>Striker Comet + 2 Cosmic card + 2000</t>
+    <t>Destroy it at turn's end, then destroy all face-up foe units sharing a border with this card.</t>
+  </si>
+  <si>
+    <t>Striker Comet + 2 Cosmic card + 1000 cost</t>
   </si>
   <si>
     <t xml:space="preserve">10000
@@ -3345,7 +3381,10 @@
     <t>After destroying foe’s card: +80 crystals</t>
   </si>
   <si>
-    <t>2 Mutant cards + 1000 crystals</t>
+    <t>2 ??? + 600 cost</t>
+  </si>
+  <si>
+    <t>2 Mutant cards + 600 cost</t>
   </si>
   <si>
     <t>00000
@@ -3358,13 +3397,13 @@
     <t>Gamma Mermaid</t>
   </si>
   <si>
-    <t>-20 DEF to ???</t>
-  </si>
-  <si>
-    <t>-20 DEF to non-Bio defender</t>
-  </si>
-  <si>
-    <t>1 Gamma cards + 1 Bio card + 1000</t>
+    <t>Non-Bio defender get ???. With Mutagen Flag: +20 ???</t>
+  </si>
+  <si>
+    <t>Non-Bio defender get -20 DEF. With Mutagen Flag: +20 ATK&amp;DEF to all your Bio units</t>
+  </si>
+  <si>
+    <t>1 Gamma cards + 1 Bio card + 500 cost</t>
   </si>
   <si>
     <t xml:space="preserve">00000
@@ -3381,19 +3420,19 @@
     <t>Fujin Raijin Suigin</t>
   </si>
   <si>
-    <t>Fujin + Raijin + Suigin + 1000</t>
+    <t>Fujin + Raijin + Suigin + 1000 cost</t>
   </si>
   <si>
     <t>Dark Invader</t>
   </si>
   <si>
-    <t>Liam the Vastrunner + 1 Cosmic card + 1500</t>
+    <t>Liam the Vastrunner + 1 Cosmic card + 1500 cost</t>
   </si>
   <si>
     <t>Europan Tankmaster</t>
   </si>
   <si>
-    <t>2 Europan cards + 1000</t>
+    <t>2 Europan cards + 1000 cost</t>
   </si>
   <si>
     <t>Nanomites Dragon</t>
@@ -3451,19 +3490,19 @@
     <t xml:space="preserve">Hypnosis </t>
   </si>
   <si>
-    <t>The attacking character cannot attack during their next turn</t>
+    <t>The attacking unit cannot attack during their next turn</t>
   </si>
   <si>
     <t>Flame Trap</t>
   </si>
   <si>
-    <t>Permanently -10 ATK to the Attacking character</t>
+    <t>Permanently -10 ATK to the Attacking unit</t>
   </si>
   <si>
     <t>Echo Barrier</t>
   </si>
   <si>
-    <t>All attacker’s characters cannot attack until the end of this turn</t>
+    <t>This turn, foe cannot perform any more attack.</t>
   </si>
   <si>
     <t>Mana Drain</t>
@@ -3481,7 +3520,7 @@
     <t>Spike Trap</t>
   </si>
   <si>
-    <t>Destroy the attacking character</t>
+    <t>Destroy the attacking unit</t>
   </si>
   <si>
     <t>Snare Trap</t>
@@ -3505,19 +3544,19 @@
     <t>Foul Gas</t>
   </si>
   <si>
-    <t>-5 ATK to all the attacking player’s characters until the end of this turn</t>
+    <t>-5 ATK to all the attacking player’s units until the end of this turn</t>
   </si>
   <si>
     <t>Choking Gas</t>
   </si>
   <si>
-    <t>-20 ATK to all the attacking player’s characters until the end of this turn</t>
+    <t>-20 ATK to all the attacking player’s units until the end of this turn</t>
   </si>
   <si>
     <t>Potent Poison</t>
   </si>
   <si>
-    <t>Attacking character permanently lose 5 ATK and DEF for each trap cards in your void</t>
+    <t>Attacking unit permanently lose 5 ATK and DEF for each trap cards in your void</t>
   </si>
   <si>
     <t>Acid Trap Hole</t>
@@ -3541,55 +3580,55 @@
     <t>Soul Blast</t>
   </si>
   <si>
-    <t>Attacking player lose 150 Crystals for each character cards in your void</t>
+    <t>Attacking player lose 150 Crystals for each unit cards in your void</t>
   </si>
   <si>
     <t>Grudge</t>
   </si>
   <si>
-    <t>-10 ATK to the attacking monster permanently for each character cards in your void</t>
+    <t>-10 ATK to the attacking monster permanently for each unit cards in your void</t>
   </si>
   <si>
     <t>Anti-virus</t>
   </si>
   <si>
-    <t>If attacking character Is Bio affinity, flip a coin. If head, destroy it.</t>
+    <t>If attacking unit Is Bio affinity, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Witch Hunt</t>
   </si>
   <si>
-    <t>If attacking character Is Arcane affinity, flip a coin. If head, destroy it.</t>
+    <t>If attacking unit Is Arcane affinity, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Standoff</t>
   </si>
   <si>
-    <t>If attacking character Is Anima affinity, flip a coin. If head, destroy it.</t>
+    <t>If attacking unit Is Anima affinity, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Apple of Adam</t>
   </si>
   <si>
-    <t>If attacking character Is Divine affinity, flip a coin. If head, destroy it.</t>
+    <t>If attacking unit Is Divine affinity, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Purify</t>
   </si>
   <si>
-    <t>If attacking character Is Chaos affinity, flip a coin. If head, destroy it.</t>
+    <t>If attacking unit Is Chaos affinity, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Solar Flare</t>
   </si>
   <si>
-    <t>If attacking character Is Cosmic affinity, flip a coin. If head, destroy it.</t>
+    <t>If attacking unit Is Cosmic affinity, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Hunting Season</t>
   </si>
   <si>
-    <t>If attacking character Is Nature affinity, flip a coin. If head, destroy it.</t>
+    <t>If attacking unit Is Nature affinity, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Dart Trap</t>
@@ -3601,49 +3640,49 @@
     <t>Science Cage</t>
   </si>
   <si>
-    <t>If attacking character Is Bio affinity, end their turn immediately. Remove all flags from it.</t>
+    <t>If attacking unit Is Bio affinity, end their turn immediately. Remove all flags from it.</t>
   </si>
   <si>
     <t>Loop Hole</t>
   </si>
   <si>
-    <t>If attacking character Is Arcane, the next attack of your opponent on a dead endcard will end the their turn</t>
+    <t>If attacking unit Is Arcane, the next attack of your opponent on a dead endcard will end the their turn</t>
   </si>
   <si>
     <t>Talisman of Light</t>
   </si>
   <si>
-    <t>If attacking character Is Chaos, -20 ATK to that monster permanently</t>
+    <t>If attacking unit Is Chaos, -20 ATK to that monster permanently</t>
   </si>
   <si>
     <t>Forbidden Grail</t>
   </si>
   <si>
-    <t>If attacking character Is Divine, -20 DEF to that monster permanently</t>
+    <t>If attacking unit Is Divine, -20 DEF to that monster permanently</t>
   </si>
   <si>
     <t>Electric Fence</t>
   </si>
   <si>
-    <t>If attacking character Is Nature, it cannot attack for the rest of their next turn</t>
+    <t>If attacking unit Is Nature, it cannot attack for the rest of their next turn</t>
   </si>
   <si>
     <t>Discourage</t>
   </si>
   <si>
-    <t>If attacking character Is Anima -15 ATK to all face-up cards on their field until the end of their turn</t>
+    <t>If attacking unit Is Anima -15 ATK to all face-up cards on their field until the end of their turn</t>
   </si>
   <si>
     <t>Galaxy Toll</t>
   </si>
   <si>
-    <t>If attacking character Is Cosmic, your opponent choose either pay 800 crystal cost. Or it cannot attack for the rest of their next turn</t>
+    <t>If attacking unit Is Cosmic, your opponent choose either pay 800 crystal cost. Or it cannot attack for the rest of their next turn</t>
   </si>
   <si>
     <t>Union Cage</t>
   </si>
   <si>
-    <t>If attacking character Is Union card, that character cannot attack until the end of their next turn.</t>
+    <t>If attacking unit Is Union card, that unit cannot attack until the end of their next turn.</t>
   </si>
   <si>
     <t>Plunder</t>
@@ -3655,31 +3694,31 @@
     <t>Decoy Puppet</t>
   </si>
   <si>
-    <t>This turn, foe cannot attack again.</t>
+    <t>This turn, foe cannot perform any more attack using unit with 400 or less cost.</t>
   </si>
   <si>
     <t>Hard Scale</t>
   </si>
   <si>
-    <t>+5 DEF to all of your card until this turn’s end</t>
+    <t>All of your unit gain +5 DEF in Reckoning until this turn’s end</t>
   </si>
   <si>
     <t>Steel Scale</t>
   </si>
   <si>
-    <t>Can be triggered face-down. +15 DEF to 1 of your card until the end of this turn</t>
+    <t>All of your unit gain +15 DEF in Reckoning until this turn’s end</t>
   </si>
   <si>
     <t>Trick Door</t>
   </si>
   <si>
-    <t>Swap position between 2 face-up characters on your side of the field</t>
+    <t>Swap position between 2 face-up units on your side of the field</t>
   </si>
   <si>
     <t>Boiling Oil</t>
   </si>
   <si>
-    <t>Can be triggered face-down. -10 ATK to 1 of your opponent card until the end of this turn</t>
+    <t>All of foe’s unit get -10 ATK in Reckoning until this turn’s end</t>
   </si>
   <si>
     <t>Lightning Rod</t>
@@ -3709,7 +3748,7 @@
     <t>Red Card</t>
   </si>
   <si>
-    <t>Flip 2 coin, if head, that character cannot attack next turn</t>
+    <t>Flip 2 coin, if head, that unit cannot attack next turn</t>
   </si>
   <si>
     <t>Counter Punch</t>
@@ -3745,19 +3784,19 @@
     <t>Self-destruct</t>
   </si>
   <si>
-    <t>Select 1 of your character. +10 ATK until your next turn’s end, but also destroy it. You pay no cost.</t>
+    <t>Select 1 of your unit. +10 ATK until your next turn’s end, but also destroy it. You pay no cost.</t>
   </si>
   <si>
     <t>Bounty</t>
   </si>
   <si>
-    <t>Until the end of your turn, if you destroy that character, you receive 200 crystals</t>
+    <t>Until the end of your turn, if you destroy that unit, you receive 200 crystals</t>
   </si>
   <si>
     <t>Pepper Spray</t>
   </si>
   <si>
-    <t>Flip 2 coin, if head, the attacking character lose -5 ATK until the end of their next turn.</t>
+    <t>Flip 2 coin, if head, the attacking unit lose -5 ATK until the end of their next turn.</t>
   </si>
   <si>
     <t>Curse of Pain</t>
@@ -3820,7 +3859,7 @@
     <t>Corrupted Spy</t>
   </si>
   <si>
-    <t>Reveal 3 square on opponent's side of the field. If you found any trap or Character, you pay 700 Crystal or each card found.</t>
+    <t>Reveal 3 square on opponent's side of the field. If you found any trap or Unit, you pay 700 Crystal or each card found.</t>
   </si>
   <si>
     <t>Tease</t>
@@ -3832,13 +3871,13 @@
     <t>Bribe</t>
   </si>
   <si>
-    <t>Your foe can choose to reveal a character card and receive 700 crystals or do nothing</t>
+    <t>Your foe can choose to reveal a unit card and receive 700 crystals or do nothing</t>
   </si>
   <si>
     <t>Release Mutagen</t>
   </si>
   <si>
-    <t>Select and reveal (if face-down) 1 of your Bio Character on the field. Add Mutagen Flag to it.</t>
+    <t>Select and reveal (if face-down) 1 of your Bio Unit on the field. Add Mutagen Flag to it.</t>
   </si>
   <si>
     <t>Prayer</t>
@@ -3850,7 +3889,7 @@
     <t>Arcane Nova</t>
   </si>
   <si>
-    <t>Destroy 5 face-up opponent Characters. You opponent do not lose crystals under this effect. Discard all of your Tech afterward.</t>
+    <t>Destroy 5 face-up opponent Units. You opponent do not lose crystals under this effect. Discard all of your Tech afterward.</t>
   </si>
   <si>
     <t>Rift Strike</t>
@@ -3862,25 +3901,25 @@
     <t>Great Diplomacy</t>
   </si>
   <si>
-    <t>Turn all characters on your field face up</t>
+    <t>Turn all units on your field face up</t>
   </si>
   <si>
     <t>War Supply</t>
   </si>
   <si>
-    <t>+10 ATK&amp;DEF for all face up characters until the end of this turn.</t>
+    <t>Your units get +10 ATK&amp;DEF in Reckoning until turn’s end</t>
   </si>
   <si>
     <t>Harsh Training</t>
   </si>
   <si>
-    <t xml:space="preserve"> +10 ATK permanently for 1 character. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+10 ATK permanently to one of your unit. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Illegal Steroid</t>
   </si>
   <si>
-    <t>+30 ATK for 1 character until the end of this turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+30 ATK for 1 unit until the end of this turn.</t>
   </si>
   <si>
     <t>Secret Dagger</t>
@@ -3898,31 +3937,31 @@
     <t xml:space="preserve">Bulletproof Vest </t>
   </si>
   <si>
-    <t>+15 DEF permanently for 1 face-up character. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+15 DEF permanently for 1 face-up unit. If use on face-down card, flip it up.</t>
   </si>
   <si>
     <t>Siege Cannon</t>
   </si>
   <si>
-    <t>Until the end of this turn, once, foe’s defending character is destroyed.</t>
+    <t>Until the end of this turn, once, foe’s defending unit is destroyed.</t>
   </si>
   <si>
     <t>Silence Agent</t>
   </si>
   <si>
-    <t>Destroy 1 face-up card</t>
+    <t>Destroy 1 of foe’s face-up card</t>
   </si>
   <si>
     <t>Accident</t>
   </si>
   <si>
-    <t>Destroy 1 face-up foe’s card. If there is no face-up card, foe must chooses the target. Foe pay no cost.</t>
+    <t>Destroy 1 of foe’s face-up card. If there is no face-up card, foe must chooses the target. Foe pay no cost.</t>
   </si>
   <si>
     <t>Berserk</t>
   </si>
   <si>
-    <t>Select 1 face-up character. Until this turn, that character can attack 3 times. Also, you can't command any other character to attack. You can’t use this card if you’ve already commanded an attack.</t>
+    <t>Select 1 of your face-up unit. You get 1 additional attack, but can only perform attack with that unit. You can’t use this card if you’ve already performed any attack.</t>
   </si>
   <si>
     <t>Radar</t>
@@ -3934,37 +3973,37 @@
     <t>Palace Party</t>
   </si>
   <si>
-    <t>Reveal 1 of your face-down character. Your opponent must reveal 1 of their face-down character (if any)</t>
+    <t>Reveal 1 of your face-down unit. Your opponent must reveal 1 of their face-down unit (if any)</t>
   </si>
   <si>
     <t>Essence Transfer</t>
   </si>
   <si>
-    <t>Choose 1 of your Characters. Move all its ATK and DEF bonuses or debuffs to another face-up Character on your field. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>Choose 1 of your Units. Move all its ATK and DEF bonuses or debuffs to another face-up Unit on your field. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Blood Ritual</t>
   </si>
   <si>
-    <t>Destroy 1 face-up card on the your field. You don't pay Crystal cost for the destroyed card. Choose 1 of your opponent's face-up character. Its ATK and DEF becomes 0 permanently</t>
+    <t>Destroy 1 face-up card on the your field. You don't pay Crystal cost for the destroyed card. Choose 1 of your opponent's face-up unit. Its ATK and DEF becomes 0 permanently</t>
   </si>
   <si>
     <t>Arcane Duplication</t>
   </si>
   <si>
-    <t>Choose 1 of your face-up Characters. Create a token copy of it on an empty square on your field. Destroy it at the start of your next turn.</t>
+    <t>Choose 1 of your face-up Units. Create a token copy of it on an empty square on your field. Destroy it at the start of your next turn.</t>
   </si>
   <si>
     <t xml:space="preserve">Time Travel </t>
   </si>
   <si>
-    <t>Once only, revive 1 character to any unoccupied or empty cell in face-up position. Double its crystal cost.</t>
+    <t>Once only, revive 1 unit to any unoccupied or empty cell in face-up position. Double its crystal cost.</t>
   </si>
   <si>
     <t>Resurrection</t>
   </si>
   <si>
-    <t>Once, revive 1 character. It has no ATK,DEF, or ability.</t>
+    <t>Once, revive 1 unit. It has no ATK,DEF, or ability.</t>
   </si>
   <si>
     <t>Tech Copy</t>
@@ -4000,7 +4039,7 @@
     <t xml:space="preserve">Yin Yang Swap </t>
   </si>
   <si>
-    <t>Swap ATK and DEF on 1 face-up character until the end of this turn</t>
+    <t>Swap ATK and DEF on 1 face-up unit until the end of this turn</t>
   </si>
   <si>
     <t>Coin on the Street</t>
@@ -4054,7 +4093,7 @@
     <t>Phony Fight</t>
   </si>
   <si>
-    <t>-10 DEF to 1 face-up character on the field until the end of this turn. Your opponent receive 500 crystals</t>
+    <t>-10 DEF to 1 face-up unit on the field until the end of this turn. Your opponent receive 500 crystals</t>
   </si>
   <si>
     <t>Facetious</t>
@@ -4078,25 +4117,25 @@
     <t>Flimsy Axe</t>
   </si>
   <si>
-    <t>Flip a coin. If head, +5 ATK to one of your character until the end of your turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>Flip a coin. If head, +5 ATK to one of your unit until the end of your turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Flimsy Shield</t>
   </si>
   <si>
-    <t>Flip a coin. If head, +5 DEF to one of your character until the end of your opponent’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>Flip a coin. If head, +5 DEF to one of your unit until the end of your opponent’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>All-out Tactics</t>
   </si>
   <si>
-    <t>+10 ATK to one of your character permanently. But its DEF becomes 0 permanently. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+10 ATK to one of your unit permanently. But its DEF becomes 0 permanently. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Fair Fight</t>
   </si>
   <si>
-    <t>You and your opponent select 1 your their character. +10 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>You and your opponent select 1 your their unit. +10 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Greater Telepathy</t>
@@ -4114,13 +4153,13 @@
     <t>Old Spear</t>
   </si>
   <si>
-    <t>+5 ATK to one of your character until the end of your turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+5 ATK to one of your unit until the end of your turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Old Shield</t>
   </si>
   <si>
-    <t>+5 DEF to one of your character until the end of your opponent’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+5 DEF to one of your unit until the end of your opponent’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Provoke</t>
@@ -4156,19 +4195,19 @@
     <t>Pretify</t>
   </si>
   <si>
-    <t>+20 DEF to one of your or your opponent’s face-up character permanently, but its ATK becomes 0 permanently. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+20 DEF to one of your or your opponent’s face-up unit permanently, but its ATK becomes 0 permanently. If used on your face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Stone Skin</t>
   </si>
   <si>
-    <t>+10 DEF to one of your face-up character permanently, but its ATK becomes 0 permanently. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+10 DEF to one of your face-up unit permanently, but its ATK becomes 0 permanently. If used on your face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Battle Royale</t>
   </si>
   <si>
-    <t>You and your opponent select 1 your their character. +30 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>You and your opponent select 1 your their unit. +30 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Guerrilla Tactics</t>
@@ -4258,7 +4297,7 @@
     <t>Ouija</t>
   </si>
   <si>
-    <t>Reveal cell on opponent's side of the field up to number of your character in the void.</t>
+    <t>Reveal cell on opponent's side of the field up to number of your unit in the void.</t>
   </si>
   <si>
     <t>Deep Mine</t>
@@ -4288,7 +4327,7 @@
     <t>GPS Tracker</t>
   </si>
   <si>
-    <t>Reveal 2 adjacent cells next to face-up character on opponent's side of the field.</t>
+    <t>Reveal 2 adjacent cells next to face-up unit on opponent's side of the field.</t>
   </si>
   <si>
     <t>Blessing</t>
@@ -4312,7 +4351,10 @@
     <t>Crack the Whip</t>
   </si>
   <si>
-    <t>One of your character card can attack twice. But it cannot attack again next turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+    <t>One of your unit card can attack twice. But it cannot attack again next turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+  </si>
+  <si>
+    <t>Need Revise</t>
   </si>
   <si>
     <t>Full open fire</t>
@@ -4384,13 +4426,13 @@
     <t>Punching Bag</t>
   </si>
   <si>
-    <t>One of your character ATK and DEF becomes 0 permanently. It cannot be destroyed until the end of opponent’s turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+    <t>One of your unit ATK and DEF becomes 0 permanently. It cannot be destroyed until the end of opponent’s turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Scattered Shot</t>
   </si>
   <si>
-    <t>Flip 3 coins. Destroy opponent’s face-up character equal to number of heads. You opponent do not lose crystals under this effect</t>
+    <t>Flip 3 coins. Destroy opponent’s face-up unit equal to number of heads. You opponent do not lose crystals under this effect</t>
   </si>
   <si>
     <t>Spotlight</t>
@@ -4409,6 +4451,12 @@
   </si>
   <si>
     <t>Select 1 face-up opponent’s card. Destroy other face-up cards on that same columns as the selected cell. Your opponent don’t pay crystal cost.</t>
+  </si>
+  <si>
+    <t>Mining Season</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both player can only target face-down card</t>
   </si>
   <si>
     <t>Expected</t>
@@ -7081,10 +7129,10 @@
         <v>1200</v>
       </c>
       <c r="D25" s="16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E25" s="16">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s" s="17">
         <v>11</v>
@@ -7101,7 +7149,7 @@
       </c>
       <c r="K25" s="16">
         <f>(D25*6)+(E25*4)</f>
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="L25" t="s" s="17">
         <v>35</v>
@@ -7601,7 +7649,7 @@
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
     </row>
-    <row r="38" ht="44.05" customHeight="1">
+    <row r="38" ht="56.05" customHeight="1">
       <c r="A38" t="s" s="8">
         <v>98</v>
       </c>
@@ -7697,7 +7745,7 @@
         <v>33</v>
       </c>
       <c r="C40" s="16">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D40" s="16">
         <v>20</v>
@@ -7986,7 +8034,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" ht="80.05" customHeight="1">
+    <row r="47" ht="68.05" customHeight="1">
       <c r="A47" t="s" s="8">
         <v>114</v>
       </c>
@@ -8064,7 +8112,7 @@
       <c r="O48" s="10"/>
       <c r="P48" s="10"/>
     </row>
-    <row r="49" ht="56.05" customHeight="1">
+    <row r="49" ht="44.05" customHeight="1">
       <c r="A49" t="s" s="8">
         <v>117</v>
       </c>
@@ -8776,7 +8824,7 @@
         <v>33</v>
       </c>
       <c r="C67" s="16">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D67" s="16">
         <v>10</v>
@@ -18017,7 +18065,7 @@
         <v>45</v>
       </c>
       <c r="E308" s="16">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F308" t="s" s="17">
         <v>11</v>
@@ -18034,7 +18082,7 @@
       </c>
       <c r="K308" s="16">
         <f>(D308*6)+(E308*4)</f>
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="L308" t="s" s="17">
         <v>35</v>
@@ -19412,10 +19460,10 @@
         <v>33</v>
       </c>
       <c r="C351" s="16">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="D351" s="16">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E351" s="16">
         <v>40</v>
@@ -19435,7 +19483,7 @@
       </c>
       <c r="K351" s="16">
         <f>(D351*6)+(E351*4)</f>
-        <v>490</v>
+        <v>580</v>
       </c>
       <c r="L351" t="s" s="17">
         <v>35</v>
@@ -19788,10 +19836,10 @@
         <v>33</v>
       </c>
       <c r="C363" s="16">
-        <v>790</v>
+        <v>1000</v>
       </c>
       <c r="D363" s="16">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E363" s="16">
         <v>45</v>
@@ -19811,7 +19859,7 @@
       </c>
       <c r="K363" s="16">
         <f>(D363*6)+(E363*4)</f>
-        <v>450</v>
+        <v>660</v>
       </c>
       <c r="L363" t="s" s="17">
         <v>35</v>
@@ -19921,7 +19969,7 @@
         <v>1100</v>
       </c>
       <c r="D367" s="16">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E367" s="16">
         <v>80</v>
@@ -19941,7 +19989,7 @@
       </c>
       <c r="K367" s="16">
         <f>(D367*6)+(E367*4)</f>
-        <v>860</v>
+        <v>920</v>
       </c>
       <c r="L367" t="s" s="17">
         <v>35</v>
@@ -24753,7 +24801,9 @@
       <c r="L9" t="s" s="17">
         <v>694</v>
       </c>
-      <c r="M9" s="10"/>
+      <c r="M9" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N9" t="s" s="17">
         <v>35</v>
       </c>
@@ -24932,15 +24982,17 @@
         <v>39</v>
       </c>
       <c r="J14" t="s" s="17">
+        <v>660</v>
+      </c>
+      <c r="K14" t="s" s="17">
         <v>717</v>
       </c>
-      <c r="K14" t="s" s="17">
+      <c r="L14" t="s" s="17">
         <v>718</v>
       </c>
-      <c r="L14" t="s" s="17">
-        <v>719</v>
-      </c>
-      <c r="M14" s="10"/>
+      <c r="M14" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N14" t="s" s="17">
         <v>35</v>
       </c>
@@ -24948,7 +25000,7 @@
     </row>
     <row r="15" ht="68.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B15" t="s" s="9">
         <v>659</v>
@@ -24965,21 +25017,23 @@
       </c>
       <c r="G15" s="10"/>
       <c r="H15" t="s" s="17">
+        <v>720</v>
+      </c>
+      <c r="I15" t="s" s="17">
         <v>721</v>
       </c>
-      <c r="I15" t="s" s="17">
+      <c r="J15" t="s" s="17">
+        <v>660</v>
+      </c>
+      <c r="K15" t="s" s="17">
         <v>722</v>
       </c>
-      <c r="J15" t="s" s="17">
-        <v>708</v>
-      </c>
-      <c r="K15" t="s" s="17">
+      <c r="L15" t="s" s="17">
         <v>723</v>
       </c>
-      <c r="L15" t="s" s="17">
-        <v>724</v>
-      </c>
-      <c r="M15" s="10"/>
+      <c r="M15" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N15" t="s" s="17">
         <v>35</v>
       </c>
@@ -24987,7 +25041,7 @@
     </row>
     <row r="16" ht="68.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B16" t="s" s="9">
         <v>659</v>
@@ -25004,13 +25058,13 @@
       </c>
       <c r="G16" s="10"/>
       <c r="H16" t="s" s="17">
+        <v>725</v>
+      </c>
+      <c r="I16" t="s" s="17">
         <v>726</v>
       </c>
-      <c r="I16" t="s" s="17">
+      <c r="J16" t="s" s="17">
         <v>727</v>
-      </c>
-      <c r="J16" t="s" s="17">
-        <v>660</v>
       </c>
       <c r="K16" t="s" s="17">
         <v>728</v>
@@ -25018,7 +25072,9 @@
       <c r="L16" t="s" s="17">
         <v>729</v>
       </c>
-      <c r="M16" s="10"/>
+      <c r="M16" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N16" t="s" s="17">
         <v>35</v>
       </c>
@@ -25049,7 +25105,7 @@
         <v>732</v>
       </c>
       <c r="J17" t="s" s="17">
-        <v>660</v>
+        <v>727</v>
       </c>
       <c r="K17" t="s" s="17">
         <v>733</v>
@@ -25057,7 +25113,9 @@
       <c r="L17" t="s" s="17">
         <v>734</v>
       </c>
-      <c r="M17" s="10"/>
+      <c r="M17" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N17" t="s" s="17">
         <v>35</v>
       </c>
@@ -25088,15 +25146,17 @@
         <v>737</v>
       </c>
       <c r="J18" t="s" s="17">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="K18" t="s" s="17">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L18" t="s" s="17">
-        <v>739</v>
-      </c>
-      <c r="M18" s="10"/>
+        <v>740</v>
+      </c>
+      <c r="M18" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N18" t="s" s="17">
         <v>35</v>
       </c>
@@ -25104,7 +25164,7 @@
     </row>
     <row r="19" ht="68.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B19" t="s" s="9">
         <v>659</v>
@@ -25121,21 +25181,23 @@
       </c>
       <c r="G19" s="10"/>
       <c r="H19" t="s" s="17">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I19" t="s" s="17">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J19" t="s" s="17">
-        <v>660</v>
+        <v>744</v>
       </c>
       <c r="K19" t="s" s="17">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="L19" t="s" s="17">
         <v>688</v>
       </c>
-      <c r="M19" s="10"/>
+      <c r="M19" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N19" t="s" s="17">
         <v>35</v>
       </c>
@@ -25143,7 +25205,7 @@
     </row>
     <row r="20" ht="68.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B20" t="s" s="9">
         <v>659</v>
@@ -25160,21 +25222,23 @@
       </c>
       <c r="G20" s="10"/>
       <c r="H20" t="s" s="17">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="I20" t="s" s="17">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="J20" t="s" s="17">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="K20" t="s" s="17">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="L20" t="s" s="17">
-        <v>749</v>
-      </c>
-      <c r="M20" s="10"/>
+        <v>751</v>
+      </c>
+      <c r="M20" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N20" t="s" s="17">
         <v>35</v>
       </c>
@@ -25182,7 +25246,7 @@
     </row>
     <row r="21" ht="68.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B21" t="s" s="9">
         <v>659</v>
@@ -25199,19 +25263,19 @@
       </c>
       <c r="G21" s="10"/>
       <c r="H21" t="s" s="17">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="I21" t="s" s="17">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="J21" t="s" s="17">
         <v>660</v>
       </c>
       <c r="K21" t="s" s="17">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="L21" t="s" s="17">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
@@ -25219,7 +25283,7 @@
     </row>
     <row r="22" ht="68.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B22" t="s" s="9">
         <v>659</v>
@@ -25236,19 +25300,19 @@
       </c>
       <c r="G22" s="10"/>
       <c r="H22" t="s" s="17">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="I22" t="s" s="17">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="J22" t="s" s="17">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="K22" t="s" s="17">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="L22" t="s" s="17">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
@@ -25256,7 +25320,7 @@
     </row>
     <row r="23" ht="80.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B23" t="s" s="9">
         <v>659</v>
@@ -25273,19 +25337,19 @@
       </c>
       <c r="G23" s="10"/>
       <c r="H23" t="s" s="17">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="I23" t="s" s="17">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="J23" t="s" s="17">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="K23" t="s" s="17">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="L23" t="s" s="17">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
@@ -25293,7 +25357,7 @@
     </row>
     <row r="24" ht="68.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B24" t="s" s="9">
         <v>659</v>
@@ -25310,19 +25374,19 @@
       </c>
       <c r="G24" s="10"/>
       <c r="H24" t="s" s="17">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="I24" t="s" s="17">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="J24" t="s" s="17">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="K24" t="s" s="17">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="L24" t="s" s="17">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
@@ -25330,7 +25394,7 @@
     </row>
     <row r="25" ht="68.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B25" t="s" s="9">
         <v>659</v>
@@ -25347,19 +25411,19 @@
       </c>
       <c r="G25" s="10"/>
       <c r="H25" t="s" s="17">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="I25" t="s" s="17">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="J25" t="s" s="17">
         <v>660</v>
       </c>
       <c r="K25" t="s" s="17">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="L25" t="s" s="17">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
@@ -25367,7 +25431,7 @@
     </row>
     <row r="26" ht="68.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B26" t="s" s="9">
         <v>659</v>
@@ -25390,15 +25454,17 @@
         <v>39</v>
       </c>
       <c r="J26" t="s" s="17">
-        <v>660</v>
+        <v>727</v>
       </c>
       <c r="K26" t="s" s="17">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="L26" t="s" s="17">
-        <v>780</v>
-      </c>
-      <c r="M26" s="10"/>
+        <v>782</v>
+      </c>
+      <c r="M26" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N26" t="s" s="17">
         <v>35</v>
       </c>
@@ -25406,7 +25472,7 @@
     </row>
     <row r="27" ht="68.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B27" t="s" s="9">
         <v>659</v>
@@ -25423,19 +25489,19 @@
       </c>
       <c r="G27" s="10"/>
       <c r="H27" t="s" s="17">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="I27" t="s" s="17">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="J27" t="s" s="17">
         <v>660</v>
       </c>
       <c r="K27" t="s" s="17">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="L27" t="s" s="17">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
@@ -25443,7 +25509,7 @@
     </row>
     <row r="28" ht="92.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B28" t="s" s="9">
         <v>659</v>
@@ -25460,21 +25526,23 @@
       </c>
       <c r="G28" s="10"/>
       <c r="H28" t="s" s="17">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="I28" t="s" s="17">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="J28" t="s" s="17">
-        <v>660</v>
+        <v>791</v>
       </c>
       <c r="K28" t="s" s="17">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="L28" t="s" s="17">
-        <v>790</v>
-      </c>
-      <c r="M28" s="10"/>
+        <v>793</v>
+      </c>
+      <c r="M28" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N28" t="s" s="17">
         <v>35</v>
       </c>
@@ -25482,7 +25550,7 @@
     </row>
     <row r="29" ht="68.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B29" t="s" s="9">
         <v>659</v>
@@ -25499,19 +25567,19 @@
       </c>
       <c r="G29" s="10"/>
       <c r="H29" t="s" s="17">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="I29" t="s" s="17">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="J29" t="s" s="17">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="K29" t="s" s="17">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="L29" t="s" s="17">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -25519,7 +25587,7 @@
     </row>
     <row r="30" ht="68.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B30" t="s" s="9">
         <v>659</v>
@@ -25545,10 +25613,10 @@
         <v>660</v>
       </c>
       <c r="K30" t="s" s="17">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="L30" t="s" s="17">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
@@ -25556,7 +25624,7 @@
     </row>
     <row r="31" ht="80.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B31" t="s" s="9">
         <v>659</v>
@@ -25573,19 +25641,19 @@
       </c>
       <c r="G31" s="10"/>
       <c r="H31" t="s" s="17">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="I31" t="s" s="17">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="J31" t="s" s="17">
-        <v>803</v>
+        <v>686</v>
       </c>
       <c r="K31" t="s" s="17">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="L31" t="s" s="17">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
@@ -25593,7 +25661,7 @@
     </row>
     <row r="32" ht="68.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B32" t="s" s="9">
         <v>659</v>
@@ -25610,21 +25678,23 @@
       </c>
       <c r="G32" s="10"/>
       <c r="H32" t="s" s="17">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="I32" t="s" s="17">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="J32" t="s" s="17">
-        <v>660</v>
+        <v>744</v>
       </c>
       <c r="K32" t="s" s="17">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="L32" t="s" s="17">
-        <v>810</v>
-      </c>
-      <c r="M32" s="10"/>
+        <v>812</v>
+      </c>
+      <c r="M32" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N32" t="s" s="17">
         <v>35</v>
       </c>
@@ -25632,7 +25702,7 @@
     </row>
     <row r="33" ht="68.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B33" t="s" s="9">
         <v>659</v>
@@ -25655,15 +25725,17 @@
         <v>39</v>
       </c>
       <c r="J33" t="s" s="17">
-        <v>660</v>
+        <v>738</v>
       </c>
       <c r="K33" t="s" s="17">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="L33" t="s" s="17">
-        <v>813</v>
-      </c>
-      <c r="M33" s="10"/>
+        <v>815</v>
+      </c>
+      <c r="M33" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N33" t="s" s="17">
         <v>35</v>
       </c>
@@ -25671,7 +25743,7 @@
     </row>
     <row r="34" ht="68.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B34" t="s" s="9">
         <v>659</v>
@@ -25688,21 +25760,23 @@
       </c>
       <c r="G34" s="10"/>
       <c r="H34" t="s" s="17">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="I34" t="s" s="17">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="J34" t="s" s="17">
-        <v>660</v>
+        <v>819</v>
       </c>
       <c r="K34" t="s" s="17">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="L34" t="s" s="17">
-        <v>818</v>
-      </c>
-      <c r="M34" s="10"/>
+        <v>821</v>
+      </c>
+      <c r="M34" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N34" t="s" s="17">
         <v>35</v>
       </c>
@@ -25710,7 +25784,7 @@
     </row>
     <row r="35" ht="68.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B35" t="s" s="9">
         <v>659</v>
@@ -25733,15 +25807,17 @@
         <v>39</v>
       </c>
       <c r="J35" t="s" s="17">
-        <v>747</v>
+        <v>823</v>
       </c>
       <c r="K35" t="s" s="17">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L35" t="s" s="17">
-        <v>821</v>
-      </c>
-      <c r="M35" s="10"/>
+        <v>825</v>
+      </c>
+      <c r="M35" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N35" t="s" s="17">
         <v>35</v>
       </c>
@@ -25749,7 +25825,7 @@
     </row>
     <row r="36" ht="68.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B36" t="s" s="9">
         <v>659</v>
@@ -25766,19 +25842,19 @@
       </c>
       <c r="G36" s="10"/>
       <c r="H36" t="s" s="17">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="I36" t="s" s="17">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="J36" t="s" s="17">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="K36" t="s" s="17">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="L36" t="s" s="17">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
@@ -25786,7 +25862,7 @@
     </row>
     <row r="37" ht="68.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B37" t="s" s="9">
         <v>659</v>
@@ -25809,15 +25885,17 @@
         <v>39</v>
       </c>
       <c r="J37" t="s" s="17">
-        <v>747</v>
+        <v>833</v>
       </c>
       <c r="K37" t="s" s="17">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="L37" t="s" s="17">
-        <v>830</v>
-      </c>
-      <c r="M37" s="10"/>
+        <v>835</v>
+      </c>
+      <c r="M37" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N37" t="s" s="17">
         <v>35</v>
       </c>
@@ -25825,7 +25903,7 @@
     </row>
     <row r="38" ht="80.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="B38" t="s" s="9">
         <v>659</v>
@@ -25842,19 +25920,19 @@
       </c>
       <c r="G38" s="10"/>
       <c r="H38" t="s" s="17">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="I38" t="s" s="17">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="J38" t="s" s="17">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="K38" t="s" s="17">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L38" t="s" s="17">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -25862,7 +25940,7 @@
     </row>
     <row r="39" ht="68.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B39" t="s" s="9">
         <v>659</v>
@@ -25879,21 +25957,23 @@
       </c>
       <c r="G39" s="10"/>
       <c r="H39" t="s" s="17">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="I39" t="s" s="17">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="J39" t="s" s="17">
         <v>666</v>
       </c>
       <c r="K39" t="s" s="17">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="L39" t="s" s="17">
-        <v>841</v>
-      </c>
-      <c r="M39" s="10"/>
+        <v>846</v>
+      </c>
+      <c r="M39" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N39" t="s" s="17">
         <v>35</v>
       </c>
@@ -25901,7 +25981,7 @@
     </row>
     <row r="40" ht="68.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="B40" t="s" s="9">
         <v>659</v>
@@ -25918,21 +25998,23 @@
       </c>
       <c r="G40" s="10"/>
       <c r="H40" t="s" s="17">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="I40" t="s" s="17">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="J40" t="s" s="17">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="K40" t="s" s="17">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="L40" t="s" s="17">
-        <v>847</v>
-      </c>
-      <c r="M40" s="10"/>
+        <v>852</v>
+      </c>
+      <c r="M40" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N40" t="s" s="17">
         <v>35</v>
       </c>
@@ -25940,7 +26022,7 @@
     </row>
     <row r="41" ht="68.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B41" t="s" s="9">
         <v>659</v>
@@ -25963,15 +26045,17 @@
         <v>39</v>
       </c>
       <c r="J41" t="s" s="17">
-        <v>758</v>
+        <v>854</v>
       </c>
       <c r="K41" t="s" s="17">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="L41" t="s" s="17">
-        <v>850</v>
-      </c>
-      <c r="M41" s="10"/>
+        <v>856</v>
+      </c>
+      <c r="M41" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N41" t="s" s="17">
         <v>35</v>
       </c>
@@ -25979,7 +26063,7 @@
     </row>
     <row r="42" ht="68.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="B42" t="s" s="9">
         <v>659</v>
@@ -25996,19 +26080,19 @@
       </c>
       <c r="G42" s="10"/>
       <c r="H42" t="s" s="17">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="I42" t="s" s="17">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="J42" t="s" s="17">
         <v>660</v>
       </c>
       <c r="K42" t="s" s="17">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="L42" t="s" s="17">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
@@ -26016,7 +26100,7 @@
     </row>
     <row r="43" ht="80.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="B43" t="s" s="9">
         <v>659</v>
@@ -26033,19 +26117,19 @@
       </c>
       <c r="G43" s="10"/>
       <c r="H43" t="s" s="17">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="I43" t="s" s="17">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="J43" t="s" s="17">
         <v>660</v>
       </c>
       <c r="K43" t="s" s="17">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="L43" t="s" s="17">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
@@ -26053,7 +26137,7 @@
     </row>
     <row r="44" ht="68.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="B44" t="s" s="9">
         <v>659</v>
@@ -26070,19 +26154,19 @@
       </c>
       <c r="G44" s="10"/>
       <c r="H44" t="s" s="17">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="I44" t="s" s="17">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="J44" t="s" s="17">
-        <v>747</v>
+        <v>870</v>
       </c>
       <c r="K44" t="s" s="17">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="L44" t="s" s="17">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
@@ -26090,7 +26174,7 @@
     </row>
     <row r="45" ht="68.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="B45" t="s" s="9">
         <v>659</v>
@@ -26107,19 +26191,19 @@
       </c>
       <c r="G45" s="10"/>
       <c r="H45" t="s" s="17">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="I45" t="s" s="17">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="J45" t="s" s="17">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="K45" t="s" s="17">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="L45" t="s" s="17">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10"/>
@@ -26127,7 +26211,7 @@
     </row>
     <row r="46" ht="68.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B46" t="s" s="9">
         <v>659</v>
@@ -26144,21 +26228,23 @@
       </c>
       <c r="G46" s="10"/>
       <c r="H46" t="s" s="17">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="I46" t="s" s="17">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="J46" t="s" s="17">
-        <v>869</v>
+        <v>882</v>
       </c>
       <c r="K46" t="s" s="17">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="L46" t="s" s="17">
-        <v>876</v>
-      </c>
-      <c r="M46" s="10"/>
+        <v>884</v>
+      </c>
+      <c r="M46" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N46" t="s" s="17">
         <v>35</v>
       </c>
@@ -26166,7 +26252,7 @@
     </row>
     <row r="47" ht="68.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="B47" t="s" s="9">
         <v>659</v>
@@ -26183,19 +26269,19 @@
       </c>
       <c r="G47" s="10"/>
       <c r="H47" t="s" s="17">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="I47" t="s" s="17">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="J47" t="s" s="17">
         <v>660</v>
       </c>
       <c r="K47" t="s" s="17">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="L47" t="s" s="17">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
@@ -26203,7 +26289,7 @@
     </row>
     <row r="48" ht="68.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="B48" t="s" s="9">
         <v>659</v>
@@ -26220,19 +26306,19 @@
       </c>
       <c r="G48" s="10"/>
       <c r="H48" t="s" s="17">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="I48" t="s" s="17">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="J48" t="s" s="17">
         <v>660</v>
       </c>
       <c r="K48" t="s" s="17">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="L48" t="s" s="17">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
@@ -26240,7 +26326,7 @@
     </row>
     <row r="49" ht="68.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="B49" t="s" s="9">
         <v>659</v>
@@ -26263,15 +26349,17 @@
         <v>39</v>
       </c>
       <c r="J49" t="s" s="17">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="K49" t="s" s="17">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="L49" t="s" s="17">
-        <v>889</v>
-      </c>
-      <c r="M49" s="10"/>
+        <v>897</v>
+      </c>
+      <c r="M49" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N49" t="s" s="17">
         <v>35</v>
       </c>
@@ -26279,7 +26367,7 @@
     </row>
     <row r="50" ht="68.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="B50" t="s" s="9">
         <v>659</v>
@@ -26296,19 +26384,19 @@
       </c>
       <c r="G50" s="10"/>
       <c r="H50" t="s" s="17">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="I50" t="s" s="17">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="J50" t="s" s="17">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="K50" t="s" s="17">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="L50" t="s" s="17">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10"/>
@@ -26316,7 +26404,7 @@
     </row>
     <row r="51" ht="68.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="B51" t="s" s="9">
         <v>659</v>
@@ -26333,19 +26421,19 @@
       </c>
       <c r="G51" s="10"/>
       <c r="H51" t="s" s="17">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="I51" t="s" s="17">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="J51" t="s" s="17">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="K51" t="s" s="17">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="L51" t="s" s="17">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10"/>
@@ -26353,7 +26441,7 @@
     </row>
     <row r="52" ht="80.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="B52" t="s" s="9">
         <v>659</v>
@@ -26370,19 +26458,23 @@
       </c>
       <c r="G52" s="10"/>
       <c r="H52" t="s" s="17">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="I52" t="s" s="17">
-        <v>897</v>
-      </c>
-      <c r="J52" s="10"/>
+        <v>905</v>
+      </c>
+      <c r="J52" t="s" s="17">
+        <v>906</v>
+      </c>
       <c r="K52" t="s" s="17">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="L52" t="s" s="17">
-        <v>899</v>
-      </c>
-      <c r="M52" s="10"/>
+        <v>908</v>
+      </c>
+      <c r="M52" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N52" t="s" s="17">
         <v>35</v>
       </c>
@@ -26390,7 +26482,7 @@
     </row>
     <row r="53" ht="92.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="B53" t="s" s="9">
         <v>659</v>
@@ -26407,19 +26499,19 @@
       </c>
       <c r="G53" s="10"/>
       <c r="H53" t="s" s="17">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="I53" t="s" s="17">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="J53" t="s" s="17">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="K53" t="s" s="17">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="L53" t="s" s="17">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
@@ -26427,7 +26519,7 @@
     </row>
     <row r="54" ht="68.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="B54" t="s" s="9">
         <v>659</v>
@@ -26444,19 +26536,19 @@
       </c>
       <c r="G54" s="10"/>
       <c r="H54" t="s" s="17">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="I54" t="s" s="17">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="J54" t="s" s="17">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="K54" t="s" s="17">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="L54" t="s" s="17">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10"/>
@@ -26464,7 +26556,7 @@
     </row>
     <row r="55" ht="80.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="B55" t="s" s="9">
         <v>659</v>
@@ -26482,14 +26574,14 @@
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
       <c r="I55" t="s" s="17">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="J55" s="10"/>
       <c r="K55" t="s" s="17">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="L55" t="s" s="17">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10"/>
@@ -26497,7 +26589,7 @@
     </row>
     <row r="56" ht="68.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="B56" t="s" s="9">
         <v>659</v>
@@ -26514,19 +26606,23 @@
       </c>
       <c r="G56" s="10"/>
       <c r="H56" t="s" s="17">
-        <v>917</v>
+        <v>926</v>
       </c>
       <c r="I56" t="s" s="17">
-        <v>918</v>
-      </c>
-      <c r="J56" s="10"/>
+        <v>927</v>
+      </c>
+      <c r="J56" t="s" s="17">
+        <v>928</v>
+      </c>
       <c r="K56" t="s" s="17">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="L56" t="s" s="17">
-        <v>911</v>
-      </c>
-      <c r="M56" s="10"/>
+        <v>920</v>
+      </c>
+      <c r="M56" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N56" t="s" s="17">
         <v>35</v>
       </c>
@@ -26534,7 +26630,7 @@
     </row>
     <row r="57" ht="80.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="B57" t="s" s="9">
         <v>659</v>
@@ -26551,17 +26647,17 @@
       </c>
       <c r="G57" s="10"/>
       <c r="H57" t="s" s="17">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="I57" t="s" s="17">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="J57" s="10"/>
       <c r="K57" t="s" s="17">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="L57" t="s" s="17">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
@@ -26569,7 +26665,7 @@
     </row>
     <row r="58" ht="80.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="B58" t="s" s="9">
         <v>659</v>
@@ -26587,14 +26683,14 @@
       <c r="G58" s="10"/>
       <c r="H58" s="10"/>
       <c r="I58" t="s" s="17">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="J58" s="10"/>
       <c r="K58" t="s" s="17">
-        <v>927</v>
+        <v>937</v>
       </c>
       <c r="L58" t="s" s="17">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
@@ -26602,7 +26698,7 @@
     </row>
     <row r="59" ht="92.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="B59" t="s" s="9">
         <v>659</v>
@@ -26620,14 +26716,14 @@
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
       <c r="I59" t="s" s="17">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="J59" s="10"/>
       <c r="K59" t="s" s="17">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="L59" t="s" s="17">
-        <v>932</v>
+        <v>942</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
@@ -26635,7 +26731,7 @@
     </row>
     <row r="60" ht="80.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="B60" t="s" s="9">
         <v>659</v>
@@ -26653,14 +26749,14 @@
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
       <c r="I60" t="s" s="17">
-        <v>934</v>
+        <v>944</v>
       </c>
       <c r="J60" s="10"/>
       <c r="K60" t="s" s="17">
-        <v>935</v>
+        <v>945</v>
       </c>
       <c r="L60" t="s" s="17">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
@@ -26668,7 +26764,7 @@
     </row>
     <row r="61" ht="80.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>937</v>
+        <v>947</v>
       </c>
       <c r="B61" t="s" s="9">
         <v>659</v>
@@ -26690,10 +26786,10 @@
       </c>
       <c r="J61" s="10"/>
       <c r="K61" t="s" s="17">
-        <v>938</v>
+        <v>948</v>
       </c>
       <c r="L61" t="s" s="17">
-        <v>939</v>
+        <v>949</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
@@ -26701,7 +26797,7 @@
     </row>
     <row r="62" ht="80.05" customHeight="1">
       <c r="A62" t="s" s="8">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="B62" t="s" s="9">
         <v>659</v>
@@ -26719,14 +26815,14 @@
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
       <c r="I62" t="s" s="17">
-        <v>941</v>
+        <v>951</v>
       </c>
       <c r="J62" s="10"/>
       <c r="K62" t="s" s="17">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="L62" t="s" s="17">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10"/>
@@ -26734,7 +26830,7 @@
     </row>
     <row r="63" ht="80.05" customHeight="1">
       <c r="A63" t="s" s="8">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="B63" t="s" s="9">
         <v>659</v>
@@ -26756,10 +26852,10 @@
       </c>
       <c r="J63" s="10"/>
       <c r="K63" t="s" s="17">
-        <v>945</v>
+        <v>955</v>
       </c>
       <c r="L63" t="s" s="17">
-        <v>946</v>
+        <v>956</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10"/>
@@ -26767,7 +26863,7 @@
     </row>
     <row r="64" ht="80.05" customHeight="1">
       <c r="A64" t="s" s="8">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="B64" t="s" s="9">
         <v>659</v>
@@ -26785,14 +26881,14 @@
       <c r="G64" s="10"/>
       <c r="H64" s="10"/>
       <c r="I64" t="s" s="17">
-        <v>948</v>
+        <v>958</v>
       </c>
       <c r="J64" s="10"/>
       <c r="K64" t="s" s="17">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="L64" t="s" s="17">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10"/>
@@ -26800,7 +26896,7 @@
     </row>
     <row r="65" ht="80.05" customHeight="1">
       <c r="A65" t="s" s="8">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="B65" t="s" s="9">
         <v>659</v>
@@ -26818,14 +26914,14 @@
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" t="s" s="17">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="J65" s="10"/>
       <c r="K65" t="s" s="17">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="L65" t="s" s="17">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10"/>
@@ -26833,7 +26929,7 @@
     </row>
     <row r="66" ht="80.05" customHeight="1">
       <c r="A66" t="s" s="8">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="B66" t="s" s="9">
         <v>659</v>
@@ -26851,14 +26947,14 @@
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
       <c r="I66" t="s" s="17">
-        <v>955</v>
+        <v>965</v>
       </c>
       <c r="J66" s="10"/>
       <c r="K66" t="s" s="17">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="L66" t="s" s="17">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10"/>
@@ -26866,7 +26962,7 @@
     </row>
     <row r="67" ht="80.05" customHeight="1">
       <c r="A67" t="s" s="8">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B67" t="s" s="9">
         <v>659</v>
@@ -26884,14 +26980,14 @@
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
       <c r="I67" t="s" s="17">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="J67" s="10"/>
       <c r="K67" t="s" s="17">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="L67" t="s" s="17">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10"/>
@@ -26899,7 +26995,7 @@
     </row>
     <row r="68" ht="104.05" customHeight="1">
       <c r="A68" t="s" s="8">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="B68" t="s" s="9">
         <v>659</v>
@@ -26917,14 +27013,14 @@
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
       <c r="I68" t="s" s="17">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="J68" s="10"/>
       <c r="K68" t="s" s="17">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="L68" t="s" s="17">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10"/>
@@ -26932,7 +27028,7 @@
     </row>
     <row r="69" ht="80.05" customHeight="1">
       <c r="A69" t="s" s="8">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="B69" t="s" s="9">
         <v>659</v>
@@ -26954,10 +27050,10 @@
       </c>
       <c r="J69" s="10"/>
       <c r="K69" t="s" s="17">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="L69" t="s" s="17">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10"/>
@@ -26965,7 +27061,7 @@
     </row>
     <row r="70" ht="80.05" customHeight="1">
       <c r="A70" t="s" s="8">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="B70" t="s" s="9">
         <v>659</v>
@@ -26983,14 +27079,14 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" t="s" s="17">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="J70" s="10"/>
       <c r="K70" t="s" s="17">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="L70" t="s" s="17">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10"/>
@@ -26998,7 +27094,7 @@
     </row>
     <row r="71" ht="80.05" customHeight="1">
       <c r="A71" t="s" s="8">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="B71" t="s" s="9">
         <v>659</v>
@@ -27016,14 +27112,14 @@
       <c r="G71" s="10"/>
       <c r="H71" s="10"/>
       <c r="I71" t="s" s="17">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="J71" s="10"/>
       <c r="K71" t="s" s="17">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="L71" t="s" s="17">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10"/>
@@ -27031,7 +27127,7 @@
     </row>
     <row r="72" ht="80.05" customHeight="1">
       <c r="A72" t="s" s="8">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="B72" t="s" s="9">
         <v>659</v>
@@ -27053,14 +27149,18 @@
       <c r="I72" t="s" s="17">
         <v>39</v>
       </c>
-      <c r="J72" s="10"/>
+      <c r="J72" t="s" s="17">
+        <v>850</v>
+      </c>
       <c r="K72" t="s" s="17">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="L72" t="s" s="17">
-        <v>975</v>
-      </c>
-      <c r="M72" s="10"/>
+        <v>985</v>
+      </c>
+      <c r="M72" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N72" t="s" s="17">
         <v>35</v>
       </c>
@@ -27068,7 +27168,7 @@
     </row>
     <row r="73" ht="80.05" customHeight="1">
       <c r="A73" t="s" s="8">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="B73" t="s" s="9">
         <v>659</v>
@@ -27085,19 +27185,23 @@
       </c>
       <c r="G73" s="10"/>
       <c r="H73" t="s" s="17">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="I73" t="s" s="17">
-        <v>978</v>
-      </c>
-      <c r="J73" s="10"/>
+        <v>988</v>
+      </c>
+      <c r="J73" t="s" s="17">
+        <v>660</v>
+      </c>
       <c r="K73" t="s" s="17">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="L73" t="s" s="17">
-        <v>980</v>
-      </c>
-      <c r="M73" s="10"/>
+        <v>990</v>
+      </c>
+      <c r="M73" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N73" t="s" s="17">
         <v>35</v>
       </c>
@@ -27105,7 +27209,7 @@
     </row>
     <row r="74" ht="80.05" customHeight="1">
       <c r="A74" t="s" s="8">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="B74" t="s" s="9">
         <v>659</v>
@@ -27122,19 +27226,23 @@
       </c>
       <c r="G74" s="10"/>
       <c r="H74" t="s" s="17">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="I74" t="s" s="17">
-        <v>983</v>
-      </c>
-      <c r="J74" s="10"/>
+        <v>993</v>
+      </c>
+      <c r="J74" t="s" s="17">
+        <v>744</v>
+      </c>
       <c r="K74" t="s" s="17">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="L74" t="s" s="17">
-        <v>985</v>
-      </c>
-      <c r="M74" s="10"/>
+        <v>995</v>
+      </c>
+      <c r="M74" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N74" t="s" s="17">
         <v>35</v>
       </c>
@@ -27142,7 +27250,7 @@
     </row>
     <row r="75" ht="80.05" customHeight="1">
       <c r="A75" t="s" s="8">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="B75" t="s" s="9">
         <v>659</v>
@@ -27159,19 +27267,23 @@
       </c>
       <c r="G75" s="10"/>
       <c r="H75" t="s" s="17">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="I75" t="s" s="17">
-        <v>988</v>
-      </c>
-      <c r="J75" s="10"/>
+        <v>998</v>
+      </c>
+      <c r="J75" t="s" s="17">
+        <v>999</v>
+      </c>
       <c r="K75" t="s" s="17">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="L75" t="s" s="17">
-        <v>990</v>
-      </c>
-      <c r="M75" s="10"/>
+        <v>1001</v>
+      </c>
+      <c r="M75" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N75" t="s" s="17">
         <v>35</v>
       </c>
@@ -27179,7 +27291,7 @@
     </row>
     <row r="76" ht="80.05" customHeight="1">
       <c r="A76" t="s" s="8">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="B76" t="s" s="9">
         <v>659</v>
@@ -27196,19 +27308,23 @@
       </c>
       <c r="G76" s="10"/>
       <c r="H76" t="s" s="17">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="I76" t="s" s="17">
-        <v>993</v>
-      </c>
-      <c r="J76" s="10"/>
+        <v>1004</v>
+      </c>
+      <c r="J76" t="s" s="17">
+        <v>1005</v>
+      </c>
       <c r="K76" t="s" s="17">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="L76" t="s" s="17">
-        <v>995</v>
-      </c>
-      <c r="M76" s="10"/>
+        <v>1007</v>
+      </c>
+      <c r="M76" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N76" t="s" s="17">
         <v>35</v>
       </c>
@@ -27216,7 +27332,7 @@
     </row>
     <row r="77" ht="80.05" customHeight="1">
       <c r="A77" t="s" s="8">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="B77" t="s" s="9">
         <v>659</v>
@@ -27233,19 +27349,23 @@
       </c>
       <c r="G77" s="10"/>
       <c r="H77" t="s" s="17">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="I77" t="s" s="17">
-        <v>998</v>
-      </c>
-      <c r="J77" s="10"/>
+        <v>1010</v>
+      </c>
+      <c r="J77" t="s" s="17">
+        <v>999</v>
+      </c>
       <c r="K77" t="s" s="17">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="L77" t="s" s="17">
-        <v>1000</v>
-      </c>
-      <c r="M77" s="10"/>
+        <v>1012</v>
+      </c>
+      <c r="M77" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N77" t="s" s="17">
         <v>35</v>
       </c>
@@ -27253,7 +27373,7 @@
     </row>
     <row r="78" ht="80.05" customHeight="1">
       <c r="A78" t="s" s="8">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="B78" t="s" s="9">
         <v>659</v>
@@ -27275,14 +27395,18 @@
       <c r="I78" t="s" s="17">
         <v>39</v>
       </c>
-      <c r="J78" s="10"/>
+      <c r="J78" t="s" s="17">
+        <v>1005</v>
+      </c>
       <c r="K78" t="s" s="17">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="L78" t="s" s="17">
-        <v>1003</v>
-      </c>
-      <c r="M78" s="10"/>
+        <v>1015</v>
+      </c>
+      <c r="M78" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N78" t="s" s="17">
         <v>35</v>
       </c>
@@ -27290,7 +27414,7 @@
     </row>
     <row r="79" ht="80.05" customHeight="1">
       <c r="A79" t="s" s="8">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="B79" t="s" s="9">
         <v>659</v>
@@ -27307,19 +27431,23 @@
       </c>
       <c r="G79" s="10"/>
       <c r="H79" t="s" s="17">
+        <v>1017</v>
+      </c>
+      <c r="I79" t="s" s="17">
+        <v>1018</v>
+      </c>
+      <c r="J79" t="s" s="17">
         <v>1005</v>
       </c>
-      <c r="I79" t="s" s="17">
-        <v>1006</v>
-      </c>
-      <c r="J79" s="10"/>
       <c r="K79" t="s" s="17">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="L79" t="s" s="17">
-        <v>1008</v>
-      </c>
-      <c r="M79" s="10"/>
+        <v>1020</v>
+      </c>
+      <c r="M79" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N79" t="s" s="17">
         <v>35</v>
       </c>
@@ -27327,7 +27455,7 @@
     </row>
     <row r="80" ht="68.05" customHeight="1">
       <c r="A80" t="s" s="8">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="B80" t="s" s="9">
         <v>659</v>
@@ -27344,19 +27472,23 @@
       </c>
       <c r="G80" s="10"/>
       <c r="H80" t="s" s="17">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="I80" t="s" s="17">
-        <v>1011</v>
-      </c>
-      <c r="J80" s="10"/>
+        <v>1023</v>
+      </c>
+      <c r="J80" t="s" s="17">
+        <v>1024</v>
+      </c>
       <c r="K80" t="s" s="17">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="L80" t="s" s="17">
-        <v>1013</v>
-      </c>
-      <c r="M80" s="10"/>
+        <v>1026</v>
+      </c>
+      <c r="M80" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N80" t="s" s="17">
         <v>35</v>
       </c>
@@ -27364,7 +27496,7 @@
     </row>
     <row r="81" ht="80.05" customHeight="1">
       <c r="A81" t="s" s="8">
-        <v>1014</v>
+        <v>1027</v>
       </c>
       <c r="B81" t="s" s="9">
         <v>659</v>
@@ -27381,19 +27513,23 @@
       </c>
       <c r="G81" s="10"/>
       <c r="H81" t="s" s="17">
-        <v>1015</v>
+        <v>1028</v>
       </c>
       <c r="I81" t="s" s="17">
-        <v>1016</v>
-      </c>
-      <c r="J81" s="10"/>
+        <v>1029</v>
+      </c>
+      <c r="J81" t="s" s="17">
+        <v>1005</v>
+      </c>
       <c r="K81" t="s" s="17">
-        <v>1017</v>
+        <v>1030</v>
       </c>
       <c r="L81" t="s" s="17">
-        <v>1018</v>
-      </c>
-      <c r="M81" s="10"/>
+        <v>1031</v>
+      </c>
+      <c r="M81" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="N81" t="s" s="17">
         <v>35</v>
       </c>
@@ -27401,7 +27537,7 @@
     </row>
     <row r="82" ht="20.05" customHeight="1">
       <c r="A82" t="s" s="8">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="B82" s="12"/>
       <c r="C82" s="10"/>
@@ -27439,7 +27575,7 @@
     </row>
     <row r="84" ht="32.05" customHeight="1">
       <c r="A84" t="s" s="8">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="B84" s="12"/>
       <c r="C84" s="10"/>
@@ -27459,7 +27595,7 @@
       </c>
       <c r="J84" s="10"/>
       <c r="K84" t="s" s="17">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="L84" s="10"/>
       <c r="M84" s="10"/>
@@ -27468,7 +27604,7 @@
     </row>
     <row r="85" ht="44.05" customHeight="1">
       <c r="A85" t="s" s="8">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="B85" s="12"/>
       <c r="C85" s="10"/>
@@ -27482,7 +27618,7 @@
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
       <c r="K85" t="s" s="17">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="L85" s="10"/>
       <c r="M85" s="10"/>
@@ -27491,7 +27627,7 @@
     </row>
     <row r="86" ht="32.05" customHeight="1">
       <c r="A86" t="s" s="8">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="B86" s="12"/>
       <c r="C86" s="10"/>
@@ -27505,7 +27641,7 @@
       <c r="I86" s="10"/>
       <c r="J86" s="10"/>
       <c r="K86" t="s" s="17">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="L86" s="10"/>
       <c r="M86" s="10"/>
@@ -27514,7 +27650,7 @@
     </row>
     <row r="87" ht="20.05" customHeight="1">
       <c r="A87" t="s" s="8">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="B87" s="12"/>
       <c r="C87" s="10"/>
@@ -35563,23 +35699,23 @@
       </c>
       <c r="N2" t="s" s="3">
         <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N545,"Yes")</f>
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="O2" t="s" s="3">
         <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O545,"Yes")</f>
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="P2" t="s" s="3">
         <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P545,"Yes")</f>
-        <v>1029</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="3" ht="32.25" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C3" s="14">
         <v>0</v>
@@ -35591,7 +35727,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" t="s" s="15">
@@ -35610,10 +35746,10 @@
     </row>
     <row r="4" ht="44.05" customHeight="1">
       <c r="A4" t="s" s="8">
-        <v>1033</v>
+        <v>1046</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C4" s="16">
         <v>200</v>
@@ -35625,7 +35761,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="s" s="17">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" t="s" s="17">
@@ -35644,10 +35780,10 @@
     </row>
     <row r="5" ht="44.05" customHeight="1">
       <c r="A5" t="s" s="8">
-        <v>1035</v>
+        <v>1048</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -35659,7 +35795,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s" s="17">
-        <v>1036</v>
+        <v>1049</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" t="s" s="17">
@@ -35678,10 +35814,10 @@
     </row>
     <row r="6" ht="44.05" customHeight="1">
       <c r="A6" t="s" s="8">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -35693,7 +35829,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="s" s="17">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" t="s" s="17">
@@ -35712,10 +35848,10 @@
     </row>
     <row r="7" ht="32.05" customHeight="1">
       <c r="A7" t="s" s="8">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C7" s="16">
         <v>500</v>
@@ -35727,7 +35863,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s" s="17">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" t="s" s="17">
@@ -35746,10 +35882,10 @@
     </row>
     <row r="8" ht="44.05" customHeight="1">
       <c r="A8" t="s" s="8">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
@@ -35761,7 +35897,7 @@
         <v>5</v>
       </c>
       <c r="H8" t="s" s="17">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" t="s" s="17">
@@ -35780,10 +35916,10 @@
     </row>
     <row r="9" ht="32.05" customHeight="1">
       <c r="A9" t="s" s="8">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C9" s="16">
         <v>800</v>
@@ -35795,7 +35931,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="17">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" t="s" s="17">
@@ -35814,10 +35950,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="8">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C10" s="16">
         <v>250</v>
@@ -35829,7 +35965,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="17">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" t="s" s="17">
@@ -35848,10 +35984,10 @@
     </row>
     <row r="11" ht="32.05" customHeight="1">
       <c r="A11" t="s" s="8">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C11" s="16">
         <v>1000</v>
@@ -35863,7 +35999,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="17">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" t="s" s="17">
@@ -35882,10 +36018,10 @@
     </row>
     <row r="12" ht="44.05" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>1049</v>
+        <v>1062</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C12" s="16">
         <v>200</v>
@@ -35897,7 +36033,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="s" s="17">
-        <v>1050</v>
+        <v>1063</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" t="s" s="17">
@@ -35912,10 +36048,10 @@
     </row>
     <row r="13" ht="32.05" customHeight="1">
       <c r="A13" t="s" s="8">
-        <v>1051</v>
+        <v>1064</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C13" s="16">
         <v>500</v>
@@ -35927,7 +36063,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="s" s="17">
-        <v>1052</v>
+        <v>1065</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" t="s" s="17">
@@ -35946,10 +36082,10 @@
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" t="s" s="8">
-        <v>1053</v>
+        <v>1066</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C14" s="16">
         <v>1500</v>
@@ -35961,7 +36097,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="17">
-        <v>1054</v>
+        <v>1067</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" t="s" s="17">
@@ -35980,10 +36116,10 @@
     </row>
     <row r="15" ht="32.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C15" s="16">
         <v>500</v>
@@ -35995,7 +36131,7 @@
         <v>4</v>
       </c>
       <c r="H15" t="s" s="17">
-        <v>1056</v>
+        <v>1069</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" t="s" s="17">
@@ -36014,10 +36150,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C16" s="16">
         <v>1500</v>
@@ -36029,7 +36165,7 @@
         <v>5</v>
       </c>
       <c r="H16" t="s" s="17">
-        <v>1058</v>
+        <v>1071</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" t="s" s="17">
@@ -36048,10 +36184,10 @@
     </row>
     <row r="17" ht="44.05" customHeight="1">
       <c r="A17" t="s" s="8">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C17" s="16">
         <v>900</v>
@@ -36063,7 +36199,7 @@
         <v>4</v>
       </c>
       <c r="H17" t="s" s="17">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" t="s" s="17">
@@ -36082,10 +36218,10 @@
     </row>
     <row r="18" ht="44.05" customHeight="1">
       <c r="A18" t="s" s="8">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
@@ -36097,7 +36233,7 @@
         <v>3</v>
       </c>
       <c r="H18" t="s" s="17">
-        <v>1062</v>
+        <v>1075</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" t="s" s="17">
@@ -36116,10 +36252,10 @@
     </row>
     <row r="19" ht="44.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>1063</v>
+        <v>1076</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C19" s="16">
         <v>800</v>
@@ -36131,7 +36267,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="17">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" t="s" s="17">
@@ -36144,12 +36280,12 @@
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
     </row>
-    <row r="20" ht="56.05" customHeight="1">
+    <row r="20" ht="44.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>1065</v>
+        <v>1078</v>
       </c>
       <c r="B20" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C20" s="16">
         <v>600</v>
@@ -36161,7 +36297,7 @@
         <v>4</v>
       </c>
       <c r="H20" t="s" s="17">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" t="s" s="17">
@@ -36176,10 +36312,10 @@
     </row>
     <row r="21" ht="32.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>1067</v>
+        <v>1080</v>
       </c>
       <c r="B21" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C21" s="16">
         <v>0</v>
@@ -36191,7 +36327,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s" s="17">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" t="s" s="17">
@@ -36210,10 +36346,10 @@
     </row>
     <row r="22" ht="32.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="B22" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C22" s="16">
         <v>50</v>
@@ -36225,7 +36361,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s" s="17">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" t="s" s="17">
@@ -36240,10 +36376,10 @@
     </row>
     <row r="23" ht="32.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="B23" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C23" s="16">
         <v>100</v>
@@ -36255,7 +36391,7 @@
         <v>3</v>
       </c>
       <c r="H23" t="s" s="17">
-        <v>1072</v>
+        <v>1085</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" t="s" s="17">
@@ -36270,10 +36406,10 @@
     </row>
     <row r="24" ht="44.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>1073</v>
+        <v>1086</v>
       </c>
       <c r="B24" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C24" s="16">
         <v>1000</v>
@@ -36285,7 +36421,7 @@
         <v>5</v>
       </c>
       <c r="H24" t="s" s="17">
-        <v>1074</v>
+        <v>1087</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" t="s" s="17">
@@ -36300,10 +36436,10 @@
     </row>
     <row r="25" ht="44.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C25" s="16">
         <v>850</v>
@@ -36315,7 +36451,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s" s="17">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" t="s" s="17">
@@ -36328,12 +36464,12 @@
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
     </row>
-    <row r="26" ht="44.05" customHeight="1">
+    <row r="26" ht="32.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C26" s="16">
         <v>600</v>
@@ -36345,7 +36481,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s" s="17">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" t="s" s="17">
@@ -36360,10 +36496,10 @@
     </row>
     <row r="27" ht="44.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C27" s="16">
         <v>600</v>
@@ -36375,7 +36511,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="17">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" t="s" s="17">
@@ -36390,10 +36526,10 @@
     </row>
     <row r="28" ht="44.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>1081</v>
+        <v>1094</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C28" s="16">
         <v>600</v>
@@ -36405,7 +36541,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s" s="17">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" t="s" s="17">
@@ -36418,12 +36554,12 @@
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
     </row>
-    <row r="29" ht="44.05" customHeight="1">
+    <row r="29" ht="32.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C29" s="16">
         <v>600</v>
@@ -36435,7 +36571,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s" s="17">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" t="s" s="17">
@@ -36450,10 +36586,10 @@
     </row>
     <row r="30" ht="44.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C30" s="16">
         <v>600</v>
@@ -36465,7 +36601,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s" s="17">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" t="s" s="17">
@@ -36480,10 +36616,10 @@
     </row>
     <row r="31" ht="44.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C31" s="16">
         <v>600</v>
@@ -36495,7 +36631,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s" s="17">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" t="s" s="17">
@@ -36510,10 +36646,10 @@
     </row>
     <row r="32" ht="44.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>1089</v>
+        <v>1102</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C32" s="16">
         <v>600</v>
@@ -36525,7 +36661,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s" s="17">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" t="s" s="17">
@@ -36540,10 +36676,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C33" s="16">
         <v>300</v>
@@ -36555,7 +36691,7 @@
         <v>2</v>
       </c>
       <c r="H33" t="s" s="17">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" t="s" s="17">
@@ -36568,12 +36704,12 @@
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
     </row>
-    <row r="34" ht="56.05" customHeight="1">
+    <row r="34" ht="44.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C34" s="16">
         <v>800</v>
@@ -36585,7 +36721,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="17">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" t="s" s="17">
@@ -36600,10 +36736,10 @@
     </row>
     <row r="35" ht="56.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C35" s="16">
         <v>800</v>
@@ -36615,7 +36751,7 @@
         <v>3</v>
       </c>
       <c r="H35" t="s" s="17">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" t="s" s="17">
@@ -36630,10 +36766,10 @@
     </row>
     <row r="36" ht="44.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C36" s="16">
         <v>800</v>
@@ -36645,7 +36781,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="17">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" t="s" s="17">
@@ -36660,10 +36796,10 @@
     </row>
     <row r="37" ht="44.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="B37" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C37" s="16">
         <v>800</v>
@@ -36675,7 +36811,7 @@
         <v>3</v>
       </c>
       <c r="H37" t="s" s="17">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" t="s" s="17">
@@ -36690,10 +36826,10 @@
     </row>
     <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="B38" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C38" s="16">
         <v>800</v>
@@ -36705,7 +36841,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="17">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" t="s" s="17">
@@ -36720,10 +36856,10 @@
     </row>
     <row r="39" ht="56.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="B39" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C39" s="16">
         <v>800</v>
@@ -36735,7 +36871,7 @@
         <v>3</v>
       </c>
       <c r="H39" t="s" s="17">
-        <v>1104</v>
+        <v>1117</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" t="s" s="17">
@@ -36750,10 +36886,10 @@
     </row>
     <row r="40" ht="68.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="B40" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C40" s="16">
         <v>800</v>
@@ -36765,7 +36901,7 @@
         <v>3</v>
       </c>
       <c r="H40" t="s" s="17">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" t="s" s="17">
@@ -36778,12 +36914,12 @@
       <c r="O40" s="10"/>
       <c r="P40" s="10"/>
     </row>
-    <row r="41" ht="56.05" customHeight="1">
+    <row r="41" ht="44.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C41" s="16">
         <v>1200</v>
@@ -36795,7 +36931,7 @@
         <v>3</v>
       </c>
       <c r="H41" t="s" s="17">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" t="s" s="17">
@@ -36810,10 +36946,10 @@
     </row>
     <row r="42" ht="44.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C42" s="16">
         <v>1500</v>
@@ -36825,7 +36961,7 @@
         <v>4</v>
       </c>
       <c r="H42" t="s" s="17">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" t="s" s="17">
@@ -36838,15 +36974,15 @@
       <c r="O42" s="10"/>
       <c r="P42" s="10"/>
     </row>
-    <row r="43" ht="32.05" customHeight="1">
+    <row r="43" ht="44.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C43" s="16">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -36855,10 +36991,12 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="17">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
+      <c r="J43" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K43" s="10"/>
       <c r="L43" t="s" s="17">
         <v>35</v>
@@ -36872,10 +37010,10 @@
     </row>
     <row r="44" ht="32.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C44" s="16">
         <v>700</v>
@@ -36887,10 +37025,12 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="17">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
+      <c r="J44" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K44" s="10"/>
       <c r="L44" t="s" s="17">
         <v>35</v>
@@ -36902,12 +37042,12 @@
       </c>
       <c r="P44" s="10"/>
     </row>
-    <row r="45" ht="44.05" customHeight="1">
+    <row r="45" ht="32.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C45" s="16">
         <v>1200</v>
@@ -36919,7 +37059,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s" s="17">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -36930,12 +37070,12 @@
       <c r="O45" s="10"/>
       <c r="P45" s="10"/>
     </row>
-    <row r="46" ht="44.05" customHeight="1">
+    <row r="46" ht="32.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C46" s="16">
         <v>1500</v>
@@ -36947,7 +37087,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="17">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -36958,12 +37098,12 @@
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
     </row>
-    <row r="47" ht="44.05" customHeight="1">
+    <row r="47" ht="32.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C47" s="16">
         <v>950</v>
@@ -36975,7 +37115,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="17">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -36988,10 +37128,10 @@
     </row>
     <row r="48" ht="44.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C48" s="16">
         <v>0</v>
@@ -37003,7 +37143,7 @@
         <v>3</v>
       </c>
       <c r="H48" t="s" s="17">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -37016,10 +37156,10 @@
     </row>
     <row r="49" ht="68.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C49" s="16">
         <v>2000</v>
@@ -37031,7 +37171,7 @@
         <v>5</v>
       </c>
       <c r="H49" t="s" s="17">
-        <v>1124</v>
+        <v>1137</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
@@ -37044,10 +37184,10 @@
     </row>
     <row r="50" ht="56.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C50" s="16">
         <v>100</v>
@@ -37059,7 +37199,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="17">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
@@ -37072,7 +37212,7 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="16">
@@ -37085,7 +37225,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="17">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
@@ -37096,12 +37236,12 @@
       <c r="O51" s="10"/>
       <c r="P51" s="10"/>
     </row>
-    <row r="52" ht="44.05" customHeight="1">
+    <row r="52" ht="32.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C52" s="16">
         <v>0</v>
@@ -37113,10 +37253,12 @@
         <v>2</v>
       </c>
       <c r="H52" t="s" s="17">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
+      <c r="J52" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K52" s="10"/>
       <c r="L52" t="s" s="17">
         <v>35</v>
@@ -37130,7 +37272,7 @@
     </row>
     <row r="53" ht="32.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="16">
@@ -37143,7 +37285,7 @@
         <v>2</v>
       </c>
       <c r="H53" t="s" s="17">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
@@ -37156,7 +37298,7 @@
     </row>
     <row r="54" ht="32.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="16">
@@ -37169,7 +37311,7 @@
         <v>3</v>
       </c>
       <c r="H54" t="s" s="17">
-        <v>1134</v>
+        <v>1147</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
@@ -37182,10 +37324,10 @@
     </row>
     <row r="55" ht="32.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="B55" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C55" s="16">
         <v>0</v>
@@ -37197,10 +37339,12 @@
         <v>1</v>
       </c>
       <c r="H55" t="s" s="17">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
+      <c r="J55" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K55" s="10"/>
       <c r="L55" t="s" s="17">
         <v>35</v>
@@ -37214,10 +37358,10 @@
     </row>
     <row r="56" ht="44.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C56" s="16">
         <v>0</v>
@@ -37229,10 +37373,12 @@
         <v>1</v>
       </c>
       <c r="H56" t="s" s="17">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
+      <c r="J56" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K56" s="10"/>
       <c r="L56" t="s" s="17">
         <v>35</v>
@@ -37246,7 +37392,7 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="16">
@@ -37259,7 +37405,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="s" s="17">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
@@ -37270,12 +37416,12 @@
       <c r="O57" s="10"/>
       <c r="P57" s="10"/>
     </row>
-    <row r="58" ht="56.05" customHeight="1">
+    <row r="58" ht="44.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C58" s="16">
         <v>0</v>
@@ -37287,10 +37433,12 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="17">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
+      <c r="J58" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K58" s="10"/>
       <c r="L58" t="s" s="17">
         <v>35</v>
@@ -37304,7 +37452,7 @@
     </row>
     <row r="59" ht="44.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="16">
@@ -37317,7 +37465,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="17">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
@@ -37330,10 +37478,10 @@
     </row>
     <row r="60" ht="44.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="C60" s="16">
         <v>0</v>
@@ -37345,10 +37493,12 @@
         <v>1</v>
       </c>
       <c r="H60" t="s" s="17">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
+      <c r="J60" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K60" s="10"/>
       <c r="L60" t="s" s="17">
         <v>35</v>
@@ -37362,7 +37512,7 @@
     </row>
     <row r="61" ht="56.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="16">
@@ -37375,7 +37525,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="17">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -46176,7 +46326,7 @@
         <v>24</v>
       </c>
       <c r="J2" t="s" s="3">
-        <v>1149</v>
+        <v>1162</v>
       </c>
       <c r="K2" t="s" s="3">
         <v>26</v>
@@ -46189,23 +46339,23 @@
       </c>
       <c r="N2" t="s" s="3">
         <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N556,"Yes")</f>
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="O2" t="s" s="3">
         <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O556,"Yes")</f>
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="P2" t="s" s="3">
         <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P556,"Yes")</f>
-        <v>1152</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="3" ht="32.25" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C3" s="14">
         <v>0</v>
@@ -46217,7 +46367,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" t="s" s="15">
@@ -46234,10 +46384,10 @@
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" t="s" s="8">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C4" s="16">
         <v>0</v>
@@ -46249,7 +46399,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s" s="17">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" t="s" s="17">
@@ -46268,10 +46418,10 @@
     </row>
     <row r="5" ht="44.05" customHeight="1">
       <c r="A5" t="s" s="8">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -46283,7 +46433,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="s" s="17">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" t="s" s="17">
@@ -46298,10 +46448,10 @@
     </row>
     <row r="6" ht="80.05" customHeight="1">
       <c r="A6" t="s" s="8">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -46313,7 +46463,7 @@
         <v>5</v>
       </c>
       <c r="H6" t="s" s="17">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" t="s" s="17">
@@ -46328,10 +46478,10 @@
     </row>
     <row r="7" ht="56.05" customHeight="1">
       <c r="A7" t="s" s="8">
-        <v>1162</v>
+        <v>1175</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
@@ -46343,7 +46493,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s" s="17">
-        <v>1163</v>
+        <v>1176</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" t="s" s="17">
@@ -46358,10 +46508,10 @@
     </row>
     <row r="8" ht="56.05" customHeight="1">
       <c r="A8" t="s" s="8">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
@@ -46373,7 +46523,7 @@
         <v>3</v>
       </c>
       <c r="H8" t="s" s="17">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" t="s" s="17">
@@ -46388,10 +46538,10 @@
     </row>
     <row r="9" ht="56.05" customHeight="1">
       <c r="A9" t="s" s="8">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C9" s="16">
         <v>0</v>
@@ -46403,7 +46553,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="17">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" t="s" s="17">
@@ -46418,10 +46568,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="8">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C10" s="16">
         <v>0</v>
@@ -46433,7 +46583,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="17">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" t="s" s="17">
@@ -46452,10 +46602,10 @@
     </row>
     <row r="11" ht="44.05" customHeight="1">
       <c r="A11" t="s" s="8">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C11" s="16">
         <v>0</v>
@@ -46467,7 +46617,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="17">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" t="s" s="17">
@@ -46486,10 +46636,10 @@
     </row>
     <row r="12" ht="44.05" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C12" s="16">
         <v>0</v>
@@ -46501,7 +46651,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s" s="17">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" t="s" s="17">
@@ -46520,10 +46670,10 @@
     </row>
     <row r="13" ht="44.05" customHeight="1">
       <c r="A13" t="s" s="8">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C13" s="16">
         <v>0</v>
@@ -46535,7 +46685,7 @@
         <v>4</v>
       </c>
       <c r="H13" t="s" s="17">
-        <v>1175</v>
+        <v>1188</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" t="s" s="17">
@@ -46554,10 +46704,10 @@
     </row>
     <row r="14" ht="68.05" customHeight="1">
       <c r="A14" t="s" s="8">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C14" s="16">
         <v>3000</v>
@@ -46569,7 +46719,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="17">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" t="s" s="17">
@@ -46584,10 +46734,10 @@
     </row>
     <row r="15" ht="68.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C15" s="16">
         <v>2000</v>
@@ -46599,7 +46749,7 @@
         <v>3</v>
       </c>
       <c r="H15" t="s" s="17">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" t="s" s="17">
@@ -46614,10 +46764,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C16" s="16">
         <v>1000</v>
@@ -46629,7 +46779,7 @@
         <v>4</v>
       </c>
       <c r="H16" t="s" s="17">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" t="s" s="17">
@@ -46646,12 +46796,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" ht="44.05" customHeight="1">
+    <row r="17" ht="32.05" customHeight="1">
       <c r="A17" t="s" s="8">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C17" s="16">
         <v>1000</v>
@@ -46663,7 +46813,7 @@
         <v>3</v>
       </c>
       <c r="H17" t="s" s="17">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" t="s" s="17">
@@ -46682,10 +46832,10 @@
     </row>
     <row r="18" ht="56.05" customHeight="1">
       <c r="A18" t="s" s="8">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C18" s="16">
         <v>500</v>
@@ -46697,7 +46847,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="s" s="17">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" t="s" s="17">
@@ -46710,12 +46860,12 @@
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" ht="56.05" customHeight="1">
+    <row r="19" ht="32.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C19" s="16">
         <v>1000</v>
@@ -46727,7 +46877,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="17">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" t="s" s="17">
@@ -46742,10 +46892,10 @@
     </row>
     <row r="20" ht="56.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="B20" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C20" s="16">
         <v>600</v>
@@ -46757,7 +46907,7 @@
         <v>3</v>
       </c>
       <c r="H20" t="s" s="17">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" t="s" s="17">
@@ -46772,10 +46922,10 @@
     </row>
     <row r="21" ht="32.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>1190</v>
+        <v>1203</v>
       </c>
       <c r="B21" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C21" s="16">
         <v>1500</v>
@@ -46787,7 +46937,7 @@
         <v>4</v>
       </c>
       <c r="H21" t="s" s="17">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" t="s" s="17">
@@ -46800,12 +46950,12 @@
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" ht="56.05" customHeight="1">
+    <row r="22" ht="44.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="B22" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C22" s="16">
         <v>850</v>
@@ -46817,7 +46967,7 @@
         <v>3</v>
       </c>
       <c r="H22" t="s" s="17">
-        <v>1193</v>
+        <v>1206</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" t="s" s="17">
@@ -46832,10 +46982,10 @@
     </row>
     <row r="23" ht="44.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B23" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C23" s="16">
         <v>1000</v>
@@ -46847,7 +46997,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="s" s="17">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" t="s" s="17">
@@ -46866,10 +47016,10 @@
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="B24" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C24" s="16">
         <v>2000</v>
@@ -46881,7 +47031,7 @@
         <v>4</v>
       </c>
       <c r="H24" t="s" s="17">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" t="s" s="17">
@@ -46896,10 +47046,10 @@
     </row>
     <row r="25" ht="56.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C25" s="16">
         <v>1000</v>
@@ -46911,7 +47061,7 @@
         <v>3</v>
       </c>
       <c r="H25" t="s" s="17">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" t="s" s="17">
@@ -46928,12 +47078,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" ht="92.05" customHeight="1">
+    <row r="26" ht="80.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C26" s="16">
         <v>2000</v>
@@ -46945,7 +47095,7 @@
         <v>5</v>
       </c>
       <c r="H26" t="s" s="17">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" t="s" s="17">
@@ -46960,10 +47110,10 @@
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C27" s="16">
         <v>600</v>
@@ -46975,7 +47125,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="17">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" t="s" s="17">
@@ -46992,12 +47142,12 @@
       <c r="O27" s="10"/>
       <c r="P27" s="10"/>
     </row>
-    <row r="28" ht="56.05" customHeight="1">
+    <row r="28" ht="44.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C28" s="16">
         <v>500</v>
@@ -47009,7 +47159,7 @@
         <v>2</v>
       </c>
       <c r="H28" t="s" s="17">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" t="s" s="17">
@@ -47022,12 +47172,12 @@
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
     </row>
-    <row r="29" ht="92.05" customHeight="1">
+    <row r="29" ht="80.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C29" s="16">
         <v>700</v>
@@ -47039,7 +47189,7 @@
         <v>5</v>
       </c>
       <c r="H29" t="s" s="17">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" t="s" s="17">
@@ -47054,10 +47204,10 @@
     </row>
     <row r="30" ht="80.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C30" s="16">
         <v>1200</v>
@@ -47069,7 +47219,7 @@
         <v>4</v>
       </c>
       <c r="H30" t="s" s="17">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" t="s" s="17">
@@ -47084,10 +47234,10 @@
     </row>
     <row r="31" ht="68.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C31" s="16">
         <v>1000</v>
@@ -47099,7 +47249,7 @@
         <v>5</v>
       </c>
       <c r="H31" t="s" s="17">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" t="s" s="17">
@@ -47114,10 +47264,10 @@
     </row>
     <row r="32" ht="56.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C32" s="16">
         <v>1800</v>
@@ -47129,7 +47279,7 @@
         <v>5</v>
       </c>
       <c r="H32" t="s" s="17">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" t="s" s="17">
@@ -47144,10 +47294,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C33" s="16">
         <v>1500</v>
@@ -47159,7 +47309,7 @@
         <v>4</v>
       </c>
       <c r="H33" t="s" s="17">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" t="s" s="17">
@@ -47178,10 +47328,10 @@
     </row>
     <row r="34" ht="56.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C34" s="16">
         <v>1000</v>
@@ -47193,7 +47343,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="17">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
@@ -47206,10 +47356,10 @@
     </row>
     <row r="35" ht="44.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C35" s="16">
         <v>600</v>
@@ -47221,7 +47371,7 @@
         <v>2</v>
       </c>
       <c r="H35" t="s" s="17">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
@@ -47234,10 +47384,10 @@
     </row>
     <row r="36" ht="56.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C36" s="16">
         <v>250</v>
@@ -47249,7 +47399,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="17">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
@@ -47262,10 +47412,10 @@
     </row>
     <row r="37" ht="32.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="B37" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C37" s="16">
         <v>300</v>
@@ -47277,7 +47427,7 @@
         <v>2</v>
       </c>
       <c r="H37" t="s" s="17">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -47290,10 +47440,10 @@
     </row>
     <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="B38" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C38" s="16">
         <v>1000</v>
@@ -47305,7 +47455,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="17">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -47316,12 +47466,12 @@
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
     </row>
-    <row r="39" ht="44.05" customHeight="1">
+    <row r="39" ht="32.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="B39" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C39" s="16">
         <v>1200</v>
@@ -47333,7 +47483,7 @@
         <v>4</v>
       </c>
       <c r="H39" t="s" s="17">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -47346,10 +47496,10 @@
     </row>
     <row r="40" ht="20.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="B40" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C40" s="16">
         <v>0</v>
@@ -47361,7 +47511,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="s" s="17">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
@@ -47374,10 +47524,10 @@
     </row>
     <row r="41" ht="32.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C41" s="16">
         <v>0</v>
@@ -47389,7 +47539,7 @@
         <v>2</v>
       </c>
       <c r="H41" t="s" s="17">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
@@ -47402,10 +47552,10 @@
     </row>
     <row r="42" ht="32.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>1232</v>
+        <v>1245</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C42" s="16">
         <v>0</v>
@@ -47417,7 +47567,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s" s="17">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -47430,10 +47580,10 @@
     </row>
     <row r="43" ht="32.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C43" s="16">
         <v>0</v>
@@ -47445,7 +47595,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="17">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
@@ -47458,10 +47608,10 @@
     </row>
     <row r="44" ht="20.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C44" s="16">
         <v>0</v>
@@ -47473,7 +47623,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="17">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
@@ -47486,10 +47636,10 @@
     </row>
     <row r="45" ht="68.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C45" s="16">
         <v>0</v>
@@ -47501,7 +47651,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s" s="17">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -47514,10 +47664,10 @@
     </row>
     <row r="46" ht="44.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C46" s="16">
         <v>0</v>
@@ -47529,7 +47679,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="17">
-        <v>1241</v>
+        <v>1254</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -47542,10 +47692,10 @@
     </row>
     <row r="47" ht="44.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>1242</v>
+        <v>1255</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C47" s="16">
         <v>0</v>
@@ -47557,7 +47707,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="17">
-        <v>1243</v>
+        <v>1256</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -47570,10 +47720,10 @@
     </row>
     <row r="48" ht="56.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C48" s="16">
         <v>500</v>
@@ -47585,7 +47735,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="s" s="17">
-        <v>1245</v>
+        <v>1258</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -47598,10 +47748,10 @@
     </row>
     <row r="49" ht="32.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C49" s="16">
         <v>0</v>
@@ -47613,7 +47763,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s" s="17">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
@@ -47626,10 +47776,10 @@
     </row>
     <row r="50" ht="32.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C50" s="16">
         <v>600</v>
@@ -47641,7 +47791,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="17">
-        <v>1249</v>
+        <v>1262</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
@@ -47654,10 +47804,10 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="B51" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C51" s="16">
         <v>0</v>
@@ -47669,7 +47819,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="17">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
@@ -47682,10 +47832,10 @@
     </row>
     <row r="52" ht="68.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>1252</v>
+        <v>1265</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C52" s="16">
         <v>200</v>
@@ -47697,7 +47847,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s" s="17">
-        <v>1253</v>
+        <v>1266</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
@@ -47708,12 +47858,12 @@
       <c r="O52" s="10"/>
       <c r="P52" s="10"/>
     </row>
-    <row r="53" ht="80.05" customHeight="1">
+    <row r="53" ht="68.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="B53" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C53" s="16">
         <v>200</v>
@@ -47725,7 +47875,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="s" s="17">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
@@ -47738,10 +47888,10 @@
     </row>
     <row r="54" ht="80.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>1256</v>
+        <v>1269</v>
       </c>
       <c r="B54" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C54" s="16">
         <v>600</v>
@@ -47753,7 +47903,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s" s="17">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
@@ -47766,10 +47916,10 @@
     </row>
     <row r="55" ht="68.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B55" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C55" s="16">
         <v>500</v>
@@ -47781,7 +47931,7 @@
         <v>2</v>
       </c>
       <c r="H55" t="s" s="17">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
@@ -47794,10 +47944,10 @@
     </row>
     <row r="56" ht="44.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>1260</v>
+        <v>1273</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C56" s="16">
         <v>900</v>
@@ -47809,7 +47959,7 @@
         <v>2</v>
       </c>
       <c r="H56" t="s" s="17">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
@@ -47822,10 +47972,10 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="B57" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C57" s="16">
         <v>0</v>
@@ -47837,7 +47987,7 @@
         <v>2</v>
       </c>
       <c r="H57" t="s" s="17">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
@@ -47848,12 +47998,12 @@
       <c r="O57" s="10"/>
       <c r="P57" s="10"/>
     </row>
-    <row r="58" ht="68.05" customHeight="1">
+    <row r="58" ht="56.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>1264</v>
+        <v>1277</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C58" s="16">
         <v>450</v>
@@ -47865,7 +48015,7 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="17">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
@@ -47878,10 +48028,10 @@
     </row>
     <row r="59" ht="68.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="B59" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C59" s="16">
         <v>450</v>
@@ -47893,7 +48043,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="17">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
@@ -47906,10 +48056,10 @@
     </row>
     <row r="60" ht="56.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C60" s="16">
         <v>200</v>
@@ -47921,7 +48071,7 @@
         <v>4</v>
       </c>
       <c r="H60" t="s" s="17">
-        <v>1269</v>
+        <v>1282</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
@@ -47934,10 +48084,10 @@
     </row>
     <row r="61" ht="32.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>1270</v>
+        <v>1283</v>
       </c>
       <c r="B61" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C61" s="16">
         <v>1200</v>
@@ -47949,7 +48099,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="17">
-        <v>1271</v>
+        <v>1284</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -47962,10 +48112,10 @@
     </row>
     <row r="62" ht="44.05" customHeight="1">
       <c r="A62" t="s" s="8">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="B62" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C62" s="16">
         <v>0</v>
@@ -47977,7 +48127,7 @@
         <v>2</v>
       </c>
       <c r="H62" t="s" s="17">
-        <v>1273</v>
+        <v>1286</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
@@ -47990,10 +48140,10 @@
     </row>
     <row r="63" ht="44.05" customHeight="1">
       <c r="A63" t="s" s="8">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="B63" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C63" s="16">
         <v>0</v>
@@ -48005,7 +48155,7 @@
         <v>4</v>
       </c>
       <c r="H63" t="s" s="17">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
@@ -48018,10 +48168,10 @@
     </row>
     <row r="64" ht="32.05" customHeight="1">
       <c r="A64" t="s" s="8">
-        <v>1276</v>
+        <v>1289</v>
       </c>
       <c r="B64" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C64" s="16">
         <v>0</v>
@@ -48033,7 +48183,7 @@
         <v>4</v>
       </c>
       <c r="H64" t="s" s="17">
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
@@ -48046,10 +48196,10 @@
     </row>
     <row r="65" ht="92.05" customHeight="1">
       <c r="A65" t="s" s="8">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="B65" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C65" s="16">
         <v>800</v>
@@ -48061,7 +48211,7 @@
         <v>3</v>
       </c>
       <c r="H65" t="s" s="17">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
@@ -48074,10 +48224,10 @@
     </row>
     <row r="66" ht="80.05" customHeight="1">
       <c r="A66" t="s" s="8">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="B66" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C66" s="16">
         <v>800</v>
@@ -48089,7 +48239,7 @@
         <v>2</v>
       </c>
       <c r="H66" t="s" s="17">
-        <v>1281</v>
+        <v>1294</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
@@ -48102,10 +48252,10 @@
     </row>
     <row r="67" ht="68.05" customHeight="1">
       <c r="A67" t="s" s="8">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="B67" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C67" s="16">
         <v>1000</v>
@@ -48117,7 +48267,7 @@
         <v>5</v>
       </c>
       <c r="H67" t="s" s="17">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
@@ -48130,10 +48280,10 @@
     </row>
     <row r="68" ht="68.05" customHeight="1">
       <c r="A68" t="s" s="8">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="B68" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C68" s="16">
         <v>1500</v>
@@ -48145,7 +48295,7 @@
         <v>3</v>
       </c>
       <c r="H68" t="s" s="17">
-        <v>1285</v>
+        <v>1298</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
@@ -48158,10 +48308,10 @@
     </row>
     <row r="69" ht="56.05" customHeight="1">
       <c r="A69" t="s" s="8">
-        <v>1286</v>
+        <v>1299</v>
       </c>
       <c r="B69" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C69" s="16">
         <v>1200</v>
@@ -48173,7 +48323,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s" s="17">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
@@ -48186,10 +48336,10 @@
     </row>
     <row r="70" ht="56.05" customHeight="1">
       <c r="A70" t="s" s="8">
-        <v>1288</v>
+        <v>1301</v>
       </c>
       <c r="B70" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C70" s="16">
         <v>300</v>
@@ -48201,7 +48351,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="s" s="17">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
@@ -48214,10 +48364,10 @@
     </row>
     <row r="71" ht="68.05" customHeight="1">
       <c r="A71" t="s" s="8">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="B71" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C71" s="16">
         <v>300</v>
@@ -48229,7 +48379,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="s" s="17">
-        <v>1291</v>
+        <v>1304</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
@@ -48242,10 +48392,10 @@
     </row>
     <row r="72" ht="80.05" customHeight="1">
       <c r="A72" t="s" s="8">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="B72" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C72" s="16">
         <v>500</v>
@@ -48257,7 +48407,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s" s="17">
-        <v>1293</v>
+        <v>1306</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
@@ -48270,10 +48420,10 @@
     </row>
     <row r="73" ht="44.05" customHeight="1">
       <c r="A73" t="s" s="8">
-        <v>1294</v>
+        <v>1307</v>
       </c>
       <c r="B73" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C73" s="16">
         <v>2000</v>
@@ -48285,7 +48435,7 @@
         <v>4</v>
       </c>
       <c r="H73" t="s" s="17">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
@@ -48298,10 +48448,10 @@
     </row>
     <row r="74" ht="44.05" customHeight="1">
       <c r="A74" t="s" s="8">
-        <v>1296</v>
+        <v>1309</v>
       </c>
       <c r="B74" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C74" s="16">
         <v>2000</v>
@@ -48313,7 +48463,7 @@
         <v>5</v>
       </c>
       <c r="H74" t="s" s="17">
-        <v>1297</v>
+        <v>1310</v>
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
@@ -48326,10 +48476,10 @@
     </row>
     <row r="75" ht="44.05" customHeight="1">
       <c r="A75" t="s" s="8">
-        <v>1298</v>
+        <v>1311</v>
       </c>
       <c r="B75" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C75" s="16">
         <v>2000</v>
@@ -48341,7 +48491,7 @@
         <v>5</v>
       </c>
       <c r="H75" t="s" s="17">
-        <v>1299</v>
+        <v>1312</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
@@ -48354,10 +48504,10 @@
     </row>
     <row r="76" ht="44.05" customHeight="1">
       <c r="A76" t="s" s="8">
-        <v>1300</v>
+        <v>1313</v>
       </c>
       <c r="B76" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C76" s="16">
         <v>2000</v>
@@ -48369,7 +48519,7 @@
         <v>5</v>
       </c>
       <c r="H76" t="s" s="17">
-        <v>1301</v>
+        <v>1314</v>
       </c>
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
@@ -48382,10 +48532,10 @@
     </row>
     <row r="77" ht="44.05" customHeight="1">
       <c r="A77" t="s" s="8">
-        <v>1302</v>
+        <v>1315</v>
       </c>
       <c r="B77" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C77" s="16">
         <v>2000</v>
@@ -48397,7 +48547,7 @@
         <v>5</v>
       </c>
       <c r="H77" t="s" s="17">
-        <v>1303</v>
+        <v>1316</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
@@ -48410,10 +48560,10 @@
     </row>
     <row r="78" ht="44.05" customHeight="1">
       <c r="A78" t="s" s="8">
-        <v>1304</v>
+        <v>1317</v>
       </c>
       <c r="B78" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C78" s="16">
         <v>2000</v>
@@ -48425,7 +48575,7 @@
         <v>5</v>
       </c>
       <c r="H78" t="s" s="17">
-        <v>1305</v>
+        <v>1318</v>
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
@@ -48438,10 +48588,10 @@
     </row>
     <row r="79" ht="44.05" customHeight="1">
       <c r="A79" t="s" s="8">
-        <v>1306</v>
+        <v>1319</v>
       </c>
       <c r="B79" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C79" s="16">
         <v>2000</v>
@@ -48453,7 +48603,7 @@
         <v>5</v>
       </c>
       <c r="H79" t="s" s="17">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
@@ -48466,10 +48616,10 @@
     </row>
     <row r="80" ht="20.05" customHeight="1">
       <c r="A80" t="s" s="8">
-        <v>1308</v>
+        <v>1321</v>
       </c>
       <c r="B80" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C80" s="16">
         <v>1200</v>
@@ -48481,7 +48631,7 @@
         <v>4</v>
       </c>
       <c r="H80" t="s" s="17">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
@@ -48494,10 +48644,10 @@
     </row>
     <row r="81" ht="56.05" customHeight="1">
       <c r="A81" t="s" s="8">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="B81" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C81" s="16">
         <v>2000</v>
@@ -48509,7 +48659,7 @@
         <v>3</v>
       </c>
       <c r="H81" t="s" s="17">
-        <v>1311</v>
+        <v>1324</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
@@ -48522,10 +48672,10 @@
     </row>
     <row r="82" ht="44.05" customHeight="1">
       <c r="A82" t="s" s="8">
-        <v>1312</v>
+        <v>1325</v>
       </c>
       <c r="B82" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C82" s="16">
         <v>1000</v>
@@ -48537,7 +48687,7 @@
         <v>3</v>
       </c>
       <c r="H82" t="s" s="17">
-        <v>1313</v>
+        <v>1326</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
@@ -48550,10 +48700,10 @@
     </row>
     <row r="83" ht="44.05" customHeight="1">
       <c r="A83" t="s" s="8">
-        <v>1314</v>
+        <v>1327</v>
       </c>
       <c r="B83" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C83" s="16">
         <v>500</v>
@@ -48565,7 +48715,7 @@
         <v>2</v>
       </c>
       <c r="H83" t="s" s="17">
-        <v>1315</v>
+        <v>1328</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
@@ -48578,10 +48728,10 @@
     </row>
     <row r="84" ht="44.05" customHeight="1">
       <c r="A84" t="s" s="8">
-        <v>1316</v>
+        <v>1329</v>
       </c>
       <c r="B84" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C84" s="16">
         <v>250</v>
@@ -48593,7 +48743,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s" s="17">
-        <v>1317</v>
+        <v>1330</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
@@ -48606,10 +48756,10 @@
     </row>
     <row r="85" ht="80.05" customHeight="1">
       <c r="A85" t="s" s="8">
-        <v>1318</v>
+        <v>1331</v>
       </c>
       <c r="B85" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C85" s="16">
         <v>1500</v>
@@ -48621,7 +48771,7 @@
         <v>4</v>
       </c>
       <c r="H85" t="s" s="17">
-        <v>1319</v>
+        <v>1332</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
@@ -48634,10 +48784,10 @@
     </row>
     <row r="86" ht="32.05" customHeight="1">
       <c r="A86" t="s" s="8">
-        <v>1320</v>
+        <v>1333</v>
       </c>
       <c r="B86" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C86" s="16">
         <v>1000</v>
@@ -48649,7 +48799,7 @@
         <v>3</v>
       </c>
       <c r="H86" t="s" s="17">
-        <v>1321</v>
+        <v>1334</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="10"/>
@@ -48662,10 +48812,10 @@
     </row>
     <row r="87" ht="44.05" customHeight="1">
       <c r="A87" t="s" s="8">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="B87" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C87" s="16">
         <v>800</v>
@@ -48677,7 +48827,7 @@
         <v>2</v>
       </c>
       <c r="H87" t="s" s="17">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
@@ -48690,10 +48840,10 @@
     </row>
     <row r="88" ht="32.05" customHeight="1">
       <c r="A88" t="s" s="8">
-        <v>1324</v>
+        <v>1337</v>
       </c>
       <c r="B88" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C88" s="16">
         <v>200</v>
@@ -48705,7 +48855,7 @@
         <v>2</v>
       </c>
       <c r="H88" t="s" s="17">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
@@ -48718,10 +48868,10 @@
     </row>
     <row r="89" ht="32.05" customHeight="1">
       <c r="A89" t="s" s="8">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B89" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C89" s="16">
         <v>1500</v>
@@ -48733,7 +48883,7 @@
         <v>3</v>
       </c>
       <c r="H89" t="s" s="17">
-        <v>1327</v>
+        <v>1340</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="10"/>
@@ -48746,10 +48896,10 @@
     </row>
     <row r="90" ht="32.05" customHeight="1">
       <c r="A90" t="s" s="8">
-        <v>1328</v>
+        <v>1341</v>
       </c>
       <c r="B90" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C90" s="16">
         <v>500</v>
@@ -48761,7 +48911,7 @@
         <v>5</v>
       </c>
       <c r="H90" t="s" s="17">
-        <v>1329</v>
+        <v>1342</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
@@ -48774,10 +48924,10 @@
     </row>
     <row r="91" ht="80.05" customHeight="1">
       <c r="A91" t="s" s="8">
-        <v>1330</v>
+        <v>1343</v>
       </c>
       <c r="B91" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C91" s="16">
         <v>1000</v>
@@ -48789,11 +48939,11 @@
         <v>2</v>
       </c>
       <c r="H91" t="s" s="17">
-        <v>1331</v>
+        <v>1344</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" t="s" s="17">
-        <v>35</v>
+        <v>1345</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="10"/>
@@ -48804,10 +48954,10 @@
     </row>
     <row r="92" ht="56.05" customHeight="1">
       <c r="A92" t="s" s="8">
-        <v>1332</v>
+        <v>1346</v>
       </c>
       <c r="B92" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C92" s="16">
         <v>1500</v>
@@ -48819,7 +48969,7 @@
         <v>4</v>
       </c>
       <c r="H92" t="s" s="17">
-        <v>1333</v>
+        <v>1347</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
@@ -48832,10 +48982,10 @@
     </row>
     <row r="93" ht="56.05" customHeight="1">
       <c r="A93" t="s" s="8">
-        <v>1334</v>
+        <v>1348</v>
       </c>
       <c r="B93" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C93" s="16">
         <v>300</v>
@@ -48847,7 +48997,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s" s="17">
-        <v>1335</v>
+        <v>1349</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
@@ -48860,10 +49010,10 @@
     </row>
     <row r="94" ht="68.05" customHeight="1">
       <c r="A94" t="s" s="8">
-        <v>1336</v>
+        <v>1350</v>
       </c>
       <c r="B94" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C94" s="16">
         <v>200</v>
@@ -48875,7 +49025,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="s" s="17">
-        <v>1337</v>
+        <v>1351</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="10"/>
@@ -48888,10 +49038,10 @@
     </row>
     <row r="95" ht="68.05" customHeight="1">
       <c r="A95" t="s" s="8">
-        <v>1338</v>
+        <v>1352</v>
       </c>
       <c r="B95" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C95" s="16">
         <v>0</v>
@@ -48903,7 +49053,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="s" s="17">
-        <v>1339</v>
+        <v>1353</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
@@ -48916,10 +49066,10 @@
     </row>
     <row r="96" ht="44.05" customHeight="1">
       <c r="A96" t="s" s="8">
-        <v>1340</v>
+        <v>1354</v>
       </c>
       <c r="B96" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C96" s="16">
         <v>0</v>
@@ -48931,7 +49081,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="s" s="17">
-        <v>1341</v>
+        <v>1355</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10"/>
@@ -48944,10 +49094,10 @@
     </row>
     <row r="97" ht="56.05" customHeight="1">
       <c r="A97" t="s" s="8">
-        <v>1342</v>
+        <v>1356</v>
       </c>
       <c r="B97" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C97" s="16">
         <v>1000</v>
@@ -48959,7 +49109,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s" s="17">
-        <v>1343</v>
+        <v>1357</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
@@ -48972,10 +49122,10 @@
     </row>
     <row r="98" ht="32.05" customHeight="1">
       <c r="A98" t="s" s="8">
-        <v>1344</v>
+        <v>1358</v>
       </c>
       <c r="B98" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C98" s="16">
         <v>0</v>
@@ -48987,7 +49137,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="s" s="17">
-        <v>1345</v>
+        <v>1359</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="10"/>
@@ -49000,10 +49150,10 @@
     </row>
     <row r="99" ht="44.05" customHeight="1">
       <c r="A99" t="s" s="8">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="B99" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C99" s="16">
         <v>0</v>
@@ -49015,7 +49165,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="s" s="17">
-        <v>1347</v>
+        <v>1361</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
@@ -49028,10 +49178,10 @@
     </row>
     <row r="100" ht="44.05" customHeight="1">
       <c r="A100" t="s" s="8">
-        <v>1348</v>
+        <v>1362</v>
       </c>
       <c r="B100" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C100" s="16">
         <v>500</v>
@@ -49043,7 +49193,7 @@
         <v>2</v>
       </c>
       <c r="H100" t="s" s="17">
-        <v>1349</v>
+        <v>1363</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="10"/>
@@ -49056,10 +49206,10 @@
     </row>
     <row r="101" ht="44.05" customHeight="1">
       <c r="A101" t="s" s="8">
-        <v>1350</v>
+        <v>1364</v>
       </c>
       <c r="B101" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C101" s="16">
         <v>0</v>
@@ -49071,7 +49221,7 @@
         <v>2</v>
       </c>
       <c r="H101" t="s" s="17">
-        <v>1351</v>
+        <v>1365</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="10"/>
@@ -49084,10 +49234,10 @@
     </row>
     <row r="102" ht="44.05" customHeight="1">
       <c r="A102" t="s" s="8">
-        <v>1352</v>
+        <v>1366</v>
       </c>
       <c r="B102" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C102" s="16">
         <v>600</v>
@@ -49099,7 +49249,7 @@
         <v>2</v>
       </c>
       <c r="H102" t="s" s="17">
-        <v>1353</v>
+        <v>1367</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
@@ -49112,10 +49262,10 @@
     </row>
     <row r="103" ht="92.05" customHeight="1">
       <c r="A103" t="s" s="8">
-        <v>1354</v>
+        <v>1368</v>
       </c>
       <c r="B103" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C103" s="16">
         <v>500</v>
@@ -49127,7 +49277,7 @@
         <v>2</v>
       </c>
       <c r="H103" t="s" s="17">
-        <v>1355</v>
+        <v>1369</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="10"/>
@@ -49140,10 +49290,10 @@
     </row>
     <row r="104" ht="68.05" customHeight="1">
       <c r="A104" t="s" s="8">
-        <v>1356</v>
+        <v>1370</v>
       </c>
       <c r="B104" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C104" s="16">
         <v>2000</v>
@@ -49155,7 +49305,7 @@
         <v>4</v>
       </c>
       <c r="H104" t="s" s="17">
-        <v>1357</v>
+        <v>1371</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" t="s" s="17">
@@ -49170,10 +49320,10 @@
     </row>
     <row r="105" ht="32.05" customHeight="1">
       <c r="A105" t="s" s="8">
-        <v>1358</v>
+        <v>1372</v>
       </c>
       <c r="B105" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C105" s="16">
         <v>1500</v>
@@ -49185,7 +49335,7 @@
         <v>4</v>
       </c>
       <c r="H105" t="s" s="17">
-        <v>1359</v>
+        <v>1373</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
@@ -49198,10 +49348,10 @@
     </row>
     <row r="106" ht="32.05" customHeight="1">
       <c r="A106" t="s" s="8">
-        <v>1360</v>
+        <v>1374</v>
       </c>
       <c r="B106" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C106" s="16">
         <v>0</v>
@@ -49213,7 +49363,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s" s="17">
-        <v>1361</v>
+        <v>1375</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
@@ -49226,10 +49376,10 @@
     </row>
     <row r="107" ht="80.05" customHeight="1">
       <c r="A107" t="s" s="8">
-        <v>1362</v>
+        <v>1376</v>
       </c>
       <c r="B107" t="s" s="9">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="C107" s="16">
         <v>2000</v>
@@ -49241,7 +49391,7 @@
         <v>3</v>
       </c>
       <c r="H107" t="s" s="17">
-        <v>1363</v>
+        <v>1377</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="10"/>
@@ -49252,15 +49402,23 @@
       <c r="O107" s="10"/>
       <c r="P107" s="10"/>
     </row>
-    <row r="108" ht="20.05" customHeight="1">
-      <c r="A108" s="11"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="10"/>
+    <row r="108" ht="44.05" customHeight="1">
+      <c r="A108" t="s" s="8">
+        <v>1378</v>
+      </c>
+      <c r="B108" t="s" s="9">
+        <v>1167</v>
+      </c>
+      <c r="C108" s="16">
+        <v>300</v>
+      </c>
       <c r="D108" s="10"/>
       <c r="E108" s="10"/>
       <c r="F108" s="10"/>
       <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
+      <c r="H108" t="s" s="17">
+        <v>1379</v>
+      </c>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
       <c r="K108" s="10"/>
@@ -57373,21 +57531,21 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="22">
-        <v>1364</v>
+        <v>1380</v>
       </c>
       <c r="C2" t="s" s="22">
-        <v>1365</v>
+        <v>1381</v>
       </c>
       <c r="D2" t="s" s="22">
-        <v>1366</v>
+        <v>1382</v>
       </c>
       <c r="E2" t="s" s="22">
-        <v>1367</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="3" ht="16.55" customHeight="1">
       <c r="A3" t="s" s="23">
-        <v>1368</v>
+        <v>1384</v>
       </c>
       <c r="B3" s="24">
         <v>52</v>
@@ -57396,16 +57554,16 @@
         <v>0.347</v>
       </c>
       <c r="D3" t="s" s="26">
-        <v>1369</v>
+        <v>1385</v>
       </c>
       <c r="E3" s="27">
-        <f>_xlfn.COUNTIFS('Character'!$L$3:$L$568,"Yes",'Character'!$G$3:$G$568,1)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,1)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,1)</f>
+        <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,1)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,1)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,1)</f>
         <v>54</v>
       </c>
     </row>
     <row r="4" ht="16.35" customHeight="1">
       <c r="A4" t="s" s="28">
-        <v>1370</v>
+        <v>1386</v>
       </c>
       <c r="B4" s="29">
         <v>48</v>
@@ -57414,16 +57572,16 @@
         <v>0.337</v>
       </c>
       <c r="D4" t="s" s="31">
-        <v>1371</v>
+        <v>1387</v>
       </c>
       <c r="E4" s="32">
-        <f>_xlfn.COUNTIFS('Character'!$L$3:$L$568,"Yes",'Character'!$G$3:$G$568,2)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,2)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,2)</f>
+        <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,2)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,2)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,2)</f>
         <v>52</v>
       </c>
     </row>
     <row r="5" ht="16.35" customHeight="1">
       <c r="A5" t="s" s="28">
-        <v>1372</v>
+        <v>1388</v>
       </c>
       <c r="B5" s="29">
         <v>27</v>
@@ -57432,16 +57590,16 @@
         <v>0.167</v>
       </c>
       <c r="D5" t="s" s="31">
-        <v>1371</v>
+        <v>1387</v>
       </c>
       <c r="E5" s="32">
-        <f>_xlfn.COUNTIFS('Character'!$L$3:$L$568,"Yes",'Character'!$G$3:$G$568,3)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,3)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,3)</f>
+        <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,3)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,3)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,3)</f>
         <v>31</v>
       </c>
     </row>
     <row r="6" ht="30.35" customHeight="1">
       <c r="A6" t="s" s="28">
-        <v>1373</v>
+        <v>1389</v>
       </c>
       <c r="B6" s="29">
         <v>16</v>
@@ -57450,16 +57608,16 @@
         <v>0.1</v>
       </c>
       <c r="D6" t="s" s="31">
-        <v>1374</v>
+        <v>1390</v>
       </c>
       <c r="E6" s="32">
-        <f>_xlfn.COUNTIFS('Character'!$L$3:$L$568,"Yes",'Character'!$G$3:$G$568,4)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,4)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,4)</f>
+        <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,4)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,4)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,4)</f>
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="16.35" customHeight="1">
       <c r="A7" t="s" s="33">
-        <v>1375</v>
+        <v>1391</v>
       </c>
       <c r="B7" s="34">
         <v>9</v>
@@ -57468,10 +57626,10 @@
         <v>0.053</v>
       </c>
       <c r="D7" t="s" s="31">
-        <v>1376</v>
+        <v>1392</v>
       </c>
       <c r="E7" s="32">
-        <f>_xlfn.COUNTIFS('Character'!$L$3:$L$568,"Yes",'Character'!$G$3:$G$568,5)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,5)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,5)</f>
+        <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,5)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,5)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,5)</f>
         <v>12</v>
       </c>
     </row>
@@ -57501,17 +57659,17 @@
         <v>22</v>
       </c>
       <c r="B11" t="s" s="41">
-        <v>1364</v>
+        <v>1380</v>
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
       <c r="E11" t="s" s="43">
-        <v>1367</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="12" ht="16.35" customHeight="1">
       <c r="A12" t="s" s="28">
-        <v>1377</v>
+        <v>1393</v>
       </c>
       <c r="B12" s="29">
         <v>60</v>
@@ -57519,13 +57677,13 @@
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
       <c r="E12" s="32">
-        <f>_xlfn.COUNTIFS('Character'!$N$3:$N$568,"Yes")+_xlfn.COUNTIFS('Trap'!$N$3:$N$545,"Yes")+_xlfn.COUNTIFS('Tech'!$N$3:$N$556,"Yes")</f>
+        <f>_xlfn.COUNTIFS('Unit'!$N$3:$N$568,"Yes")+_xlfn.COUNTIFS('Trap'!$N$3:$N$545,"Yes")+_xlfn.COUNTIFS('Tech'!$N$3:$N$556,"Yes")</f>
         <v>60</v>
       </c>
     </row>
     <row r="13" ht="16.35" customHeight="1">
       <c r="A13" t="s" s="28">
-        <v>1378</v>
+        <v>1394</v>
       </c>
       <c r="B13" s="29">
         <v>60</v>
@@ -57533,13 +57691,13 @@
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="32">
-        <f>_xlfn.COUNTIFS('Character'!$O$3:$O$568,"Yes")+_xlfn.COUNTIFS('Trap'!$O$3:$O$545,"Yes")+_xlfn.COUNTIFS('Tech'!$O$3:$O$556,"Yes")</f>
+        <f>_xlfn.COUNTIFS('Unit'!$O$3:$O$568,"Yes")+_xlfn.COUNTIFS('Trap'!$O$3:$O$545,"Yes")+_xlfn.COUNTIFS('Tech'!$O$3:$O$556,"Yes")</f>
         <v>60</v>
       </c>
     </row>
     <row r="14" ht="16.35" customHeight="1">
       <c r="A14" t="s" s="28">
-        <v>1379</v>
+        <v>1395</v>
       </c>
       <c r="B14" s="29">
         <v>60</v>
@@ -57547,7 +57705,7 @@
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
       <c r="E14" s="32">
-        <f>_xlfn.COUNTIFS('Character'!$P$3:$P$568,"Yes")+_xlfn.COUNTIFS('Trap'!$P$3:$P$545,"Yes")+_xlfn.COUNTIFS('Tech'!$P$3:$P$556,"Yes")</f>
+        <f>_xlfn.COUNTIFS('Unit'!$P$3:$P$568,"Yes")+_xlfn.COUNTIFS('Trap'!$P$3:$P$545,"Yes")+_xlfn.COUNTIFS('Tech'!$P$3:$P$556,"Yes")</f>
         <v>60</v>
       </c>
     </row>
@@ -57587,10 +57745,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" t="s" s="3">
-        <v>1380</v>
+        <v>1396</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>1381</v>
+        <v>1397</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -57600,10 +57758,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1382</v>
+        <v>1398</v>
       </c>
       <c r="C3" t="s" s="15">
-        <v>1383</v>
+        <v>1399</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -57613,10 +57771,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1384</v>
+        <v>1400</v>
       </c>
       <c r="C4" t="s" s="17">
-        <v>1385</v>
+        <v>1401</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -57626,10 +57784,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>1386</v>
+        <v>1402</v>
       </c>
       <c r="C5" t="s" s="17">
-        <v>1387</v>
+        <v>1403</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -57639,10 +57797,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="C6" t="s" s="17">
-        <v>1389</v>
+        <v>1405</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -57652,10 +57810,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1390</v>
+        <v>1406</v>
       </c>
       <c r="C7" t="s" s="17">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -57665,10 +57823,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1392</v>
+        <v>1408</v>
       </c>
       <c r="C8" t="s" s="17">
-        <v>1393</v>
+        <v>1409</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -57678,10 +57836,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1394</v>
+        <v>1410</v>
       </c>
       <c r="C9" t="s" s="17">
-        <v>1395</v>
+        <v>1411</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>

--- a/context/card_data_demo.xlsx
+++ b/context/card_data_demo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1422">
   <si>
     <t>Table 1</t>
   </si>
@@ -109,7 +109,7 @@
     <t>Booster Pack - Blightsilver / 47</t>
   </si>
   <si>
-    <t>Booster Pack - Unseen Presence / 47</t>
+    <t>Booster Pack - Unseen Presence / 48</t>
   </si>
   <si>
     <t>Booster Pack - Wind of Dominance / 51</t>
@@ -433,7 +433,7 @@
     <t>Berserker of Ice Sea</t>
   </si>
   <si>
-    <t>If this card is exposed, increase its attack by 50</t>
+    <t>Once at foe’s next turn ends, +35 ATK</t>
   </si>
   <si>
     <t>Armored Elephant</t>
@@ -595,7 +595,7 @@
     <t>Halo Guardian</t>
   </si>
   <si>
-    <t>+5 ATK and DEF for each face-up Chaos card on opponent’s field</t>
+    <t>+5 ATK and DEF for each face-up Chaos card on foe’s field</t>
   </si>
   <si>
     <t>Benjamin the Holy Craftsman</t>
@@ -865,7 +865,7 @@
     <t>Hungry Imp</t>
   </si>
   <si>
-    <t>+5 ATK and DEF for each face-up Anima or Nature cards on opponent’s side of the field.</t>
+    <t>+5 ATK and DEF for each face-up Anima or Nature cards on foe’s side</t>
   </si>
   <si>
     <t>Dark Monk</t>
@@ -991,13 +991,13 @@
     <t>Sinister Cultist</t>
   </si>
   <si>
-    <t>Whenever your opponent lose crystal, they lose 100 more crystals</t>
+    <t>Whenever your foe lose crystal, they lose 100 more crystals</t>
   </si>
   <si>
     <t>Nanami the Long Neck</t>
   </si>
   <si>
-    <t>If this card is revealed, your opponent choose 1 tech card at show it to you</t>
+    <t>If this card is revealed, your foe choose 1 tech card at show it to you</t>
   </si>
   <si>
     <t>Flying Dutchman</t>
@@ -1021,7 +1021,7 @@
     <t>Blood Mage</t>
   </si>
   <si>
-    <t>When this card battles, you can pay 2000 to destroy the opponent attacker or defender without resolving damage calculation.</t>
+    <t>When this card battles, you can pay 2000 to destroy the foe attacker or defender without resolving damage calculation.</t>
   </si>
   <si>
     <t>Oni</t>
@@ -1036,13 +1036,13 @@
     <t>Bone Dragon</t>
   </si>
   <si>
-    <t>When it’s destroyed, at the end of opponent’s turn, flip a coin. If head, revive it.</t>
+    <t>When it’s destroyed, at the end of foe’s turn, flip a coin. If head, revive it.</t>
   </si>
   <si>
     <t>Eldritch Overlord</t>
   </si>
   <si>
-    <t>+10 ATK for each card in opponent’s void</t>
+    <t>+10 ATK for each card in foe’s void</t>
   </si>
   <si>
     <t>Azaxuna the Fallen</t>
@@ -1174,7 +1174,7 @@
     <t>Ostrich Cannon</t>
   </si>
   <si>
-    <t>This card cannot attack during your next turn.</t>
+    <t>After performed an attack, this card cannot attack during your next turn.</t>
   </si>
   <si>
     <t>Shotgun Shark</t>
@@ -1183,7 +1183,7 @@
     <t>Steel Eagle</t>
   </si>
   <si>
-    <t>After this card attacked (survived or not), reveal 1 of your opponent’s face-down cell</t>
+    <t>After this card attacked (survived or not), reveal 1 of your foe’s face-down cell</t>
   </si>
   <si>
     <t>Warfare Bear</t>
@@ -1198,7 +1198,7 @@
     <t>Shock Jellyfish</t>
   </si>
   <si>
-    <t>If this card defended, opponent’s turn ends immediately</t>
+    <t>If this card defended, foe’s turn ends immediately</t>
   </si>
   <si>
     <t>Tardigrade Warrior</t>
@@ -1216,7 +1216,7 @@
     <t>Smoke Owl</t>
   </si>
   <si>
-    <t>Opponent cannot select face-down card as an attack target</t>
+    <t>Foe cannot select face-down card as an attack target</t>
   </si>
   <si>
     <t>Death Cobra</t>
@@ -1228,7 +1228,7 @@
     <t>Blood Hound</t>
   </si>
   <si>
-    <t>When opponent attacks a Dead End, swap this card with it. Usable face-down.</t>
+    <t>When foe attacks a Dead End, swap this card with it. Usable face-down.</t>
   </si>
   <si>
     <t>Crab Ronin</t>
@@ -1240,13 +1240,13 @@
     <t>Dryad</t>
   </si>
   <si>
-    <t>While this is face-up, whenever you destroy opponent’s card, gain 300 crystals</t>
+    <t>While this is face-up, whenever you destroy foe’s card, gain 300 crystals</t>
   </si>
   <si>
     <t>Wending the Wise Princess</t>
   </si>
   <si>
-    <t>Once, when this card is revealed, choose either reveal 1 card on opponent’s field or put 1 princes flag on your face-up unit</t>
+    <t>Once, when this card is revealed, choose either reveal 1 card on foe’s field or put 1 princes flag on your face-up unit</t>
   </si>
   <si>
     <t>Fern the Mermaid Princess</t>
@@ -1321,7 +1321,7 @@
     <t>Dwarven Explorer</t>
   </si>
   <si>
-    <t>After this card battled, reveal 1 of your opponent’s cell</t>
+    <t>After this card battled, reveal 1 of your foe’s cell</t>
   </si>
   <si>
     <t>Gremlin Worker</t>
@@ -1351,7 +1351,7 @@
     <t>Alluring Spellcaster</t>
   </si>
   <si>
-    <t>Once, at the beginning of your opponent’s turn, flip a coin. If head, your opponent can only attack once.</t>
+    <t>Once, at the beginning of your foe’s turn, flip a coin. If head, your foe can only attack once.</t>
   </si>
   <si>
     <t>Mystic Dagger Dancer</t>
@@ -1393,13 +1393,13 @@
     <t>Dwarven Miner</t>
   </si>
   <si>
-    <t>After this card battled, flip a coin. If head, reveal 1 of your opponent’s cell, if tail, it lose 5 ATK</t>
+    <t>After this card battled, flip a coin. If head, reveal 1 of your foe’s cell, if tail, it lose 5 ATK</t>
   </si>
   <si>
     <t>Dwarven Bomber</t>
   </si>
   <si>
-    <t>After this card battled, flip a coin. If 3 coin, reveal your opponent’s cell up to number of head. If got 3 tail, destroy this card</t>
+    <t>After this card battled, flip a coin. If 3 coin, reveal your foe’s cell up to number of head. If got 3 tail, destroy this card</t>
   </si>
   <si>
     <t>Mad Spellcaster</t>
@@ -1498,7 +1498,7 @@
     <t>Ethereal Enchanter</t>
   </si>
   <si>
-    <t>Whenever you use tech, this card gain 50 ATK and DEF until the end of opponent’s turn</t>
+    <t>Whenever you use tech, this card gain 50 ATK and DEF until the end of foe’s turn</t>
   </si>
   <si>
     <t>Mind Elemental</t>
@@ -1543,7 +1543,7 @@
     <t>The Ancient One</t>
   </si>
   <si>
-    <t>Opponent cannot use Tech cards while this card is face-up.</t>
+    <t>Foe cannot use Tech cards while this card is face-up.</t>
   </si>
   <si>
     <t>Thunder Daddy</t>
@@ -1597,7 +1597,7 @@
     <t>Sweet Lure Pod</t>
   </si>
   <si>
-    <t>This turn, opponent can only target this card for an attack.</t>
+    <t>This turn, foe can only target this card for an attack.</t>
   </si>
   <si>
     <t>Radiaghoul</t>
@@ -1627,7 +1627,7 @@
     <t>Gluttonous Amoeba</t>
   </si>
   <si>
-    <t>If this card battles, opponent’s next attack must target a face-down card</t>
+    <t>If this card battles, foe’s next attack must target a face-down card</t>
   </si>
   <si>
     <t>Sticky Grappler</t>
@@ -1840,7 +1840,7 @@
     <t>Goliath the Wonder Seeker</t>
   </si>
   <si>
-    <t>At the end of your turn, if this card survived, reveal one random opponent cell.</t>
+    <t>At the end of your turn, if this card survived, reveal one random foe cell.</t>
   </si>
   <si>
     <t>Moon Tribe Demolisher</t>
@@ -1921,9 +1921,18 @@
     <t>Grand Fort Footsoldier</t>
   </si>
   <si>
+    <t>Swords Dancer</t>
+  </si>
+  <si>
+    <t>Mina the Chemist</t>
+  </si>
+  <si>
     <t>Firework Mania</t>
   </si>
   <si>
+    <t>Logan the Lumberjack</t>
+  </si>
+  <si>
     <t>Hairpin Assassin</t>
   </si>
   <si>
@@ -1942,7 +1951,7 @@
     <t>Ox Patrol</t>
   </si>
   <si>
-    <t>+5 ATK&amp;DEF vs Non-Anima</t>
+    <t>+10 ATK&amp;DEF vs Non-Anima</t>
   </si>
   <si>
     <t>Shepherd Detective</t>
@@ -1976,6 +1985,9 @@
   </si>
   <si>
     <t>If this card is used for Union summon, increase the Union card’s ATK and DEF by 40</t>
+  </si>
+  <si>
+    <t>Alchemist</t>
   </si>
   <si>
     <t>Partial Ability</t>
@@ -2040,17 +2052,17 @@
     <t>2 ??? + 2000 cost</t>
   </si>
   <si>
-    <t>2 any units (≥100 DEF) + 2000 cost</t>
+    <t>2 any units (≥90 DEF) + 2000 cost</t>
   </si>
   <si>
     <t>00000
-01010
+00000
 01110
 01110
 00000</t>
   </si>
   <si>
-    <t>Barros the Colossol</t>
+    <t>Barros the Colossal</t>
   </si>
   <si>
     <t>2 ???+ 1500 cost</t>
@@ -2078,7 +2090,7 @@
     <t>1 ??? + 2 ??? + 1500 cost</t>
   </si>
   <si>
-    <t>1 Bio with mutagen flag + 2 Bio + 1500 cost</t>
+    <t>1 Bio with mutagen flag + 2 Bio (≥ 800 cost) + 1500 cost</t>
   </si>
   <si>
     <t>00100
@@ -2198,7 +2210,7 @@
     <t>+??? ATK permanently at ???</t>
   </si>
   <si>
-    <t>+30 ATK permanently at the end of your turn</t>
+    <t>Once, +30 ATK permanently at the end of your turn</t>
   </si>
   <si>
     <t>1 Cleaver Saint + 1 Divine card + 1500 cost</t>
@@ -2233,7 +2245,7 @@
     <t>-50 ATK if attacks dead end card</t>
   </si>
   <si>
-    <t>1 Chaos (≥ 1000 cost) + 1 Chaos (≥ 800 cost) + 1000 cost</t>
+    <t>2 Chaos (≥ 800 cost) + 1500 cost</t>
   </si>
   <si>
     <t>00000
@@ -2259,7 +2271,7 @@
   </si>
   <si>
     <t>00000
-11111
+01110
 11111
 00000
 00000</t>
@@ -2280,7 +2292,7 @@
     <t>00100
 11111
 10001
-10001
+00000
 00000</t>
   </si>
   <si>
@@ -2415,7 +2427,7 @@
     <t>+20 ATK vs Chaos and Arcane</t>
   </si>
   <si>
-    <t>2 ???+ 2000 cost</t>
+    <t>2 ???+ 1000 cost</t>
   </si>
   <si>
     <t>2 Sphinx units + 1000 cost</t>
@@ -2513,7 +2525,7 @@
     <t>1??? + 1 ??? + 1000 cost</t>
   </si>
   <si>
-    <t>Lady of the Sacred Pond + 1 Anima + 1000 cost</t>
+    <t>Lady of the Sacred Pond + 1 Anima + 600 cost</t>
   </si>
   <si>
     <t>11011
@@ -2545,7 +2557,7 @@
     <t>+50 ATK and DEF for each Divine cards on the field. This bonus does not exceed maximum of 100</t>
   </si>
   <si>
-    <t>2 Divine (800 cost) + 1500 cost</t>
+    <t>2 Divine (≥800 cost) + 1500 cost</t>
   </si>
   <si>
     <t>00100
@@ -2571,7 +2583,7 @@
 01110
 01110
 00100
-00100</t>
+00000</t>
   </si>
   <si>
     <t>Kitsune</t>
@@ -2605,8 +2617,8 @@
     <t>11011
 00100
 00100
-11111
-10101</t>
+01110
+01010</t>
   </si>
   <si>
     <t>Skeleton Overlord</t>
@@ -2637,7 +2649,7 @@
     <t>4 ??? + 2000 cost</t>
   </si>
   <si>
-    <t>4 Chaos card (500 cost) + 2000 cost</t>
+    <t>4 Chaos card (≥500 cost) + 2000 cost</t>
   </si>
   <si>
     <t>10001
@@ -2663,13 +2675,13 @@
 00001</t>
   </si>
   <si>
-    <t>Ultimate Volcanic Dragon</t>
-  </si>
-  <si>
-    <t>Can attack if ???? on your field. Pay 1000 crystals to ????.</t>
-  </si>
-  <si>
-    <t>Can attack if this is the only face-up card on your field. Pay 1000 crystals to command this card to attack.</t>
+    <t>Mass Extinction Dragon</t>
+  </si>
+  <si>
+    <t>Upon union summoned, destroy all ???</t>
+  </si>
+  <si>
+    <t>Upon union summoned, destroy all other of your units. You do not pay cost.</t>
   </si>
   <si>
     <t>5 ??? + 3000 crystals</t>
@@ -2896,10 +2908,10 @@
     <t>Ice Hawk</t>
   </si>
   <si>
-    <t>Defender is ??? on next opponent’s turn.</t>
-  </si>
-  <si>
-    <t>Defender is unable to attack on next opponent’s turn.</t>
+    <t>Defender is ??? on next foe’s turn.</t>
+  </si>
+  <si>
+    <t>Defender is unable to attack on next foe’s turn.</t>
   </si>
   <si>
     <t>Drill Woodpecker + 1 Nature + 1000 cost</t>
@@ -2940,7 +2952,7 @@
     <t>At the end of this turn, reveal ???. You cannot use this effect if ???.</t>
   </si>
   <si>
-    <t>At the end of this turn, reveal 2 card on your opponent field. You cannot use this effect if you have already attacked this turn.</t>
+    <t>At the end of this turn, reveal 2 card on your foe field. You cannot use this effect if you have already attacked this turn.</t>
   </si>
   <si>
     <t>2 ??? + 1000 crystal.</t>
@@ -2965,9 +2977,6 @@
     <t>+30 ATK and DEF vs Nature</t>
   </si>
   <si>
-    <t>1 ??? + 1 ??? + 1000</t>
-  </si>
-  <si>
     <t>Cullan the Magic Swordsman + Red Mage + 1000 cost</t>
   </si>
   <si>
@@ -2981,7 +2990,7 @@
     <t>The Undertaker</t>
   </si>
   <si>
-    <t>Whenever an opponent destroys one of your cards, gain +15 ATK permanently (max +60).</t>
+    <t>Whenever an foe destroys one of your cards, gain +15 ATK permanently (max +60).</t>
   </si>
   <si>
     <t>Mad Doctor + 1 Chaos card + 1000 cost</t>
@@ -3010,6 +3019,13 @@
     <t>Red Mage + Green Mage + Blue Mage + 500 cost</t>
   </si>
   <si>
+    <t>00001
+00010
+01100
+01100
+10000</t>
+  </si>
+  <si>
     <t>Ethereal Marquees</t>
   </si>
   <si>
@@ -3032,7 +3048,7 @@
     <t>Charm Mistress</t>
   </si>
   <si>
-    <t>At the beginning of your opponent’s turn, flip a coin. If head, your opponent can only attack once.</t>
+    <t>At the beginning of your foe’s turn, flip a coin. If head, your foe can only attack once.</t>
   </si>
   <si>
     <t>Alluring Spellcaster + 1 Arcane + 1000 cost</t>
@@ -3128,7 +3144,7 @@
     <t>Thunder Elemental</t>
   </si>
   <si>
-    <t>After successful attack, reveal 1 of your opponent’s card</t>
+    <t>After successful attack, reveal 1 of your foe’s card</t>
   </si>
   <si>
     <t>Fire Elemental + Wind Elemental + 1000 cost</t>
@@ -3180,7 +3196,7 @@
     <t>Acid Elemental</t>
   </si>
   <si>
-    <t xml:space="preserve">When this card is union summoned, put acid flag on all of your opponent’s face-up card. At the end of opponent’s turn, card with acid flag -10 DEF </t>
+    <t xml:space="preserve">When this card is union summoned, put acid flag on all of your foe’s face-up card. At the end of foe’s turn, card with acid flag -10 DEF </t>
   </si>
   <si>
     <t>Mind Elemental + Water Elemental + 1500 cost</t>
@@ -3195,7 +3211,7 @@
     <t>Magnet Elemental</t>
   </si>
   <si>
-    <t>Your opponent’s non-Arcane cards cannot target face-up card other than this card.</t>
+    <t>Your foe’s non-Arcane cards cannot target face-up card other than this card.</t>
   </si>
   <si>
     <t>Mind Elemental + Earth Elemental + 1500 cost</t>
@@ -3235,10 +3251,10 @@
     <t>Volatile Slasher</t>
   </si>
   <si>
-    <t>After Reckoning with non-Bio, it gain ???.</t>
-  </si>
-  <si>
-    <t>After Reckoning with non-Bio, it gain +50 ATK permanently.</t>
+    <t>Once, after Reckoning with non-Bio, it gain ???.</t>
+  </si>
+  <si>
+    <t>Once, after Reckoning with non-Bio, it gain +50 ATK permanently.</t>
   </si>
   <si>
     <t>1 Bladeshifter + 1 Bio card + 1000 cost</t>
@@ -3318,7 +3334,7 @@
 </t>
   </si>
   <si>
-    <t>Moon Ninja Lady</t>
+    <t>Moon Lady Ninja</t>
   </si>
   <si>
     <t>Once, this card is ???.</t>
@@ -3344,9 +3360,9 @@
     <t>Laser Walker + 1 Cosmic card + 1000 cost</t>
   </si>
   <si>
-    <t xml:space="preserve">00000
-00111
-00011
+    <t xml:space="preserve">00111
+00001
+10001
 10000
 11100
 </t>
@@ -3453,7 +3469,7 @@
     <t>Trap</t>
   </si>
   <si>
-    <t>Attacking player loses 20 Crystals</t>
+    <t>Flip 3 coin, attacking player loses 20 Crystals per each head(s).</t>
   </si>
   <si>
     <t>Hostage</t>
@@ -3562,13 +3578,13 @@
     <t>Acid Trap Hole</t>
   </si>
   <si>
-    <t>Attacking player loses 50 Crystals</t>
+    <t>Flip 2 coin, attacking player loses 50 Crystals per each head(s).</t>
   </si>
   <si>
     <t>Lava Trap Hole</t>
   </si>
   <si>
-    <t>Attacking player loses 100 Crystals</t>
+    <t>Flip 3 coin, attacking player loses 100 Crystals per each head(s).</t>
   </si>
   <si>
     <t>Fissure</t>
@@ -3646,7 +3662,7 @@
     <t>Loop Hole</t>
   </si>
   <si>
-    <t>If attacking unit Is Arcane, the next attack of your opponent on a dead endcard will end the their turn</t>
+    <t>If attacking unit Is Arcane, the next attack of your foe on a dead endcard will end the their turn</t>
   </si>
   <si>
     <t>Talisman of Light</t>
@@ -3676,7 +3692,7 @@
     <t>Galaxy Toll</t>
   </si>
   <si>
-    <t>If attacking unit Is Cosmic, your opponent choose either pay 800 crystal cost. Or it cannot attack for the rest of their next turn</t>
+    <t>If attacking unit Is Cosmic, your foe choose either pay 800 crystal cost. Or it cannot attack for the rest of their next turn</t>
   </si>
   <si>
     <t>Union Cage</t>
@@ -3688,7 +3704,7 @@
     <t>Plunder</t>
   </si>
   <si>
-    <t>Your opponent choose to let you receive 2000 crystals, or destroy the attacking monster.</t>
+    <t>Your foe choose to let you receive 2000 crystals, or destroy the attacking monster.</t>
   </si>
   <si>
     <t>Decoy Puppet</t>
@@ -3724,19 +3740,19 @@
     <t>Lightning Rod</t>
   </si>
   <si>
-    <t>Opponent lose 1000 crystals if they target this card with any tech card</t>
+    <t>Foe lose 1000 crystals if they target this card with any tech card</t>
   </si>
   <si>
     <t>Dreamcatcher</t>
   </si>
   <si>
-    <t>You can use this trap when your opponent use a tech card. That tech card effect is cancelled. Your opponent can attack for 1 additional time.</t>
+    <t>You can use this trap when your foe use a tech card. That tech card effect is cancelled. Your foe can attack for 1 additional time.</t>
   </si>
   <si>
     <t>Stumble</t>
   </si>
   <si>
-    <t>Your opponent end turn immediately. They get 1 additional attack on their next turn.</t>
+    <t>Your foe end turn immediately. They get 1 additional attack on their next turn.</t>
   </si>
   <si>
     <t>Attention Catcher</t>
@@ -3772,7 +3788,7 @@
     <t>Alarm</t>
   </si>
   <si>
-    <t>Unil the end of this urn, All face-up Anima monster gain +5 DEF</t>
+    <t>Unil the end of this urn, All face-up Anima monster gain +10 DEF</t>
   </si>
   <si>
     <t>Protective Instinct</t>
@@ -3796,13 +3812,13 @@
     <t>Pepper Spray</t>
   </si>
   <si>
-    <t>Flip 2 coin, if head, the attacking unit lose -5 ATK until the end of their next turn.</t>
+    <t>Flip 2 coin, if head, the attacking unit lose -5 ATK for each head(s) until the end of their next turn.</t>
   </si>
   <si>
     <t>Curse of Pain</t>
   </si>
   <si>
-    <t>If you have 1500 or less crystal, drain crystal from opponent until both players have same amount of crystals</t>
+    <t>If you have 1500 or less crystal, drain crystal from foe until both players have same amount of crystals</t>
   </si>
   <si>
     <t>Illustration</t>
@@ -3811,7 +3827,7 @@
     <t>Booster Pack - Blightsilver / 4</t>
   </si>
   <si>
-    <t>Booster Pack - Unseen Presence / 4</t>
+    <t>Booster Pack - Unseen Presence / 3</t>
   </si>
   <si>
     <t>Booster Pack - Wind of Dominance / 4</t>
@@ -3835,31 +3851,31 @@
     <t>Ceasefire</t>
   </si>
   <si>
-    <t>Both you and your opponent skip 1 turn (tax is forced to apply)</t>
+    <t>Both you and your foe skip 1 turn (tax is forced to apply)</t>
   </si>
   <si>
     <t>Make Friend</t>
   </si>
   <si>
-    <t>Both you and your opponent select 1 monster from own's field (can reveal face-down card for this effect). Those monster cannot attack until the end of your next turn.</t>
+    <t>Both you and your foe select 1 monster from own's field (can reveal face-down card for this effect). Those monster cannot attack until the end of your next turn.</t>
   </si>
   <si>
     <t>Double Spy</t>
   </si>
   <si>
-    <t>This card only trigger if you have Spy card in your void. Reveal 2 square on opponent's side of the field.</t>
+    <t>This card only trigger if you have Spy card in your void. Reveal 2 square on foe's side of the field.</t>
   </si>
   <si>
     <t>Invisible Spy</t>
   </si>
   <si>
-    <t>This card only trigger if you have Double Spy card in your void. Reveal 2 square on opponent's side of the field.</t>
+    <t>This card only trigger if you have Double Spy card in your void. Reveal 2 square on foe's side of the field.</t>
   </si>
   <si>
     <t>Corrupted Spy</t>
   </si>
   <si>
-    <t>Reveal 3 square on opponent's side of the field. If you found any trap or Unit, you pay 700 Crystal or each card found.</t>
+    <t>Reveal 3 square on foe's side of the field. If you found any trap or Unit, you pay 700 Crystal or each card found.</t>
   </si>
   <si>
     <t>Tease</t>
@@ -3889,19 +3905,19 @@
     <t>Arcane Nova</t>
   </si>
   <si>
-    <t>Destroy 5 face-up opponent Units. You opponent do not lose crystals under this effect. Discard all of your Tech afterward.</t>
+    <t>Destroy 5 face-up foe Units. You foe do not lose crystals under this effect. Discard all of your Tech afterward.</t>
   </si>
   <si>
     <t>Rift Strike</t>
   </si>
   <si>
-    <t>Select 1 face-up opponent’s card. Destroy other face-up cards on that same rows as the selected cell. Your opponent don’t pay crystal cost.</t>
+    <t>Select 1 face-up foe’s card. Destroy other face-up units on that same rows. Your foe don’t pay cost.</t>
   </si>
   <si>
     <t>Great Diplomacy</t>
   </si>
   <si>
-    <t>Turn all units on your field face up</t>
+    <t>Select up to 5 of your units and reveal them.</t>
   </si>
   <si>
     <t>War Supply</t>
@@ -3973,7 +3989,7 @@
     <t>Palace Party</t>
   </si>
   <si>
-    <t>Reveal 1 of your face-down unit. Your opponent must reveal 1 of their face-down unit (if any)</t>
+    <t>Reveal 1 of your face-down unit. Your foe must reveal 1 of their face-down unit (if any)</t>
   </si>
   <si>
     <t>Essence Transfer</t>
@@ -3985,7 +4001,7 @@
     <t>Blood Ritual</t>
   </si>
   <si>
-    <t>Destroy 1 face-up card on the your field. You don't pay Crystal cost for the destroyed card. Choose 1 of your opponent's face-up unit. Its ATK and DEF becomes 0 permanently</t>
+    <t>Destroy 1 face-up card on the your field. You don't pay Crystal cost for the destroyed card. Choose 1 of your foe's face-up unit. Its ATK and DEF becomes 0 permanently</t>
   </si>
   <si>
     <t>Arcane Duplication</t>
@@ -4009,19 +4025,19 @@
     <t>Tech Copy</t>
   </si>
   <si>
-    <t>Your opponent show 1 tech card in their hand. Add a copy of that card into your Tech Stack.</t>
+    <t>Your foe show 1 tech card in their hand. Add a copy of that card into your Tech Stack.</t>
   </si>
   <si>
     <t>Force Shield</t>
   </si>
   <si>
-    <t>Select 1 card on your field. It is not destroyed until the end of your opponent's turn</t>
+    <t>Select 1 card on your field. It is not destroyed until the end of your foe's turn</t>
   </si>
   <si>
     <t>Wisp Light</t>
   </si>
   <si>
-    <t>Destroy as many wisp on your side of the field  as you can. Reveal that much square on opponent's field.</t>
+    <t>Destroy as many wisp on your side of the field  as you can. Reveal that much square on foe's field.</t>
   </si>
   <si>
     <t>Lucky Day</t>
@@ -4069,13 +4085,13 @@
     <t>Gift</t>
   </si>
   <si>
-    <t>Opponent receive 50 crystals</t>
+    <t>Foe receive 50 crystals</t>
   </si>
   <si>
     <t>Hired Spanker</t>
   </si>
   <si>
-    <t xml:space="preserve">Until the end of your opponent's turn, if your opponent attack the bluffed cell, your opponent receive 1000 crystals. </t>
+    <t xml:space="preserve">Until the end of your foe's turn, if your foe attack the bluffed cell, your foe receive 1000 crystals. </t>
   </si>
   <si>
     <t>Tax Avoidance</t>
@@ -4093,7 +4109,7 @@
     <t>Phony Fight</t>
   </si>
   <si>
-    <t>-10 DEF to 1 face-up unit on the field until the end of this turn. Your opponent receive 500 crystals</t>
+    <t>-10 DEF to 1 face-up unit on the field until the end of this turn. Your foe receive 500 crystals</t>
   </si>
   <si>
     <t>Facetious</t>
@@ -4123,7 +4139,7 @@
     <t>Flimsy Shield</t>
   </si>
   <si>
-    <t>Flip a coin. If head, +5 DEF to one of your unit until the end of your opponent’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>Flip a coin. If head, +5 DEF to one of your unit until the end of your foe’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>All-out Tactics</t>
@@ -4135,7 +4151,7 @@
     <t>Fair Fight</t>
   </si>
   <si>
-    <t>You and your opponent select 1 your their unit. +10 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>You and your foe select 1 your their unit. +10 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Greater Telepathy</t>
@@ -4159,13 +4175,13 @@
     <t>Old Shield</t>
   </si>
   <si>
-    <t>+5 DEF to one of your unit until the end of your opponent’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+5 DEF to one of your unit until the end of your foe’s turn. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Provoke</t>
   </si>
   <si>
-    <t xml:space="preserve">Until the end of your opponent's turn, your opponent must attack the selected cell first. </t>
+    <t xml:space="preserve">Until the end of your foe's turn, your foe must attack the selected cell first. </t>
   </si>
   <si>
     <t>Supreme Telepathy</t>
@@ -4183,19 +4199,19 @@
     <t>Big Finger</t>
   </si>
   <si>
-    <t>Send a very big improper emoticon bubble to your opponent</t>
+    <t>Send a very big improper emoticon bubble to your foe</t>
   </si>
   <si>
     <t>Big Love</t>
   </si>
   <si>
-    <t>Send a very big lovely emoticon bubble to your opponent</t>
+    <t>Send a very big lovely emoticon bubble to your foe</t>
   </si>
   <si>
     <t>Pretify</t>
   </si>
   <si>
-    <t>+20 DEF to one of your or your opponent’s face-up unit permanently, but its ATK becomes 0 permanently. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+20 DEF to one of your or your foe’s face-up unit permanently, but its ATK becomes 0 permanently. If used on your face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Stone Skin</t>
@@ -4207,19 +4223,19 @@
     <t>Battle Royale</t>
   </si>
   <si>
-    <t>You and your opponent select 1 your their unit. +30 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
+    <t>You and your foe select 1 your their unit. +30 ATK and DEF to it. If used on face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Guerrilla Tactics</t>
   </si>
   <si>
-    <t>Until the end of your opponent's turn. Whenever your opponent attack your dead end card, flip a coin. If head, destroy it.</t>
+    <t>Until the end of your foe's turn. Whenever your foe attack your dead end card, flip a coin. If head, destroy it.</t>
   </si>
   <si>
     <t>Toll</t>
   </si>
   <si>
-    <t>Until the end of your opponent's turn. Your opponent have to pay 100 crystal tax to perform an attack.</t>
+    <t>Until the end of your foe's turn. Your foe have to pay 100 crystal tax to perform an attack.</t>
   </si>
   <si>
     <t>Skull Amulet</t>
@@ -4237,49 +4253,49 @@
     <t>Arcane Knowledge</t>
   </si>
   <si>
-    <t>+5 ATK and DEF to 1 of your Arcane card until the end of your opponent’s turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+    <t>+5 ATK and DEF to 1 of your Arcane card until the end of your foe’s turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Forest Fire</t>
   </si>
   <si>
-    <t>Destroy all Nature cards on your opponent’s field. Discard all of your Tech cards.</t>
+    <t>Destroy all Nature cards on your foe’s field. Discard all of your Tech cards.</t>
   </si>
   <si>
     <t>Black Hole</t>
   </si>
   <si>
-    <t>Destroy all Cosmo cards on your opponent’s field. Discard all of your Tech cards.</t>
+    <t>Destroy all Cosmo cards on your foe’s field. Discard all of your Tech cards.</t>
   </si>
   <si>
     <t>Holy Arrival</t>
   </si>
   <si>
-    <t>Destroy all Chaos cards on your opponent’s field. Discard all of your Tech cards.</t>
+    <t>Destroy all Chaos cards on your foe’s field. Discard all of your Tech cards.</t>
   </si>
   <si>
     <t>Corrupted Heaven</t>
   </si>
   <si>
-    <t>Destroy all Divine cards on your opponent’s field. Discard all of your Tech cards.</t>
+    <t>Destroy all Divine cards on your foe’s field. Discard all of your Tech cards.</t>
   </si>
   <si>
     <t>Earthquake</t>
   </si>
   <si>
-    <t>Destroy all Anima cards on your opponent’s field. Discard all of your Tech cards.</t>
+    <t>Destroy all Anima cards on your foe’s field. Discard all of your Tech cards.</t>
   </si>
   <si>
     <t>Lab Self-destruction</t>
   </si>
   <si>
-    <t>Destroy all Bio cards on your opponent’s field. Discard all of your Tech cards.</t>
+    <t>Destroy all Bio cards on your foe’s field. Discard all of your Tech cards.</t>
   </si>
   <si>
     <t>Anti-magic Field</t>
   </si>
   <si>
-    <t>Destroy all Arcane cards on your opponent’s field. Discard all of your Tech cards.</t>
+    <t>Destroy all Arcane cards on your foe’s field. Discard all of your Tech cards.</t>
   </si>
   <si>
     <t>Air Shower</t>
@@ -4291,43 +4307,43 @@
     <t>Mining Tax</t>
   </si>
   <si>
-    <t>Until the end of your opponent’s turn, if any player attacks a dead end card, that player loses 200 crystals</t>
+    <t>Until the end of your foe’s turn, if any player attacks a dead end card, that player loses 200 crystals</t>
   </si>
   <si>
     <t>Ouija</t>
   </si>
   <si>
-    <t>Reveal cell on opponent's side of the field up to number of your unit in the void.</t>
+    <t>Reveal cell on foe's side of the field up to number of your unit in the void.</t>
   </si>
   <si>
     <t>Deep Mine</t>
   </si>
   <si>
-    <t>Flip a coin. If head, reveal 2 square on opponent's side of the field</t>
+    <t>Flip a coin. If head, reveal 2 square on foe's side of the field</t>
   </si>
   <si>
     <t>Gold Panning</t>
   </si>
   <si>
-    <t>Flip a coin. If head, reveal 1 square on opponent's side of the field</t>
+    <t>Flip a coin. If head, reveal 1 square on foe's side of the field</t>
   </si>
   <si>
     <t>Flashlight</t>
   </si>
   <si>
-    <t>Reveal 1 row or column on your opponent side of the field. You cannot attack the turn you use this card. You cannot use this card if you’ve already attacked this turn.</t>
+    <t>Reveal 1 row or column on your foe side of the field. You cannot attack the turn you use this card. You cannot use this card if you’ve already attacked this turn.</t>
   </si>
   <si>
     <t>Lantern</t>
   </si>
   <si>
-    <t>Reveal 2 adjacent cells on opponent's side of the field.</t>
+    <t>Reveal 2 adjacent cells on foe's side of the field.</t>
   </si>
   <si>
     <t>GPS Tracker</t>
   </si>
   <si>
-    <t>Reveal 2 adjacent cells next to face-up unit on opponent's side of the field.</t>
+    <t>Reveal 2 adjacent cells next to face-up unit on foe's side of the field.</t>
   </si>
   <si>
     <t>Blessing</t>
@@ -4360,13 +4376,13 @@
     <t>Full open fire</t>
   </si>
   <si>
-    <t>This turn, you can attack 2 additional times. Next turn, your opponent can also attack 2 additional times</t>
+    <t>This turn, you can attack 2 additional times. Next turn, your foe can also attack 2 additional times</t>
   </si>
   <si>
     <t>Service Charge</t>
   </si>
   <si>
-    <t>Until the end of your opponent's turn. Your opponent have to pay 50 crystal tax to perform an attack.</t>
+    <t>Until the end of your foe's turn. Your foe have to pay 50 crystal tax to perform an attack.</t>
   </si>
   <si>
     <t>Lazy Scout</t>
@@ -4384,13 +4400,13 @@
     <t>Trash Penalty</t>
   </si>
   <si>
-    <t>Your opponent choose either clearing all of their bluffs or take 500 damage</t>
+    <t>Your foe choose either clearing all of their bluffs or take 500 damage</t>
   </si>
   <si>
     <t>Silence Zone</t>
   </si>
   <si>
-    <t>Clear all bluffs from both you and your opponent. No one can use bluff ever again during this duel.</t>
+    <t>Clear all bluffs from both you and your foe. No one can use bluff ever again during this duel.</t>
   </si>
   <si>
     <t>Big Mouth</t>
@@ -4402,13 +4418,13 @@
     <t>Bare Fist Fight</t>
   </si>
   <si>
-    <t>Both you and your opponent select and discard 1 tech card from their hand.</t>
+    <t>Both you and your foe select and discard 1 tech card from their hand.</t>
   </si>
   <si>
     <t>Mine Detector</t>
   </si>
   <si>
-    <t>Reveal 1 card on your opponent’s field. If it’s a trap, destroy it and gain 200 crystals</t>
+    <t>Reveal 1 card on your foe’s field. If it’s a trap, destroy it and gain 200 crystals</t>
   </si>
   <si>
     <t>Natural Healing</t>
@@ -4426,31 +4442,31 @@
     <t>Punching Bag</t>
   </si>
   <si>
-    <t>One of your unit ATK and DEF becomes 0 permanently. It cannot be destroyed until the end of opponent’s turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
+    <t>One of your unit ATK and DEF becomes 0 permanently. It cannot be destroyed until the end of foe’s turn. If used on your face-down card, you can turn it face-up and apply this effect.</t>
   </si>
   <si>
     <t>Scattered Shot</t>
   </si>
   <si>
-    <t>Flip 3 coins. Destroy opponent’s face-up unit equal to number of heads. You opponent do not lose crystals under this effect</t>
+    <t>Flip 3 coins. Destroy foe’s face-up unit equal to number of heads. You foe do not lose crystals under this effect</t>
   </si>
   <si>
     <t>Spotlight</t>
   </si>
   <si>
-    <t>Flip 5 coins. Reveal opponent’s cell equal to number of heads</t>
+    <t>Flip 5 coins. Reveal foe’s cell equal to number of heads</t>
   </si>
   <si>
     <t>Tight Door</t>
   </si>
   <si>
-    <t>Next turn, your opponent can attack only once</t>
+    <t>Next turn, your foe can attack only once</t>
   </si>
   <si>
     <t>Katana Strike</t>
   </si>
   <si>
-    <t>Select 1 face-up opponent’s card. Destroy other face-up cards on that same columns as the selected cell. Your opponent don’t pay crystal cost.</t>
+    <t>Select 1 face-up foe’s card. Destroy other face-up cards on that same columns as the selected cell. Your foe don’t pay crystal cost.</t>
   </si>
   <si>
     <t>Mining Season</t>
@@ -4459,6 +4475,24 @@
     <t>Until foe’s turn ends, both player can only target face-down card</t>
   </si>
   <si>
+    <t>Throne Duel</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both player can only attack with unit with 800 or more cost. Cannot use if already attacked.</t>
+  </si>
+  <si>
+    <t>Joint Maneuver</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both player can only attack with unit with 600 or less cost. Cannot use if already attacked.</t>
+  </si>
+  <si>
+    <t>Pillow Fight</t>
+  </si>
+  <si>
+    <t>Until foe’s turn ends, both player can only attack with unit with 300 or less cost. Cannot use if already attacked.</t>
+  </si>
+  <si>
     <t>Expected</t>
   </si>
   <si>
@@ -4513,7 +4547,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Opponent</t>
+    <t>Foe</t>
   </si>
   <si>
     <t>foe</t>
@@ -8313,9 +8347,7 @@
         <f>(D53*6)+(E53*4)</f>
         <v>220</v>
       </c>
-      <c r="L53" t="s" s="17">
-        <v>35</v>
-      </c>
+      <c r="L53" s="10"/>
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
       <c r="O53" s="10"/>
@@ -9911,7 +9943,7 @@
       </c>
       <c r="P93" s="10"/>
     </row>
-    <row r="94" ht="44.05" customHeight="1">
+    <row r="94" ht="32.05" customHeight="1">
       <c r="A94" t="s" s="8">
         <v>191</v>
       </c>
@@ -12438,7 +12470,9 @@
       </c>
       <c r="M157" s="10"/>
       <c r="N157" s="10"/>
-      <c r="O157" s="10"/>
+      <c r="O157" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="P157" s="10"/>
     </row>
     <row r="158" ht="56.05" customHeight="1">
@@ -12979,7 +13013,7 @@
       <c r="O171" s="10"/>
       <c r="P171" s="10"/>
     </row>
-    <row r="172" ht="44.05" customHeight="1">
+    <row r="172" ht="32.05" customHeight="1">
       <c r="A172" t="s" s="8">
         <v>323</v>
       </c>
@@ -13164,7 +13198,7 @@
       <c r="O176" s="10"/>
       <c r="P176" s="10"/>
     </row>
-    <row r="177" ht="68.05" customHeight="1">
+    <row r="177" ht="56.05" customHeight="1">
       <c r="A177" t="s" s="8">
         <v>333</v>
       </c>
@@ -14360,7 +14394,7 @@
       </c>
       <c r="P206" s="10"/>
     </row>
-    <row r="207" ht="32.05" customHeight="1">
+    <row r="207" ht="44.05" customHeight="1">
       <c r="A207" t="s" s="8">
         <v>384</v>
       </c>
@@ -14557,7 +14591,7 @@
       <c r="O211" s="10"/>
       <c r="P211" s="10"/>
     </row>
-    <row r="212" ht="44.05" customHeight="1">
+    <row r="212" ht="32.05" customHeight="1">
       <c r="A212" t="s" s="8">
         <v>392</v>
       </c>
@@ -15677,7 +15711,7 @@
       <c r="O241" s="10"/>
       <c r="P241" s="10"/>
     </row>
-    <row r="242" ht="56.05" customHeight="1">
+    <row r="242" ht="44.05" customHeight="1">
       <c r="A242" t="s" s="8">
         <v>443</v>
       </c>
@@ -15990,7 +16024,7 @@
       <c r="O250" s="10"/>
       <c r="P250" s="10"/>
     </row>
-    <row r="251" ht="56.05" customHeight="1">
+    <row r="251" ht="44.05" customHeight="1">
       <c r="A251" t="s" s="8">
         <v>457</v>
       </c>
@@ -16027,7 +16061,7 @@
       <c r="O251" s="10"/>
       <c r="P251" s="10"/>
     </row>
-    <row r="252" ht="68.05" customHeight="1">
+    <row r="252" ht="56.05" customHeight="1">
       <c r="A252" t="s" s="8">
         <v>459</v>
       </c>
@@ -20167,7 +20201,9 @@
       </c>
     </row>
     <row r="373" ht="20.05" customHeight="1">
-      <c r="A373" s="11"/>
+      <c r="A373" t="s" s="8">
+        <v>634</v>
+      </c>
       <c r="B373" t="s" s="9">
         <v>33</v>
       </c>
@@ -20194,7 +20230,9 @@
       <c r="P373" s="10"/>
     </row>
     <row r="374" ht="20.05" customHeight="1">
-      <c r="A374" s="11"/>
+      <c r="A374" t="s" s="8">
+        <v>635</v>
+      </c>
       <c r="B374" t="s" s="9">
         <v>33</v>
       </c>
@@ -20465,7 +20503,7 @@
     </row>
     <row r="384" ht="20.05" customHeight="1">
       <c r="A384" t="s" s="8">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B384" t="s" s="9">
         <v>33</v>
@@ -20500,8 +20538,10 @@
       <c r="O384" s="10"/>
       <c r="P384" s="10"/>
     </row>
-    <row r="385" ht="20.05" customHeight="1">
-      <c r="A385" s="11"/>
+    <row r="385" ht="32.05" customHeight="1">
+      <c r="A385" t="s" s="8">
+        <v>637</v>
+      </c>
       <c r="B385" t="s" s="9">
         <v>33</v>
       </c>
@@ -20610,7 +20650,7 @@
     </row>
     <row r="389" ht="32.05" customHeight="1">
       <c r="A389" t="s" s="8">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B389" t="s" s="9">
         <v>33</v>
@@ -20631,7 +20671,7 @@
         <v>1</v>
       </c>
       <c r="H389" t="s" s="17">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="I389" s="10"/>
       <c r="J389" t="s" s="17">
@@ -20707,7 +20747,7 @@
     </row>
     <row r="392" ht="20.05" customHeight="1">
       <c r="A392" t="s" s="8">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B392" t="s" s="9">
         <v>33</v>
@@ -20728,7 +20768,7 @@
         <v>2</v>
       </c>
       <c r="H392" t="s" s="17">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="I392" s="10"/>
       <c r="J392" t="s" s="17">
@@ -20750,7 +20790,7 @@
     </row>
     <row r="393" ht="20.05" customHeight="1">
       <c r="A393" t="s" s="8">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B393" t="s" s="9">
         <v>33</v>
@@ -20793,7 +20833,7 @@
     </row>
     <row r="394" ht="20.05" customHeight="1">
       <c r="A394" t="s" s="8">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B394" t="s" s="9">
         <v>33</v>
@@ -20802,7 +20842,7 @@
         <v>420</v>
       </c>
       <c r="D394" s="16">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E394" s="16">
         <v>35</v>
@@ -20814,7 +20854,7 @@
         <v>2</v>
       </c>
       <c r="H394" t="s" s="17">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="I394" s="10"/>
       <c r="J394" t="s" s="17">
@@ -20822,7 +20862,7 @@
       </c>
       <c r="K394" s="16">
         <f>(D394*6)+(E394*4)</f>
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="L394" t="s" s="17">
         <v>35</v>
@@ -20836,7 +20876,7 @@
     </row>
     <row r="395" ht="32.05" customHeight="1">
       <c r="A395" t="s" s="8">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B395" t="s" s="9">
         <v>33</v>
@@ -20857,7 +20897,7 @@
         <v>2</v>
       </c>
       <c r="H395" t="s" s="17">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="I395" s="10"/>
       <c r="J395" t="s" s="17">
@@ -20879,7 +20919,7 @@
     </row>
     <row r="396" ht="20.05" customHeight="1">
       <c r="A396" t="s" s="8">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B396" t="s" s="9">
         <v>33</v>
@@ -20900,7 +20940,7 @@
         <v>2</v>
       </c>
       <c r="H396" t="s" s="17">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="I396" s="10"/>
       <c r="J396" t="s" s="17">
@@ -20922,7 +20962,7 @@
     </row>
     <row r="397" ht="20.05" customHeight="1">
       <c r="A397" t="s" s="8">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B397" t="s" s="9">
         <v>33</v>
@@ -20943,7 +20983,7 @@
         <v>2</v>
       </c>
       <c r="H397" t="s" s="17">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="I397" s="10"/>
       <c r="J397" t="s" s="17">
@@ -20965,7 +21005,7 @@
     </row>
     <row r="398" ht="44.05" customHeight="1">
       <c r="A398" t="s" s="8">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B398" t="s" s="9">
         <v>33</v>
@@ -20986,7 +21026,7 @@
         <v>2</v>
       </c>
       <c r="H398" t="s" s="17">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="I398" s="10"/>
       <c r="J398" t="s" s="17">
@@ -21089,7 +21129,7 @@
     </row>
     <row r="402" ht="32.05" customHeight="1">
       <c r="A402" t="s" s="8">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B402" t="s" s="9">
         <v>33</v>
@@ -21666,7 +21706,7 @@
     </row>
     <row r="423" ht="44.05" customHeight="1">
       <c r="A423" t="s" s="8">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B423" t="s" s="9">
         <v>33</v>
@@ -21681,7 +21721,7 @@
         <v>4</v>
       </c>
       <c r="H423" t="s" s="17">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="I423" s="10"/>
       <c r="J423" s="10"/>
@@ -21858,7 +21898,9 @@
       <c r="P429" s="10"/>
     </row>
     <row r="430" ht="20.05" customHeight="1">
-      <c r="A430" s="11"/>
+      <c r="A430" t="s" s="8">
+        <v>656</v>
+      </c>
       <c r="B430" t="s" s="9">
         <v>33</v>
       </c>
@@ -24450,7 +24492,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:O554"/>
+  <dimension ref="A2:O552"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.9375" style="18" customWidth="1"/>
@@ -24506,19 +24548,19 @@
         <v>22</v>
       </c>
       <c r="H2" t="s" s="3">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="I2" t="s" s="3">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="J2" t="s" s="3">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="K2" t="s" s="3">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L2" t="s" s="3">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="M2" t="s" s="3">
         <v>25</v>
@@ -24532,10 +24574,10 @@
     </row>
     <row r="3" ht="68.25" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="14">
@@ -24555,13 +24597,13 @@
         <v>39</v>
       </c>
       <c r="J3" t="s" s="15">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K3" t="s" s="15">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="L3" t="s" s="15">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="M3" t="s" s="15">
         <v>35</v>
@@ -24573,10 +24615,10 @@
     </row>
     <row r="4" ht="68.05" customHeight="1">
       <c r="A4" t="s" s="8">
+        <v>667</v>
+      </c>
+      <c r="B4" t="s" s="9">
         <v>663</v>
-      </c>
-      <c r="B4" t="s" s="9">
-        <v>659</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="16">
@@ -24590,19 +24632,19 @@
       </c>
       <c r="G4" s="10"/>
       <c r="H4" t="s" s="17">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="I4" t="s" s="17">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="J4" t="s" s="17">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K4" t="s" s="17">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="L4" t="s" s="17">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="M4" t="s" s="17">
         <v>35</v>
@@ -24614,17 +24656,17 @@
     </row>
     <row r="5" ht="68.05" customHeight="1">
       <c r="A5" t="s" s="8">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="16">
         <v>0</v>
       </c>
       <c r="E5" s="16">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="F5" t="s" s="17">
         <v>9</v>
@@ -24637,13 +24679,13 @@
         <v>39</v>
       </c>
       <c r="J5" t="s" s="17">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="K5" t="s" s="17">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="L5" t="s" s="17">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="M5" t="s" s="17">
         <v>35</v>
@@ -24655,10 +24697,10 @@
     </row>
     <row r="6" ht="68.05" customHeight="1">
       <c r="A6" t="s" s="8">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="16">
@@ -24678,13 +24720,13 @@
         <v>39</v>
       </c>
       <c r="J6" t="s" s="17">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="K6" t="s" s="17">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="L6" t="s" s="17">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="M6" t="s" s="17">
         <v>35</v>
@@ -24696,10 +24738,10 @@
     </row>
     <row r="7" ht="68.05" customHeight="1">
       <c r="A7" t="s" s="8">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="16">
@@ -24713,19 +24755,19 @@
       </c>
       <c r="G7" s="10"/>
       <c r="H7" t="s" s="17">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="I7" t="s" s="17">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J7" t="s" s="17">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K7" t="s" s="17">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="L7" t="s" s="17">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
@@ -24733,10 +24775,10 @@
     </row>
     <row r="8" ht="68.05" customHeight="1">
       <c r="A8" t="s" s="8">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="16">
@@ -24750,19 +24792,19 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" t="s" s="17">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="I8" t="s" s="17">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="J8" t="s" s="17">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="K8" t="s" s="17">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="L8" t="s" s="17">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -24770,10 +24812,10 @@
     </row>
     <row r="9" ht="68.05" customHeight="1">
       <c r="A9" t="s" s="8">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="16">
@@ -24787,19 +24829,19 @@
       </c>
       <c r="G9" s="10"/>
       <c r="H9" t="s" s="17">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="I9" t="s" s="17">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="J9" t="s" s="17">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="K9" t="s" s="17">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="L9" t="s" s="17">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="M9" t="s" s="17">
         <v>35</v>
@@ -24811,10 +24853,10 @@
     </row>
     <row r="10" ht="68.05" customHeight="1">
       <c r="A10" t="s" s="8">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="16">
@@ -24828,19 +24870,19 @@
       </c>
       <c r="G10" s="10"/>
       <c r="H10" t="s" s="17">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="I10" t="s" s="17">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="J10" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K10" t="s" s="17">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="L10" t="s" s="17">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
@@ -24848,10 +24890,10 @@
     </row>
     <row r="11" ht="68.05" customHeight="1">
       <c r="A11" t="s" s="8">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="16">
@@ -24865,19 +24907,19 @@
       </c>
       <c r="G11" s="10"/>
       <c r="H11" t="s" s="17">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="I11" t="s" s="17">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="J11" t="s" s="17">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K11" t="s" s="17">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="L11" t="s" s="17">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
@@ -24885,10 +24927,10 @@
     </row>
     <row r="12" ht="68.05" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="16">
@@ -24902,19 +24944,19 @@
       </c>
       <c r="G12" s="10"/>
       <c r="H12" t="s" s="17">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="I12" t="s" s="17">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="J12" t="s" s="17">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K12" t="s" s="17">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="L12" t="s" s="17">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
@@ -24922,10 +24964,10 @@
     </row>
     <row r="13" ht="68.05" customHeight="1">
       <c r="A13" t="s" s="8">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="16">
@@ -24939,19 +24981,19 @@
       </c>
       <c r="G13" s="10"/>
       <c r="H13" t="s" s="17">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="I13" t="s" s="17">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="J13" t="s" s="17">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K13" t="s" s="17">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="L13" t="s" s="17">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
@@ -24959,10 +25001,10 @@
     </row>
     <row r="14" ht="68.05" customHeight="1">
       <c r="A14" t="s" s="8">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="16">
@@ -24982,13 +25024,13 @@
         <v>39</v>
       </c>
       <c r="J14" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K14" t="s" s="17">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="L14" t="s" s="17">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="M14" t="s" s="17">
         <v>35</v>
@@ -25000,14 +25042,14 @@
     </row>
     <row r="15" ht="68.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="16">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E15" s="16">
         <v>100</v>
@@ -25017,19 +25059,19 @@
       </c>
       <c r="G15" s="10"/>
       <c r="H15" t="s" s="17">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="I15" t="s" s="17">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="J15" t="s" s="17">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="K15" t="s" s="17">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="L15" t="s" s="17">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="M15" t="s" s="17">
         <v>35</v>
@@ -25041,10 +25083,10 @@
     </row>
     <row r="16" ht="68.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="16">
@@ -25058,19 +25100,19 @@
       </c>
       <c r="G16" s="10"/>
       <c r="H16" t="s" s="17">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="I16" t="s" s="17">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="J16" t="s" s="17">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K16" t="s" s="17">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L16" t="s" s="17">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="M16" t="s" s="17">
         <v>35</v>
@@ -25082,10 +25124,10 @@
     </row>
     <row r="17" ht="68.05" customHeight="1">
       <c r="A17" t="s" s="8">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="16">
@@ -25099,19 +25141,19 @@
       </c>
       <c r="G17" s="10"/>
       <c r="H17" t="s" s="17">
+        <v>735</v>
+      </c>
+      <c r="I17" t="s" s="17">
+        <v>736</v>
+      </c>
+      <c r="J17" t="s" s="17">
         <v>731</v>
       </c>
-      <c r="I17" t="s" s="17">
-        <v>732</v>
-      </c>
-      <c r="J17" t="s" s="17">
-        <v>727</v>
-      </c>
       <c r="K17" t="s" s="17">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="L17" t="s" s="17">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="M17" t="s" s="17">
         <v>35</v>
@@ -25123,10 +25165,10 @@
     </row>
     <row r="18" ht="68.05" customHeight="1">
       <c r="A18" t="s" s="8">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="16">
@@ -25140,19 +25182,19 @@
       </c>
       <c r="G18" s="10"/>
       <c r="H18" t="s" s="17">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="I18" t="s" s="17">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="J18" t="s" s="17">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K18" t="s" s="17">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="L18" t="s" s="17">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="M18" t="s" s="17">
         <v>35</v>
@@ -25164,10 +25206,10 @@
     </row>
     <row r="19" ht="68.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="16">
@@ -25181,19 +25223,19 @@
       </c>
       <c r="G19" s="10"/>
       <c r="H19" t="s" s="17">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="I19" t="s" s="17">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="J19" t="s" s="17">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="K19" t="s" s="17">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="L19" t="s" s="17">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="M19" t="s" s="17">
         <v>35</v>
@@ -25205,10 +25247,10 @@
     </row>
     <row r="20" ht="68.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B20" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="16">
@@ -25222,19 +25264,19 @@
       </c>
       <c r="G20" s="10"/>
       <c r="H20" t="s" s="17">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="I20" t="s" s="17">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="J20" t="s" s="17">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="K20" t="s" s="17">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L20" t="s" s="17">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="M20" t="s" s="17">
         <v>35</v>
@@ -25246,10 +25288,10 @@
     </row>
     <row r="21" ht="68.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B21" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="16">
@@ -25263,19 +25305,19 @@
       </c>
       <c r="G21" s="10"/>
       <c r="H21" t="s" s="17">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="I21" t="s" s="17">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="J21" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K21" t="s" s="17">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="L21" t="s" s="17">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
@@ -25283,10 +25325,10 @@
     </row>
     <row r="22" ht="68.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B22" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="16">
@@ -25300,19 +25342,19 @@
       </c>
       <c r="G22" s="10"/>
       <c r="H22" t="s" s="17">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="I22" t="s" s="17">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="J22" t="s" s="17">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="K22" t="s" s="17">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="L22" t="s" s="17">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
@@ -25320,10 +25362,10 @@
     </row>
     <row r="23" ht="80.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B23" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="16">
@@ -25337,19 +25379,19 @@
       </c>
       <c r="G23" s="10"/>
       <c r="H23" t="s" s="17">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="I23" t="s" s="17">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="J23" t="s" s="17">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="K23" t="s" s="17">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="L23" t="s" s="17">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
@@ -25357,10 +25399,10 @@
     </row>
     <row r="24" ht="68.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B24" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="16">
@@ -25374,19 +25416,19 @@
       </c>
       <c r="G24" s="10"/>
       <c r="H24" t="s" s="17">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="I24" t="s" s="17">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="J24" t="s" s="17">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="K24" t="s" s="17">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="L24" t="s" s="17">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
@@ -25394,10 +25436,10 @@
     </row>
     <row r="25" ht="68.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="16">
@@ -25411,19 +25453,19 @@
       </c>
       <c r="G25" s="10"/>
       <c r="H25" t="s" s="17">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="I25" t="s" s="17">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="J25" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K25" t="s" s="17">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="L25" t="s" s="17">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
@@ -25431,10 +25473,10 @@
     </row>
     <row r="26" ht="68.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="16">
@@ -25454,13 +25496,13 @@
         <v>39</v>
       </c>
       <c r="J26" t="s" s="17">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K26" t="s" s="17">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="L26" t="s" s="17">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="M26" t="s" s="17">
         <v>35</v>
@@ -25472,10 +25514,10 @@
     </row>
     <row r="27" ht="68.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="16">
@@ -25489,19 +25531,19 @@
       </c>
       <c r="G27" s="10"/>
       <c r="H27" t="s" s="17">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="I27" t="s" s="17">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="J27" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K27" t="s" s="17">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="L27" t="s" s="17">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
@@ -25509,10 +25551,10 @@
     </row>
     <row r="28" ht="92.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="16">
@@ -25526,19 +25568,19 @@
       </c>
       <c r="G28" s="10"/>
       <c r="H28" t="s" s="17">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="I28" t="s" s="17">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="J28" t="s" s="17">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="K28" t="s" s="17">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="L28" t="s" s="17">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="M28" t="s" s="17">
         <v>35</v>
@@ -25550,10 +25592,10 @@
     </row>
     <row r="29" ht="68.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="16">
@@ -25567,19 +25609,19 @@
       </c>
       <c r="G29" s="10"/>
       <c r="H29" t="s" s="17">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="I29" t="s" s="17">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="J29" t="s" s="17">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="K29" t="s" s="17">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="L29" t="s" s="17">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -25587,10 +25629,10 @@
     </row>
     <row r="30" ht="68.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="16">
@@ -25610,13 +25652,13 @@
         <v>39</v>
       </c>
       <c r="J30" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K30" t="s" s="17">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="L30" t="s" s="17">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
@@ -25624,10 +25666,10 @@
     </row>
     <row r="31" ht="80.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="16">
@@ -25641,19 +25683,19 @@
       </c>
       <c r="G31" s="10"/>
       <c r="H31" t="s" s="17">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="I31" t="s" s="17">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="J31" t="s" s="17">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="K31" t="s" s="17">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="L31" t="s" s="17">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
@@ -25661,10 +25703,10 @@
     </row>
     <row r="32" ht="68.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="16">
@@ -25678,19 +25720,19 @@
       </c>
       <c r="G32" s="10"/>
       <c r="H32" t="s" s="17">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="I32" t="s" s="17">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="J32" t="s" s="17">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="K32" t="s" s="17">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="L32" t="s" s="17">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="M32" t="s" s="17">
         <v>35</v>
@@ -25702,10 +25744,10 @@
     </row>
     <row r="33" ht="68.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="16">
@@ -25725,13 +25767,13 @@
         <v>39</v>
       </c>
       <c r="J33" t="s" s="17">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="K33" t="s" s="17">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="L33" t="s" s="17">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="M33" t="s" s="17">
         <v>35</v>
@@ -25743,10 +25785,10 @@
     </row>
     <row r="34" ht="68.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="16">
@@ -25760,19 +25802,19 @@
       </c>
       <c r="G34" s="10"/>
       <c r="H34" t="s" s="17">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="I34" t="s" s="17">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="J34" t="s" s="17">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="K34" t="s" s="17">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L34" t="s" s="17">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="M34" t="s" s="17">
         <v>35</v>
@@ -25784,10 +25826,10 @@
     </row>
     <row r="35" ht="68.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="16">
@@ -25807,13 +25849,13 @@
         <v>39</v>
       </c>
       <c r="J35" t="s" s="17">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="K35" t="s" s="17">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="L35" t="s" s="17">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="M35" t="s" s="17">
         <v>35</v>
@@ -25825,10 +25867,10 @@
     </row>
     <row r="36" ht="68.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="16">
@@ -25842,19 +25884,19 @@
       </c>
       <c r="G36" s="10"/>
       <c r="H36" t="s" s="17">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="I36" t="s" s="17">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="J36" t="s" s="17">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="K36" t="s" s="17">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="L36" t="s" s="17">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
@@ -25862,10 +25904,10 @@
     </row>
     <row r="37" ht="68.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B37" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="16">
@@ -25885,13 +25927,13 @@
         <v>39</v>
       </c>
       <c r="J37" t="s" s="17">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="K37" t="s" s="17">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="L37" t="s" s="17">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="M37" t="s" s="17">
         <v>35</v>
@@ -25901,12 +25943,12 @@
       </c>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" ht="80.05" customHeight="1">
+    <row r="38" ht="68.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B38" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="16">
@@ -25920,19 +25962,19 @@
       </c>
       <c r="G38" s="10"/>
       <c r="H38" t="s" s="17">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="I38" t="s" s="17">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="J38" t="s" s="17">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="K38" t="s" s="17">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="L38" t="s" s="17">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -25940,10 +25982,10 @@
     </row>
     <row r="39" ht="68.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B39" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="16">
@@ -25957,19 +25999,19 @@
       </c>
       <c r="G39" s="10"/>
       <c r="H39" t="s" s="17">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="I39" t="s" s="17">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="J39" t="s" s="17">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K39" t="s" s="17">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="L39" t="s" s="17">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="M39" t="s" s="17">
         <v>35</v>
@@ -25981,10 +26023,10 @@
     </row>
     <row r="40" ht="68.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="B40" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="16">
@@ -25998,19 +26040,19 @@
       </c>
       <c r="G40" s="10"/>
       <c r="H40" t="s" s="17">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="I40" t="s" s="17">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="J40" t="s" s="17">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="K40" t="s" s="17">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="L40" t="s" s="17">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="M40" t="s" s="17">
         <v>35</v>
@@ -26022,10 +26064,10 @@
     </row>
     <row r="41" ht="68.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="16">
@@ -26045,13 +26087,13 @@
         <v>39</v>
       </c>
       <c r="J41" t="s" s="17">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="K41" t="s" s="17">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="L41" t="s" s="17">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="M41" t="s" s="17">
         <v>35</v>
@@ -26063,10 +26105,10 @@
     </row>
     <row r="42" ht="68.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="16">
@@ -26080,19 +26122,19 @@
       </c>
       <c r="G42" s="10"/>
       <c r="H42" t="s" s="17">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="I42" t="s" s="17">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="J42" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K42" t="s" s="17">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="L42" t="s" s="17">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10"/>
@@ -26100,10 +26142,10 @@
     </row>
     <row r="43" ht="80.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="16">
@@ -26117,19 +26159,19 @@
       </c>
       <c r="G43" s="10"/>
       <c r="H43" t="s" s="17">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="I43" t="s" s="17">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="J43" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K43" t="s" s="17">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="L43" t="s" s="17">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10"/>
@@ -26137,10 +26179,10 @@
     </row>
     <row r="44" ht="68.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="16">
@@ -26154,19 +26196,19 @@
       </c>
       <c r="G44" s="10"/>
       <c r="H44" t="s" s="17">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="I44" t="s" s="17">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="J44" t="s" s="17">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="K44" t="s" s="17">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="L44" t="s" s="17">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10"/>
@@ -26174,10 +26216,10 @@
     </row>
     <row r="45" ht="68.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="16">
@@ -26191,19 +26233,19 @@
       </c>
       <c r="G45" s="10"/>
       <c r="H45" t="s" s="17">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="I45" t="s" s="17">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="J45" t="s" s="17">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="K45" t="s" s="17">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="L45" t="s" s="17">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10"/>
@@ -26211,10 +26253,10 @@
     </row>
     <row r="46" ht="68.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="16">
@@ -26228,19 +26270,19 @@
       </c>
       <c r="G46" s="10"/>
       <c r="H46" t="s" s="17">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="I46" t="s" s="17">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="J46" t="s" s="17">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="K46" t="s" s="17">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="L46" t="s" s="17">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="M46" t="s" s="17">
         <v>35</v>
@@ -26252,10 +26294,10 @@
     </row>
     <row r="47" ht="68.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="16">
@@ -26269,19 +26311,19 @@
       </c>
       <c r="G47" s="10"/>
       <c r="H47" t="s" s="17">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="I47" t="s" s="17">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="J47" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K47" t="s" s="17">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="L47" t="s" s="17">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10"/>
@@ -26289,10 +26331,10 @@
     </row>
     <row r="48" ht="68.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="16">
@@ -26306,19 +26348,19 @@
       </c>
       <c r="G48" s="10"/>
       <c r="H48" t="s" s="17">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="I48" t="s" s="17">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="J48" t="s" s="17">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="K48" t="s" s="17">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="L48" t="s" s="17">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10"/>
@@ -26326,10 +26368,10 @@
     </row>
     <row r="49" ht="68.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="16">
@@ -26349,13 +26391,13 @@
         <v>39</v>
       </c>
       <c r="J49" t="s" s="17">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="K49" t="s" s="17">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="L49" t="s" s="17">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="M49" t="s" s="17">
         <v>35</v>
@@ -26367,10 +26409,10 @@
     </row>
     <row r="50" ht="68.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="16">
@@ -26384,298 +26426,294 @@
       </c>
       <c r="G50" s="10"/>
       <c r="H50" t="s" s="17">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="I50" t="s" s="17">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="J50" t="s" s="17">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="K50" t="s" s="17">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="L50" t="s" s="17">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10"/>
       <c r="O50" s="10"/>
     </row>
-    <row r="51" ht="68.05" customHeight="1">
+    <row r="51" ht="80.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="B51" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="16">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E51" s="16">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F51" t="s" s="17">
         <v>3</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" t="s" s="17">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="I51" t="s" s="17">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="J51" t="s" s="17">
-        <v>760</v>
+        <v>910</v>
       </c>
       <c r="K51" t="s" s="17">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="L51" t="s" s="17">
-        <v>902</v>
-      </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
+        <v>912</v>
+      </c>
+      <c r="M51" t="s" s="17">
+        <v>35</v>
+      </c>
+      <c r="N51" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="O51" s="10"/>
     </row>
-    <row r="52" ht="80.05" customHeight="1">
+    <row r="52" ht="92.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>903</v>
+        <v>913</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="16">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E52" s="16">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F52" t="s" s="17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G52" s="10"/>
       <c r="H52" t="s" s="17">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="I52" t="s" s="17">
-        <v>905</v>
+        <v>915</v>
       </c>
       <c r="J52" t="s" s="17">
-        <v>906</v>
+        <v>916</v>
       </c>
       <c r="K52" t="s" s="17">
-        <v>907</v>
+        <v>917</v>
       </c>
       <c r="L52" t="s" s="17">
-        <v>908</v>
-      </c>
-      <c r="M52" t="s" s="17">
-        <v>35</v>
-      </c>
-      <c r="N52" t="s" s="17">
-        <v>35</v>
-      </c>
+        <v>918</v>
+      </c>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
       <c r="O52" s="10"/>
     </row>
-    <row r="53" ht="92.05" customHeight="1">
+    <row r="53" ht="68.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>909</v>
+        <v>919</v>
       </c>
       <c r="B53" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="16">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E53" s="16">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F53" t="s" s="17">
         <v>7</v>
       </c>
       <c r="G53" s="10"/>
       <c r="H53" t="s" s="17">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="I53" t="s" s="17">
-        <v>911</v>
+        <v>921</v>
       </c>
       <c r="J53" t="s" s="17">
-        <v>912</v>
+        <v>664</v>
       </c>
       <c r="K53" t="s" s="17">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="L53" t="s" s="17">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10"/>
       <c r="O53" s="10"/>
     </row>
-    <row r="54" ht="68.05" customHeight="1">
+    <row r="54" ht="80.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="B54" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="16">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E54" s="16">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G54" s="10"/>
-      <c r="H54" t="s" s="17">
-        <v>916</v>
-      </c>
+      <c r="H54" s="10"/>
       <c r="I54" t="s" s="17">
-        <v>917</v>
-      </c>
-      <c r="J54" t="s" s="17">
-        <v>918</v>
-      </c>
+        <v>925</v>
+      </c>
+      <c r="J54" s="10"/>
       <c r="K54" t="s" s="17">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="L54" t="s" s="17">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10"/>
       <c r="O54" s="10"/>
     </row>
-    <row r="55" ht="80.05" customHeight="1">
+    <row r="55" ht="68.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="B55" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="16">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="E55" s="16">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F55" t="s" s="17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+      <c r="H55" t="s" s="17">
+        <v>929</v>
+      </c>
       <c r="I55" t="s" s="17">
-        <v>922</v>
-      </c>
-      <c r="J55" s="10"/>
+        <v>930</v>
+      </c>
+      <c r="J55" t="s" s="17">
+        <v>931</v>
+      </c>
       <c r="K55" t="s" s="17">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="L55" t="s" s="17">
-        <v>924</v>
-      </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
+        <v>933</v>
+      </c>
+      <c r="M55" t="s" s="17">
+        <v>35</v>
+      </c>
+      <c r="N55" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="O55" s="10"/>
     </row>
-    <row r="56" ht="68.05" customHeight="1">
+    <row r="56" ht="80.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="16">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="E56" s="16">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="F56" t="s" s="17">
         <v>7</v>
       </c>
       <c r="G56" s="10"/>
       <c r="H56" t="s" s="17">
-        <v>926</v>
+        <v>935</v>
       </c>
       <c r="I56" t="s" s="17">
-        <v>927</v>
-      </c>
-      <c r="J56" t="s" s="17">
-        <v>928</v>
-      </c>
+        <v>936</v>
+      </c>
+      <c r="J56" s="10"/>
       <c r="K56" t="s" s="17">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="L56" t="s" s="17">
-        <v>920</v>
-      </c>
-      <c r="M56" t="s" s="17">
-        <v>35</v>
-      </c>
-      <c r="N56" t="s" s="17">
-        <v>35</v>
-      </c>
+        <v>938</v>
+      </c>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
       <c r="O56" s="10"/>
     </row>
     <row r="57" ht="80.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="B57" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="16">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="E57" s="16">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="F57" t="s" s="17">
         <v>7</v>
       </c>
       <c r="G57" s="10"/>
-      <c r="H57" t="s" s="17">
-        <v>931</v>
-      </c>
+      <c r="H57" s="10"/>
       <c r="I57" t="s" s="17">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="J57" s="10"/>
       <c r="K57" t="s" s="17">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="L57" t="s" s="17">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10"/>
       <c r="O57" s="10"/>
     </row>
-    <row r="58" ht="80.05" customHeight="1">
+    <row r="58" ht="92.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="16">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E58" s="16">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F58" t="s" s="17">
         <v>7</v>
@@ -26683,47 +26721,47 @@
       <c r="G58" s="10"/>
       <c r="H58" s="10"/>
       <c r="I58" t="s" s="17">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="J58" s="10"/>
       <c r="K58" t="s" s="17">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="L58" t="s" s="17">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10"/>
       <c r="O58" s="10"/>
     </row>
-    <row r="59" ht="92.05" customHeight="1">
+    <row r="59" ht="80.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="B59" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="16">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E59" s="16">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F59" t="s" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
       <c r="I59" t="s" s="17">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="J59" s="10"/>
       <c r="K59" t="s" s="17">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="L59" t="s" s="17">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10"/>
@@ -26731,32 +26769,32 @@
     </row>
     <row r="60" ht="80.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="16">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="E60" s="16">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F60" t="s" s="17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
       <c r="I60" t="s" s="17">
-        <v>944</v>
+        <v>39</v>
       </c>
       <c r="J60" s="10"/>
       <c r="K60" t="s" s="17">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="L60" t="s" s="17">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10"/>
@@ -26764,17 +26802,17 @@
     </row>
     <row r="61" ht="80.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="B61" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="16">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E61" s="16">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F61" t="s" s="17">
         <v>7</v>
@@ -26782,14 +26820,14 @@
       <c r="G61" s="10"/>
       <c r="H61" s="10"/>
       <c r="I61" t="s" s="17">
-        <v>39</v>
+        <v>955</v>
       </c>
       <c r="J61" s="10"/>
       <c r="K61" t="s" s="17">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="L61" t="s" s="17">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10"/>
@@ -26797,17 +26835,17 @@
     </row>
     <row r="62" ht="80.05" customHeight="1">
       <c r="A62" t="s" s="8">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="B62" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="16">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E62" s="16">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F62" t="s" s="17">
         <v>7</v>
@@ -26815,14 +26853,14 @@
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
       <c r="I62" t="s" s="17">
-        <v>951</v>
+        <v>153</v>
       </c>
       <c r="J62" s="10"/>
       <c r="K62" t="s" s="17">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="L62" t="s" s="17">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10"/>
@@ -26830,17 +26868,17 @@
     </row>
     <row r="63" ht="80.05" customHeight="1">
       <c r="A63" t="s" s="8">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="B63" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="16">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E63" s="16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s" s="17">
         <v>7</v>
@@ -26848,14 +26886,14 @@
       <c r="G63" s="10"/>
       <c r="H63" s="10"/>
       <c r="I63" t="s" s="17">
-        <v>153</v>
+        <v>962</v>
       </c>
       <c r="J63" s="10"/>
       <c r="K63" t="s" s="17">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="L63" t="s" s="17">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10"/>
@@ -26863,17 +26901,17 @@
     </row>
     <row r="64" ht="80.05" customHeight="1">
       <c r="A64" t="s" s="8">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="B64" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="16">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E64" s="16">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F64" t="s" s="17">
         <v>7</v>
@@ -26881,14 +26919,14 @@
       <c r="G64" s="10"/>
       <c r="H64" s="10"/>
       <c r="I64" t="s" s="17">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="J64" s="10"/>
       <c r="K64" t="s" s="17">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="L64" t="s" s="17">
-        <v>960</v>
+        <v>927</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10"/>
@@ -26896,17 +26934,17 @@
     </row>
     <row r="65" ht="80.05" customHeight="1">
       <c r="A65" t="s" s="8">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="B65" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="16">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E65" s="16">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F65" t="s" s="17">
         <v>7</v>
@@ -26914,14 +26952,14 @@
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" t="s" s="17">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="J65" s="10"/>
       <c r="K65" t="s" s="17">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="L65" t="s" s="17">
-        <v>924</v>
+        <v>971</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10"/>
@@ -26929,17 +26967,17 @@
     </row>
     <row r="66" ht="80.05" customHeight="1">
       <c r="A66" t="s" s="8">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="B66" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="16">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E66" s="16">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F66" t="s" s="17">
         <v>7</v>
@@ -26947,32 +26985,32 @@
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
       <c r="I66" t="s" s="17">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="J66" s="10"/>
       <c r="K66" t="s" s="17">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="L66" t="s" s="17">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10"/>
       <c r="O66" s="10"/>
     </row>
-    <row r="67" ht="80.05" customHeight="1">
+    <row r="67" ht="104.05" customHeight="1">
       <c r="A67" t="s" s="8">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="B67" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="16">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="E67" s="16">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F67" t="s" s="17">
         <v>7</v>
@@ -26980,32 +27018,32 @@
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
       <c r="I67" t="s" s="17">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="J67" s="10"/>
       <c r="K67" t="s" s="17">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="L67" t="s" s="17">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10"/>
       <c r="O67" s="10"/>
     </row>
-    <row r="68" ht="104.05" customHeight="1">
+    <row r="68" ht="80.05" customHeight="1">
       <c r="A68" t="s" s="8">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="B68" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="16">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="E68" s="16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F68" t="s" s="17">
         <v>7</v>
@@ -27013,14 +27051,14 @@
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
       <c r="I68" t="s" s="17">
-        <v>972</v>
+        <v>39</v>
       </c>
       <c r="J68" s="10"/>
       <c r="K68" t="s" s="17">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="L68" t="s" s="17">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10"/>
@@ -27028,17 +27066,17 @@
     </row>
     <row r="69" ht="80.05" customHeight="1">
       <c r="A69" t="s" s="8">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="B69" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="16">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="E69" s="16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F69" t="s" s="17">
         <v>7</v>
@@ -27046,14 +27084,14 @@
       <c r="G69" s="10"/>
       <c r="H69" s="10"/>
       <c r="I69" t="s" s="17">
-        <v>39</v>
+        <v>981</v>
       </c>
       <c r="J69" s="10"/>
       <c r="K69" t="s" s="17">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="L69" t="s" s="17">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10"/>
@@ -27061,17 +27099,17 @@
     </row>
     <row r="70" ht="80.05" customHeight="1">
       <c r="A70" t="s" s="8">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="B70" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="16">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="E70" s="16">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F70" t="s" s="17">
         <v>7</v>
@@ -27079,14 +27117,14 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" t="s" s="17">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="J70" s="10"/>
       <c r="K70" t="s" s="17">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="L70" t="s" s="17">
-        <v>967</v>
+        <v>986</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10"/>
@@ -27094,69 +27132,77 @@
     </row>
     <row r="71" ht="80.05" customHeight="1">
       <c r="A71" t="s" s="8">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="B71" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="16">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="E71" s="16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F71" t="s" s="17">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
+      <c r="H71" t="s" s="17">
+        <v>39</v>
+      </c>
       <c r="I71" t="s" s="17">
-        <v>980</v>
-      </c>
-      <c r="J71" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="J71" t="s" s="17">
+        <v>854</v>
+      </c>
       <c r="K71" t="s" s="17">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="L71" t="s" s="17">
-        <v>982</v>
-      </c>
-      <c r="M71" s="10"/>
-      <c r="N71" s="10"/>
+        <v>989</v>
+      </c>
+      <c r="M71" t="s" s="17">
+        <v>35</v>
+      </c>
+      <c r="N71" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="O71" s="10"/>
     </row>
     <row r="72" ht="80.05" customHeight="1">
       <c r="A72" t="s" s="8">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="B72" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="16">
+        <v>50</v>
+      </c>
+      <c r="E72" s="16">
         <v>45</v>
       </c>
-      <c r="E72" s="16">
-        <v>40</v>
-      </c>
       <c r="F72" t="s" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G72" s="10"/>
       <c r="H72" t="s" s="17">
-        <v>39</v>
+        <v>991</v>
       </c>
       <c r="I72" t="s" s="17">
-        <v>39</v>
+        <v>992</v>
       </c>
       <c r="J72" t="s" s="17">
-        <v>850</v>
+        <v>664</v>
       </c>
       <c r="K72" t="s" s="17">
-        <v>984</v>
+        <v>993</v>
       </c>
       <c r="L72" t="s" s="17">
-        <v>985</v>
+        <v>994</v>
       </c>
       <c r="M72" t="s" s="17">
         <v>35</v>
@@ -27168,36 +27214,36 @@
     </row>
     <row r="73" ht="80.05" customHeight="1">
       <c r="A73" t="s" s="8">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="B73" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="16">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E73" s="16">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F73" t="s" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G73" s="10"/>
       <c r="H73" t="s" s="17">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="I73" t="s" s="17">
-        <v>988</v>
+        <v>997</v>
       </c>
       <c r="J73" t="s" s="17">
-        <v>660</v>
+        <v>748</v>
       </c>
       <c r="K73" t="s" s="17">
-        <v>989</v>
+        <v>998</v>
       </c>
       <c r="L73" t="s" s="17">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="M73" t="s" s="17">
         <v>35</v>
@@ -27209,36 +27255,36 @@
     </row>
     <row r="74" ht="80.05" customHeight="1">
       <c r="A74" t="s" s="8">
-        <v>991</v>
+        <v>1000</v>
       </c>
       <c r="B74" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="16">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E74" s="16">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F74" t="s" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G74" s="10"/>
       <c r="H74" t="s" s="17">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="I74" t="s" s="17">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="J74" t="s" s="17">
-        <v>744</v>
+        <v>1003</v>
       </c>
       <c r="K74" t="s" s="17">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="L74" t="s" s="17">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="M74" t="s" s="17">
         <v>35</v>
@@ -27250,36 +27296,36 @@
     </row>
     <row r="75" ht="80.05" customHeight="1">
       <c r="A75" t="s" s="8">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="B75" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="16">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E75" s="16">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s" s="17">
         <v>15</v>
       </c>
       <c r="G75" s="10"/>
       <c r="H75" t="s" s="17">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="I75" t="s" s="17">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="J75" t="s" s="17">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="K75" t="s" s="17">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="L75" t="s" s="17">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="M75" t="s" s="17">
         <v>35</v>
@@ -27291,36 +27337,36 @@
     </row>
     <row r="76" ht="80.05" customHeight="1">
       <c r="A76" t="s" s="8">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="B76" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="16">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E76" s="16">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F76" t="s" s="17">
         <v>15</v>
       </c>
       <c r="G76" s="10"/>
       <c r="H76" t="s" s="17">
+        <v>1013</v>
+      </c>
+      <c r="I76" t="s" s="17">
+        <v>1014</v>
+      </c>
+      <c r="J76" t="s" s="17">
         <v>1003</v>
       </c>
-      <c r="I76" t="s" s="17">
-        <v>1004</v>
-      </c>
-      <c r="J76" t="s" s="17">
-        <v>1005</v>
-      </c>
       <c r="K76" t="s" s="17">
-        <v>1006</v>
+        <v>1015</v>
       </c>
       <c r="L76" t="s" s="17">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="M76" t="s" s="17">
         <v>35</v>
@@ -27332,36 +27378,36 @@
     </row>
     <row r="77" ht="80.05" customHeight="1">
       <c r="A77" t="s" s="8">
-        <v>1008</v>
+        <v>1017</v>
       </c>
       <c r="B77" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="16">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E77" s="16">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F77" t="s" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G77" s="10"/>
       <c r="H77" t="s" s="17">
+        <v>39</v>
+      </c>
+      <c r="I77" t="s" s="17">
+        <v>39</v>
+      </c>
+      <c r="J77" t="s" s="17">
         <v>1009</v>
       </c>
-      <c r="I77" t="s" s="17">
-        <v>1010</v>
-      </c>
-      <c r="J77" t="s" s="17">
-        <v>999</v>
-      </c>
       <c r="K77" t="s" s="17">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="L77" t="s" s="17">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="M77" t="s" s="17">
         <v>35</v>
@@ -27373,36 +27419,36 @@
     </row>
     <row r="78" ht="80.05" customHeight="1">
       <c r="A78" t="s" s="8">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="B78" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="16">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E78" s="16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F78" t="s" s="17">
         <v>13</v>
       </c>
       <c r="G78" s="10"/>
       <c r="H78" t="s" s="17">
-        <v>39</v>
+        <v>1021</v>
       </c>
       <c r="I78" t="s" s="17">
-        <v>39</v>
+        <v>1022</v>
       </c>
       <c r="J78" t="s" s="17">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="K78" t="s" s="17">
-        <v>1014</v>
+        <v>1023</v>
       </c>
       <c r="L78" t="s" s="17">
-        <v>1015</v>
+        <v>1024</v>
       </c>
       <c r="M78" t="s" s="17">
         <v>35</v>
@@ -27412,38 +27458,38 @@
       </c>
       <c r="O78" s="10"/>
     </row>
-    <row r="79" ht="80.05" customHeight="1">
+    <row r="79" ht="68.05" customHeight="1">
       <c r="A79" t="s" s="8">
-        <v>1016</v>
+        <v>1025</v>
       </c>
       <c r="B79" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E79" s="16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F79" t="s" s="17">
         <v>13</v>
       </c>
       <c r="G79" s="10"/>
       <c r="H79" t="s" s="17">
-        <v>1017</v>
+        <v>1026</v>
       </c>
       <c r="I79" t="s" s="17">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="J79" t="s" s="17">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="K79" t="s" s="17">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="L79" t="s" s="17">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="M79" t="s" s="17">
         <v>35</v>
@@ -27453,38 +27499,38 @@
       </c>
       <c r="O79" s="10"/>
     </row>
-    <row r="80" ht="68.05" customHeight="1">
+    <row r="80" ht="80.05" customHeight="1">
       <c r="A80" t="s" s="8">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="B80" t="s" s="9">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="16">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E80" s="16">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F80" t="s" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G80" s="10"/>
       <c r="H80" t="s" s="17">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="I80" t="s" s="17">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="J80" t="s" s="17">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="K80" t="s" s="17">
-        <v>1025</v>
+        <v>1034</v>
       </c>
       <c r="L80" t="s" s="17">
-        <v>1026</v>
+        <v>1035</v>
       </c>
       <c r="M80" t="s" s="17">
         <v>35</v>
@@ -27494,80 +27540,72 @@
       </c>
       <c r="O80" s="10"/>
     </row>
-    <row r="81" ht="80.05" customHeight="1">
+    <row r="81" ht="20.05" customHeight="1">
       <c r="A81" t="s" s="8">
-        <v>1027</v>
-      </c>
-      <c r="B81" t="s" s="9">
-        <v>659</v>
-      </c>
+        <v>1036</v>
+      </c>
+      <c r="B81" s="12"/>
       <c r="C81" s="10"/>
-      <c r="D81" s="16">
-        <v>30</v>
-      </c>
-      <c r="E81" s="16">
-        <v>20</v>
-      </c>
-      <c r="F81" t="s" s="17">
-        <v>11</v>
-      </c>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
       <c r="G81" s="10"/>
-      <c r="H81" t="s" s="17">
-        <v>1028</v>
-      </c>
-      <c r="I81" t="s" s="17">
-        <v>1029</v>
-      </c>
-      <c r="J81" t="s" s="17">
-        <v>1005</v>
-      </c>
-      <c r="K81" t="s" s="17">
-        <v>1030</v>
-      </c>
-      <c r="L81" t="s" s="17">
-        <v>1031</v>
-      </c>
-      <c r="M81" t="s" s="17">
-        <v>35</v>
-      </c>
-      <c r="N81" t="s" s="17">
-        <v>35</v>
-      </c>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
       <c r="O81" s="10"/>
     </row>
-    <row r="82" ht="20.05" customHeight="1">
+    <row r="82" ht="32.05" customHeight="1">
       <c r="A82" t="s" s="8">
-        <v>1032</v>
+        <v>1037</v>
       </c>
       <c r="B82" s="12"/>
       <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
+      <c r="D82" s="16">
+        <v>160</v>
+      </c>
+      <c r="E82" s="16">
+        <v>160</v>
+      </c>
+      <c r="F82" t="s" s="17">
+        <v>3</v>
+      </c>
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
+      <c r="I82" t="s" s="17">
+        <v>39</v>
+      </c>
       <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
+      <c r="K82" t="s" s="17">
+        <v>1038</v>
+      </c>
       <c r="L82" s="10"/>
       <c r="M82" s="10"/>
       <c r="N82" s="10"/>
       <c r="O82" s="10"/>
     </row>
-    <row r="83" ht="20.05" customHeight="1">
+    <row r="83" ht="44.05" customHeight="1">
       <c r="A83" t="s" s="8">
-        <v>569</v>
+        <v>1039</v>
       </c>
       <c r="B83" s="12"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
+      <c r="F83" t="s" s="17">
+        <v>13</v>
+      </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
+      <c r="K83" t="s" s="17">
+        <v>1040</v>
+      </c>
       <c r="L83" s="10"/>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
@@ -27575,90 +27613,72 @@
     </row>
     <row r="84" ht="32.05" customHeight="1">
       <c r="A84" t="s" s="8">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="B84" s="12"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="16">
-        <v>160</v>
-      </c>
-      <c r="E84" s="16">
-        <v>160</v>
-      </c>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
       <c r="F84" t="s" s="17">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
-      <c r="I84" t="s" s="17">
-        <v>39</v>
-      </c>
+      <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" t="s" s="17">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="L84" s="10"/>
       <c r="M84" s="10"/>
       <c r="N84" s="10"/>
       <c r="O84" s="10"/>
     </row>
-    <row r="85" ht="44.05" customHeight="1">
+    <row r="85" ht="20.05" customHeight="1">
       <c r="A85" t="s" s="8">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="B85" s="12"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
       <c r="E85" s="10"/>
       <c r="F85" t="s" s="17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G85" s="10"/>
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
-      <c r="K85" t="s" s="17">
-        <v>1036</v>
-      </c>
+      <c r="K85" s="10"/>
       <c r="L85" s="10"/>
       <c r="M85" s="10"/>
       <c r="N85" s="10"/>
       <c r="O85" s="10"/>
     </row>
-    <row r="86" ht="32.05" customHeight="1">
-      <c r="A86" t="s" s="8">
-        <v>1037</v>
-      </c>
+    <row r="86" ht="20.05" customHeight="1">
+      <c r="A86" s="11"/>
       <c r="B86" s="12"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
-      <c r="F86" t="s" s="17">
-        <v>13</v>
-      </c>
+      <c r="F86" s="10"/>
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="10"/>
       <c r="J86" s="10"/>
-      <c r="K86" t="s" s="17">
-        <v>1038</v>
-      </c>
+      <c r="K86" s="10"/>
       <c r="L86" s="10"/>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
       <c r="O86" s="10"/>
     </row>
     <row r="87" ht="20.05" customHeight="1">
-      <c r="A87" t="s" s="8">
-        <v>1039</v>
-      </c>
+      <c r="A87" s="11"/>
       <c r="B87" s="12"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
       <c r="E87" s="10"/>
-      <c r="F87" t="s" s="17">
-        <v>11</v>
-      </c>
+      <c r="F87" s="10"/>
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
@@ -35573,40 +35593,6 @@
       <c r="M552" s="10"/>
       <c r="N552" s="10"/>
       <c r="O552" s="10"/>
-    </row>
-    <row r="553" ht="20.05" customHeight="1">
-      <c r="A553" s="11"/>
-      <c r="B553" s="12"/>
-      <c r="C553" s="10"/>
-      <c r="D553" s="10"/>
-      <c r="E553" s="10"/>
-      <c r="F553" s="10"/>
-      <c r="G553" s="10"/>
-      <c r="H553" s="10"/>
-      <c r="I553" s="10"/>
-      <c r="J553" s="10"/>
-      <c r="K553" s="10"/>
-      <c r="L553" s="10"/>
-      <c r="M553" s="10"/>
-      <c r="N553" s="10"/>
-      <c r="O553" s="10"/>
-    </row>
-    <row r="554" ht="20.05" customHeight="1">
-      <c r="A554" s="11"/>
-      <c r="B554" s="12"/>
-      <c r="C554" s="10"/>
-      <c r="D554" s="10"/>
-      <c r="E554" s="10"/>
-      <c r="F554" s="10"/>
-      <c r="G554" s="10"/>
-      <c r="H554" s="10"/>
-      <c r="I554" s="10"/>
-      <c r="J554" s="10"/>
-      <c r="K554" s="10"/>
-      <c r="L554" s="10"/>
-      <c r="M554" s="10"/>
-      <c r="N554" s="10"/>
-      <c r="O554" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -35699,23 +35685,23 @@
       </c>
       <c r="N2" t="s" s="3">
         <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N545,"Yes")</f>
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="O2" t="s" s="3">
         <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O545,"Yes")</f>
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="P2" t="s" s="3">
         <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P545,"Yes")</f>
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="3" ht="32.25" customHeight="1">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C3" s="14">
         <v>0</v>
@@ -35727,7 +35713,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" t="s" s="15">
@@ -35746,10 +35732,10 @@
     </row>
     <row r="4" ht="44.05" customHeight="1">
       <c r="A4" t="s" s="8">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C4" s="16">
         <v>200</v>
@@ -35761,7 +35747,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="s" s="17">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" t="s" s="17">
@@ -35780,10 +35766,10 @@
     </row>
     <row r="5" ht="44.05" customHeight="1">
       <c r="A5" t="s" s="8">
+        <v>1052</v>
+      </c>
+      <c r="B5" t="s" s="9">
         <v>1048</v>
-      </c>
-      <c r="B5" t="s" s="9">
-        <v>1044</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -35795,7 +35781,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s" s="17">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" t="s" s="17">
@@ -35814,10 +35800,10 @@
     </row>
     <row r="6" ht="44.05" customHeight="1">
       <c r="A6" t="s" s="8">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -35829,7 +35815,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="s" s="17">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" t="s" s="17">
@@ -35848,10 +35834,10 @@
     </row>
     <row r="7" ht="32.05" customHeight="1">
       <c r="A7" t="s" s="8">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C7" s="16">
         <v>500</v>
@@ -35863,7 +35849,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s" s="17">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" t="s" s="17">
@@ -35882,10 +35868,10 @@
     </row>
     <row r="8" ht="44.05" customHeight="1">
       <c r="A8" t="s" s="8">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
@@ -35897,7 +35883,7 @@
         <v>5</v>
       </c>
       <c r="H8" t="s" s="17">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" t="s" s="17">
@@ -35916,10 +35902,10 @@
     </row>
     <row r="9" ht="32.05" customHeight="1">
       <c r="A9" t="s" s="8">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C9" s="16">
         <v>800</v>
@@ -35931,7 +35917,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="17">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" t="s" s="17">
@@ -35950,10 +35936,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="8">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C10" s="16">
         <v>250</v>
@@ -35965,7 +35951,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="17">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" t="s" s="17">
@@ -35984,10 +35970,10 @@
     </row>
     <row r="11" ht="32.05" customHeight="1">
       <c r="A11" t="s" s="8">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C11" s="16">
         <v>1000</v>
@@ -35999,7 +35985,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="17">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" t="s" s="17">
@@ -36018,10 +36004,10 @@
     </row>
     <row r="12" ht="44.05" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C12" s="16">
         <v>200</v>
@@ -36033,7 +36019,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="s" s="17">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" t="s" s="17">
@@ -36048,10 +36034,10 @@
     </row>
     <row r="13" ht="32.05" customHeight="1">
       <c r="A13" t="s" s="8">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C13" s="16">
         <v>500</v>
@@ -36063,7 +36049,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="s" s="17">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" t="s" s="17">
@@ -36082,10 +36068,10 @@
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" t="s" s="8">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C14" s="16">
         <v>1500</v>
@@ -36097,7 +36083,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="17">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" t="s" s="17">
@@ -36116,10 +36102,10 @@
     </row>
     <row r="15" ht="32.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C15" s="16">
         <v>500</v>
@@ -36131,7 +36117,7 @@
         <v>4</v>
       </c>
       <c r="H15" t="s" s="17">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" t="s" s="17">
@@ -36150,10 +36136,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C16" s="16">
         <v>1500</v>
@@ -36165,7 +36151,7 @@
         <v>5</v>
       </c>
       <c r="H16" t="s" s="17">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" t="s" s="17">
@@ -36184,10 +36170,10 @@
     </row>
     <row r="17" ht="44.05" customHeight="1">
       <c r="A17" t="s" s="8">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C17" s="16">
         <v>900</v>
@@ -36199,7 +36185,7 @@
         <v>4</v>
       </c>
       <c r="H17" t="s" s="17">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" t="s" s="17">
@@ -36218,10 +36204,10 @@
     </row>
     <row r="18" ht="44.05" customHeight="1">
       <c r="A18" t="s" s="8">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
@@ -36233,7 +36219,7 @@
         <v>3</v>
       </c>
       <c r="H18" t="s" s="17">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" t="s" s="17">
@@ -36252,10 +36238,10 @@
     </row>
     <row r="19" ht="44.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C19" s="16">
         <v>800</v>
@@ -36267,7 +36253,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="17">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" t="s" s="17">
@@ -36282,10 +36268,10 @@
     </row>
     <row r="20" ht="44.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B20" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C20" s="16">
         <v>600</v>
@@ -36297,7 +36283,7 @@
         <v>4</v>
       </c>
       <c r="H20" t="s" s="17">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" t="s" s="17">
@@ -36310,12 +36296,12 @@
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
     </row>
-    <row r="21" ht="32.05" customHeight="1">
+    <row r="21" ht="44.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B21" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C21" s="16">
         <v>0</v>
@@ -36327,7 +36313,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s" s="17">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" t="s" s="17">
@@ -36344,12 +36330,12 @@
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" ht="32.05" customHeight="1">
+    <row r="22" ht="44.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B22" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C22" s="16">
         <v>50</v>
@@ -36361,7 +36347,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s" s="17">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" t="s" s="17">
@@ -36376,10 +36362,10 @@
     </row>
     <row r="23" ht="32.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B23" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C23" s="16">
         <v>100</v>
@@ -36391,7 +36377,7 @@
         <v>3</v>
       </c>
       <c r="H23" t="s" s="17">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" t="s" s="17">
@@ -36406,10 +36392,10 @@
     </row>
     <row r="24" ht="44.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="B24" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C24" s="16">
         <v>1000</v>
@@ -36421,7 +36407,7 @@
         <v>5</v>
       </c>
       <c r="H24" t="s" s="17">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" t="s" s="17">
@@ -36436,10 +36422,10 @@
     </row>
     <row r="25" ht="44.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C25" s="16">
         <v>850</v>
@@ -36451,7 +36437,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s" s="17">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" t="s" s="17">
@@ -36466,10 +36452,10 @@
     </row>
     <row r="26" ht="32.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C26" s="16">
         <v>600</v>
@@ -36481,7 +36467,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s" s="17">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" t="s" s="17">
@@ -36496,10 +36482,10 @@
     </row>
     <row r="27" ht="44.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C27" s="16">
         <v>600</v>
@@ -36511,7 +36497,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="17">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" t="s" s="17">
@@ -36526,10 +36512,10 @@
     </row>
     <row r="28" ht="44.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C28" s="16">
         <v>600</v>
@@ -36541,7 +36527,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s" s="17">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" t="s" s="17">
@@ -36556,10 +36542,10 @@
     </row>
     <row r="29" ht="32.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C29" s="16">
         <v>600</v>
@@ -36571,7 +36557,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s" s="17">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" t="s" s="17">
@@ -36586,10 +36572,10 @@
     </row>
     <row r="30" ht="44.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C30" s="16">
         <v>600</v>
@@ -36601,7 +36587,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s" s="17">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" t="s" s="17">
@@ -36616,10 +36602,10 @@
     </row>
     <row r="31" ht="44.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C31" s="16">
         <v>600</v>
@@ -36631,7 +36617,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s" s="17">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" t="s" s="17">
@@ -36646,10 +36632,10 @@
     </row>
     <row r="32" ht="44.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C32" s="16">
         <v>600</v>
@@ -36661,7 +36647,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s" s="17">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" t="s" s="17">
@@ -36676,10 +36662,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C33" s="16">
         <v>300</v>
@@ -36691,7 +36677,7 @@
         <v>2</v>
       </c>
       <c r="H33" t="s" s="17">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" t="s" s="17">
@@ -36706,10 +36692,10 @@
     </row>
     <row r="34" ht="44.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C34" s="16">
         <v>800</v>
@@ -36721,7 +36707,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="17">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" t="s" s="17">
@@ -36736,10 +36722,10 @@
     </row>
     <row r="35" ht="56.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C35" s="16">
         <v>800</v>
@@ -36751,7 +36737,7 @@
         <v>3</v>
       </c>
       <c r="H35" t="s" s="17">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" t="s" s="17">
@@ -36766,10 +36752,10 @@
     </row>
     <row r="36" ht="44.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C36" s="16">
         <v>800</v>
@@ -36781,7 +36767,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="17">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" t="s" s="17">
@@ -36796,10 +36782,10 @@
     </row>
     <row r="37" ht="44.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="B37" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C37" s="16">
         <v>800</v>
@@ -36811,7 +36797,7 @@
         <v>3</v>
       </c>
       <c r="H37" t="s" s="17">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" t="s" s="17">
@@ -36826,10 +36812,10 @@
     </row>
     <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="B38" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C38" s="16">
         <v>800</v>
@@ -36841,7 +36827,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="17">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" t="s" s="17">
@@ -36856,10 +36842,10 @@
     </row>
     <row r="39" ht="56.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B39" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C39" s="16">
         <v>800</v>
@@ -36871,7 +36857,7 @@
         <v>3</v>
       </c>
       <c r="H39" t="s" s="17">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" t="s" s="17">
@@ -36884,12 +36870,12 @@
       <c r="O39" s="10"/>
       <c r="P39" s="10"/>
     </row>
-    <row r="40" ht="68.05" customHeight="1">
+    <row r="40" ht="56.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="B40" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C40" s="16">
         <v>800</v>
@@ -36901,7 +36887,7 @@
         <v>3</v>
       </c>
       <c r="H40" t="s" s="17">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" t="s" s="17">
@@ -36916,10 +36902,10 @@
     </row>
     <row r="41" ht="44.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C41" s="16">
         <v>1200</v>
@@ -36931,7 +36917,7 @@
         <v>3</v>
       </c>
       <c r="H41" t="s" s="17">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" t="s" s="17">
@@ -36946,10 +36932,10 @@
     </row>
     <row r="42" ht="44.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C42" s="16">
         <v>1500</v>
@@ -36961,7 +36947,7 @@
         <v>4</v>
       </c>
       <c r="H42" t="s" s="17">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" t="s" s="17">
@@ -36976,10 +36962,10 @@
     </row>
     <row r="43" ht="44.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C43" s="16">
         <v>100</v>
@@ -36991,7 +36977,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="17">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" t="s" s="17">
@@ -37010,10 +36996,10 @@
     </row>
     <row r="44" ht="32.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C44" s="16">
         <v>700</v>
@@ -37025,7 +37011,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="17">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" t="s" s="17">
@@ -37044,10 +37030,10 @@
     </row>
     <row r="45" ht="32.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C45" s="16">
         <v>1200</v>
@@ -37059,7 +37045,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s" s="17">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -37072,10 +37058,10 @@
     </row>
     <row r="46" ht="32.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C46" s="16">
         <v>1500</v>
@@ -37087,7 +37073,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="17">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -37100,10 +37086,10 @@
     </row>
     <row r="47" ht="32.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C47" s="16">
         <v>950</v>
@@ -37115,7 +37101,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="17">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -37128,10 +37114,10 @@
     </row>
     <row r="48" ht="44.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C48" s="16">
         <v>0</v>
@@ -37143,7 +37129,7 @@
         <v>3</v>
       </c>
       <c r="H48" t="s" s="17">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -37156,10 +37142,10 @@
     </row>
     <row r="49" ht="68.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C49" s="16">
         <v>2000</v>
@@ -37171,7 +37157,7 @@
         <v>5</v>
       </c>
       <c r="H49" t="s" s="17">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
@@ -37182,12 +37168,12 @@
       <c r="O49" s="10"/>
       <c r="P49" s="10"/>
     </row>
-    <row r="50" ht="56.05" customHeight="1">
+    <row r="50" ht="44.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C50" s="16">
         <v>100</v>
@@ -37199,7 +37185,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="17">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
@@ -37212,7 +37198,7 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="16">
@@ -37225,7 +37211,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="17">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
@@ -37238,10 +37224,10 @@
     </row>
     <row r="52" ht="32.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C52" s="16">
         <v>0</v>
@@ -37253,7 +37239,7 @@
         <v>2</v>
       </c>
       <c r="H52" t="s" s="17">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" t="s" s="17">
@@ -37272,7 +37258,7 @@
     </row>
     <row r="53" ht="32.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="16">
@@ -37285,7 +37271,7 @@
         <v>2</v>
       </c>
       <c r="H53" t="s" s="17">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
@@ -37298,7 +37284,7 @@
     </row>
     <row r="54" ht="32.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="16">
@@ -37311,7 +37297,7 @@
         <v>3</v>
       </c>
       <c r="H54" t="s" s="17">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
@@ -37324,10 +37310,10 @@
     </row>
     <row r="55" ht="32.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="B55" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C55" s="16">
         <v>0</v>
@@ -37339,7 +37325,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="s" s="17">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" t="s" s="17">
@@ -37358,10 +37344,10 @@
     </row>
     <row r="56" ht="44.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C56" s="16">
         <v>0</v>
@@ -37373,7 +37359,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="s" s="17">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" t="s" s="17">
@@ -37392,7 +37378,7 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="16">
@@ -37405,7 +37391,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="s" s="17">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
@@ -37418,10 +37404,10 @@
     </row>
     <row r="58" ht="44.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C58" s="16">
         <v>0</v>
@@ -37433,7 +37419,7 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="17">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" t="s" s="17">
@@ -37452,7 +37438,7 @@
     </row>
     <row r="59" ht="44.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="16">
@@ -37465,7 +37451,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="17">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
@@ -37476,12 +37462,12 @@
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
     </row>
-    <row r="60" ht="44.05" customHeight="1">
+    <row r="60" ht="56.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C60" s="16">
         <v>0</v>
@@ -37493,7 +37479,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="s" s="17">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" t="s" s="17">
@@ -37512,7 +37498,7 @@
     </row>
     <row r="61" ht="56.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="16">
@@ -37525,7 +37511,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="17">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -46326,7 +46312,7 @@
         <v>24</v>
       </c>
       <c r="J2" t="s" s="3">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="K2" t="s" s="3">
         <v>26</v>
@@ -46339,23 +46325,23 @@
       </c>
       <c r="N2" t="s" s="3">
         <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N556,"Yes")</f>
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="O2" t="s" s="3">
         <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O556,"Yes")</f>
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="P2" t="s" s="3">
         <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P556,"Yes")</f>
-        <v>1165</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="3" ht="32.25" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C3" s="14">
         <v>0</v>
@@ -46367,7 +46353,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" t="s" s="15">
@@ -46377,17 +46363,15 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
-      <c r="O3" t="s" s="15">
-        <v>35</v>
-      </c>
+      <c r="O3" s="7"/>
       <c r="P3" s="7"/>
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" t="s" s="8">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C4" s="16">
         <v>0</v>
@@ -46399,7 +46383,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s" s="17">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" t="s" s="17">
@@ -46416,12 +46400,12 @@
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" ht="44.05" customHeight="1">
+    <row r="5" ht="32.05" customHeight="1">
       <c r="A5" t="s" s="8">
+        <v>1175</v>
+      </c>
+      <c r="B5" t="s" s="9">
         <v>1171</v>
-      </c>
-      <c r="B5" t="s" s="9">
-        <v>1167</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -46433,7 +46417,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="s" s="17">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" t="s" s="17">
@@ -46448,10 +46432,10 @@
     </row>
     <row r="6" ht="80.05" customHeight="1">
       <c r="A6" t="s" s="8">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -46463,7 +46447,7 @@
         <v>5</v>
       </c>
       <c r="H6" t="s" s="17">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" t="s" s="17">
@@ -46478,10 +46462,10 @@
     </row>
     <row r="7" ht="56.05" customHeight="1">
       <c r="A7" t="s" s="8">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
@@ -46493,7 +46477,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s" s="17">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" t="s" s="17">
@@ -46508,10 +46492,10 @@
     </row>
     <row r="8" ht="56.05" customHeight="1">
       <c r="A8" t="s" s="8">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
@@ -46523,7 +46507,7 @@
         <v>3</v>
       </c>
       <c r="H8" t="s" s="17">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" t="s" s="17">
@@ -46538,10 +46522,10 @@
     </row>
     <row r="9" ht="56.05" customHeight="1">
       <c r="A9" t="s" s="8">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C9" s="16">
         <v>0</v>
@@ -46553,7 +46537,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="17">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" t="s" s="17">
@@ -46568,10 +46552,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="8">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C10" s="16">
         <v>0</v>
@@ -46583,7 +46567,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="17">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" t="s" s="17">
@@ -46602,10 +46586,10 @@
     </row>
     <row r="11" ht="44.05" customHeight="1">
       <c r="A11" t="s" s="8">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C11" s="16">
         <v>0</v>
@@ -46617,7 +46601,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="17">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" t="s" s="17">
@@ -46636,10 +46620,10 @@
     </row>
     <row r="12" ht="44.05" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C12" s="16">
         <v>0</v>
@@ -46651,7 +46635,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s" s="17">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" t="s" s="17">
@@ -46670,10 +46654,10 @@
     </row>
     <row r="13" ht="44.05" customHeight="1">
       <c r="A13" t="s" s="8">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C13" s="16">
         <v>0</v>
@@ -46685,7 +46669,7 @@
         <v>4</v>
       </c>
       <c r="H13" t="s" s="17">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" t="s" s="17">
@@ -46702,12 +46686,12 @@
       </c>
       <c r="P13" s="10"/>
     </row>
-    <row r="14" ht="68.05" customHeight="1">
+    <row r="14" ht="56.05" customHeight="1">
       <c r="A14" t="s" s="8">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C14" s="16">
         <v>3000</v>
@@ -46719,7 +46703,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="17">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" t="s" s="17">
@@ -46732,12 +46716,12 @@
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
     </row>
-    <row r="15" ht="68.05" customHeight="1">
+    <row r="15" ht="56.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C15" s="16">
         <v>2000</v>
@@ -46749,7 +46733,7 @@
         <v>3</v>
       </c>
       <c r="H15" t="s" s="17">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" t="s" s="17">
@@ -46764,10 +46748,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C16" s="16">
         <v>1000</v>
@@ -46779,7 +46763,7 @@
         <v>4</v>
       </c>
       <c r="H16" t="s" s="17">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" t="s" s="17">
@@ -46798,10 +46782,10 @@
     </row>
     <row r="17" ht="32.05" customHeight="1">
       <c r="A17" t="s" s="8">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C17" s="16">
         <v>1000</v>
@@ -46813,7 +46797,7 @@
         <v>3</v>
       </c>
       <c r="H17" t="s" s="17">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" t="s" s="17">
@@ -46832,10 +46816,10 @@
     </row>
     <row r="18" ht="56.05" customHeight="1">
       <c r="A18" t="s" s="8">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C18" s="16">
         <v>500</v>
@@ -46847,7 +46831,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="s" s="17">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" t="s" s="17">
@@ -46862,10 +46846,10 @@
     </row>
     <row r="19" ht="32.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C19" s="16">
         <v>1000</v>
@@ -46877,7 +46861,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="17">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" t="s" s="17">
@@ -46892,10 +46876,10 @@
     </row>
     <row r="20" ht="56.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="B20" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C20" s="16">
         <v>600</v>
@@ -46907,7 +46891,7 @@
         <v>3</v>
       </c>
       <c r="H20" t="s" s="17">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" t="s" s="17">
@@ -46922,10 +46906,10 @@
     </row>
     <row r="21" ht="32.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="B21" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C21" s="16">
         <v>1500</v>
@@ -46937,7 +46921,7 @@
         <v>4</v>
       </c>
       <c r="H21" t="s" s="17">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" t="s" s="17">
@@ -46952,10 +46936,10 @@
     </row>
     <row r="22" ht="44.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="B22" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C22" s="16">
         <v>850</v>
@@ -46967,7 +46951,7 @@
         <v>3</v>
       </c>
       <c r="H22" t="s" s="17">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" t="s" s="17">
@@ -46982,10 +46966,10 @@
     </row>
     <row r="23" ht="44.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="B23" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C23" s="16">
         <v>1000</v>
@@ -46997,7 +46981,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="s" s="17">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" t="s" s="17">
@@ -47016,10 +47000,10 @@
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="B24" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C24" s="16">
         <v>2000</v>
@@ -47031,7 +47015,7 @@
         <v>4</v>
       </c>
       <c r="H24" t="s" s="17">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" t="s" s="17">
@@ -47046,10 +47030,10 @@
     </row>
     <row r="25" ht="56.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C25" s="16">
         <v>1000</v>
@@ -47061,7 +47045,7 @@
         <v>3</v>
       </c>
       <c r="H25" t="s" s="17">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" t="s" s="17">
@@ -47080,10 +47064,10 @@
     </row>
     <row r="26" ht="80.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C26" s="16">
         <v>2000</v>
@@ -47095,7 +47079,7 @@
         <v>5</v>
       </c>
       <c r="H26" t="s" s="17">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" t="s" s="17">
@@ -47110,10 +47094,10 @@
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C27" s="16">
         <v>600</v>
@@ -47125,7 +47109,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="17">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" t="s" s="17">
@@ -47144,10 +47128,10 @@
     </row>
     <row r="28" ht="44.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C28" s="16">
         <v>500</v>
@@ -47159,7 +47143,7 @@
         <v>2</v>
       </c>
       <c r="H28" t="s" s="17">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" t="s" s="17">
@@ -47174,10 +47158,10 @@
     </row>
     <row r="29" ht="80.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C29" s="16">
         <v>700</v>
@@ -47189,7 +47173,7 @@
         <v>5</v>
       </c>
       <c r="H29" t="s" s="17">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" t="s" s="17">
@@ -47204,10 +47188,10 @@
     </row>
     <row r="30" ht="80.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C30" s="16">
         <v>1200</v>
@@ -47219,7 +47203,7 @@
         <v>4</v>
       </c>
       <c r="H30" t="s" s="17">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" t="s" s="17">
@@ -47234,10 +47218,10 @@
     </row>
     <row r="31" ht="68.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C31" s="16">
         <v>1000</v>
@@ -47249,7 +47233,7 @@
         <v>5</v>
       </c>
       <c r="H31" t="s" s="17">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" t="s" s="17">
@@ -47264,10 +47248,10 @@
     </row>
     <row r="32" ht="56.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C32" s="16">
         <v>1800</v>
@@ -47279,7 +47263,7 @@
         <v>5</v>
       </c>
       <c r="H32" t="s" s="17">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" t="s" s="17">
@@ -47294,10 +47278,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C33" s="16">
         <v>1500</v>
@@ -47309,7 +47293,7 @@
         <v>4</v>
       </c>
       <c r="H33" t="s" s="17">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" t="s" s="17">
@@ -47326,12 +47310,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="56.05" customHeight="1">
+    <row r="34" ht="44.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C34" s="16">
         <v>1000</v>
@@ -47343,7 +47327,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="17">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
@@ -47356,10 +47340,10 @@
     </row>
     <row r="35" ht="44.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C35" s="16">
         <v>600</v>
@@ -47371,7 +47355,7 @@
         <v>2</v>
       </c>
       <c r="H35" t="s" s="17">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
@@ -47384,10 +47368,10 @@
     </row>
     <row r="36" ht="56.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C36" s="16">
         <v>250</v>
@@ -47399,7 +47383,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="17">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
@@ -47412,10 +47396,10 @@
     </row>
     <row r="37" ht="32.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="B37" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C37" s="16">
         <v>300</v>
@@ -47427,7 +47411,7 @@
         <v>2</v>
       </c>
       <c r="H37" t="s" s="17">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -47440,10 +47424,10 @@
     </row>
     <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="B38" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C38" s="16">
         <v>1000</v>
@@ -47455,7 +47439,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="17">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -47468,10 +47452,10 @@
     </row>
     <row r="39" ht="32.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="B39" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C39" s="16">
         <v>1200</v>
@@ -47483,7 +47467,7 @@
         <v>4</v>
       </c>
       <c r="H39" t="s" s="17">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -47496,10 +47480,10 @@
     </row>
     <row r="40" ht="20.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B40" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C40" s="16">
         <v>0</v>
@@ -47511,7 +47495,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="s" s="17">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
@@ -47524,10 +47508,10 @@
     </row>
     <row r="41" ht="32.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C41" s="16">
         <v>0</v>
@@ -47539,7 +47523,7 @@
         <v>2</v>
       </c>
       <c r="H41" t="s" s="17">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
@@ -47552,10 +47536,10 @@
     </row>
     <row r="42" ht="32.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C42" s="16">
         <v>0</v>
@@ -47567,7 +47551,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s" s="17">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -47580,10 +47564,10 @@
     </row>
     <row r="43" ht="32.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C43" s="16">
         <v>0</v>
@@ -47595,7 +47579,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="17">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
@@ -47608,10 +47592,10 @@
     </row>
     <row r="44" ht="20.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C44" s="16">
         <v>0</v>
@@ -47623,7 +47607,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="17">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
@@ -47634,12 +47618,12 @@
       <c r="O44" s="10"/>
       <c r="P44" s="10"/>
     </row>
-    <row r="45" ht="68.05" customHeight="1">
+    <row r="45" ht="56.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C45" s="16">
         <v>0</v>
@@ -47651,7 +47635,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s" s="17">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -47664,10 +47648,10 @@
     </row>
     <row r="46" ht="44.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C46" s="16">
         <v>0</v>
@@ -47679,7 +47663,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="17">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -47692,10 +47676,10 @@
     </row>
     <row r="47" ht="44.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C47" s="16">
         <v>0</v>
@@ -47707,7 +47691,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="17">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -47720,10 +47704,10 @@
     </row>
     <row r="48" ht="56.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C48" s="16">
         <v>500</v>
@@ -47735,7 +47719,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="s" s="17">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -47748,10 +47732,10 @@
     </row>
     <row r="49" ht="32.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C49" s="16">
         <v>0</v>
@@ -47763,7 +47747,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s" s="17">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
@@ -47776,10 +47760,10 @@
     </row>
     <row r="50" ht="32.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C50" s="16">
         <v>600</v>
@@ -47791,7 +47775,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="17">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
@@ -47804,10 +47788,10 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="B51" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C51" s="16">
         <v>0</v>
@@ -47819,7 +47803,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="17">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
@@ -47832,10 +47816,10 @@
     </row>
     <row r="52" ht="68.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C52" s="16">
         <v>200</v>
@@ -47847,7 +47831,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s" s="17">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
@@ -47860,10 +47844,10 @@
     </row>
     <row r="53" ht="68.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="B53" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C53" s="16">
         <v>200</v>
@@ -47875,7 +47859,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="s" s="17">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
@@ -47888,10 +47872,10 @@
     </row>
     <row r="54" ht="80.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="B54" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C54" s="16">
         <v>600</v>
@@ -47903,7 +47887,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s" s="17">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
@@ -47916,10 +47900,10 @@
     </row>
     <row r="55" ht="68.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="B55" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C55" s="16">
         <v>500</v>
@@ -47931,7 +47915,7 @@
         <v>2</v>
       </c>
       <c r="H55" t="s" s="17">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
@@ -47944,10 +47928,10 @@
     </row>
     <row r="56" ht="44.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C56" s="16">
         <v>900</v>
@@ -47959,7 +47943,7 @@
         <v>2</v>
       </c>
       <c r="H56" t="s" s="17">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
@@ -47972,10 +47956,10 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="B57" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C57" s="16">
         <v>0</v>
@@ -47987,7 +47971,7 @@
         <v>2</v>
       </c>
       <c r="H57" t="s" s="17">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
@@ -48000,10 +47984,10 @@
     </row>
     <row r="58" ht="56.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C58" s="16">
         <v>450</v>
@@ -48015,7 +47999,7 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="17">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
@@ -48028,10 +48012,10 @@
     </row>
     <row r="59" ht="68.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="B59" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C59" s="16">
         <v>450</v>
@@ -48043,7 +48027,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="17">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
@@ -48054,12 +48038,12 @@
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
     </row>
-    <row r="60" ht="56.05" customHeight="1">
+    <row r="60" ht="44.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C60" s="16">
         <v>200</v>
@@ -48071,7 +48055,7 @@
         <v>4</v>
       </c>
       <c r="H60" t="s" s="17">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
@@ -48084,10 +48068,10 @@
     </row>
     <row r="61" ht="32.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="B61" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C61" s="16">
         <v>1200</v>
@@ -48099,7 +48083,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="17">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -48112,10 +48096,10 @@
     </row>
     <row r="62" ht="44.05" customHeight="1">
       <c r="A62" t="s" s="8">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B62" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C62" s="16">
         <v>0</v>
@@ -48127,7 +48111,7 @@
         <v>2</v>
       </c>
       <c r="H62" t="s" s="17">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
@@ -48138,12 +48122,12 @@
       <c r="O62" s="10"/>
       <c r="P62" s="10"/>
     </row>
-    <row r="63" ht="44.05" customHeight="1">
+    <row r="63" ht="32.05" customHeight="1">
       <c r="A63" t="s" s="8">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="B63" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C63" s="16">
         <v>0</v>
@@ -48155,7 +48139,7 @@
         <v>4</v>
       </c>
       <c r="H63" t="s" s="17">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
@@ -48168,10 +48152,10 @@
     </row>
     <row r="64" ht="32.05" customHeight="1">
       <c r="A64" t="s" s="8">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="B64" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C64" s="16">
         <v>0</v>
@@ -48183,7 +48167,7 @@
         <v>4</v>
       </c>
       <c r="H64" t="s" s="17">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
@@ -48194,12 +48178,12 @@
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
     </row>
-    <row r="65" ht="92.05" customHeight="1">
+    <row r="65" ht="80.05" customHeight="1">
       <c r="A65" t="s" s="8">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="B65" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C65" s="16">
         <v>800</v>
@@ -48211,7 +48195,7 @@
         <v>3</v>
       </c>
       <c r="H65" t="s" s="17">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
@@ -48224,10 +48208,10 @@
     </row>
     <row r="66" ht="80.05" customHeight="1">
       <c r="A66" t="s" s="8">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="B66" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C66" s="16">
         <v>800</v>
@@ -48239,7 +48223,7 @@
         <v>2</v>
       </c>
       <c r="H66" t="s" s="17">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
@@ -48252,10 +48236,10 @@
     </row>
     <row r="67" ht="68.05" customHeight="1">
       <c r="A67" t="s" s="8">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="B67" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C67" s="16">
         <v>1000</v>
@@ -48267,7 +48251,7 @@
         <v>5</v>
       </c>
       <c r="H67" t="s" s="17">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
@@ -48278,12 +48262,12 @@
       <c r="O67" s="10"/>
       <c r="P67" s="10"/>
     </row>
-    <row r="68" ht="68.05" customHeight="1">
+    <row r="68" ht="56.05" customHeight="1">
       <c r="A68" t="s" s="8">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="B68" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C68" s="16">
         <v>1500</v>
@@ -48295,7 +48279,7 @@
         <v>3</v>
       </c>
       <c r="H68" t="s" s="17">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
@@ -48306,12 +48290,12 @@
       <c r="O68" s="10"/>
       <c r="P68" s="10"/>
     </row>
-    <row r="69" ht="56.05" customHeight="1">
+    <row r="69" ht="44.05" customHeight="1">
       <c r="A69" t="s" s="8">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="B69" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C69" s="16">
         <v>1200</v>
@@ -48323,7 +48307,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s" s="17">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
@@ -48336,10 +48320,10 @@
     </row>
     <row r="70" ht="56.05" customHeight="1">
       <c r="A70" t="s" s="8">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="B70" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C70" s="16">
         <v>300</v>
@@ -48351,7 +48335,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="s" s="17">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
@@ -48364,10 +48348,10 @@
     </row>
     <row r="71" ht="68.05" customHeight="1">
       <c r="A71" t="s" s="8">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="B71" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C71" s="16">
         <v>300</v>
@@ -48379,7 +48363,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="s" s="17">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
@@ -48390,12 +48374,12 @@
       <c r="O71" s="10"/>
       <c r="P71" s="10"/>
     </row>
-    <row r="72" ht="80.05" customHeight="1">
+    <row r="72" ht="68.05" customHeight="1">
       <c r="A72" t="s" s="8">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="B72" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C72" s="16">
         <v>500</v>
@@ -48407,7 +48391,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s" s="17">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
@@ -48420,10 +48404,10 @@
     </row>
     <row r="73" ht="44.05" customHeight="1">
       <c r="A73" t="s" s="8">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="B73" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C73" s="16">
         <v>2000</v>
@@ -48435,7 +48419,7 @@
         <v>4</v>
       </c>
       <c r="H73" t="s" s="17">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
@@ -48448,10 +48432,10 @@
     </row>
     <row r="74" ht="44.05" customHeight="1">
       <c r="A74" t="s" s="8">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="B74" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C74" s="16">
         <v>2000</v>
@@ -48463,7 +48447,7 @@
         <v>5</v>
       </c>
       <c r="H74" t="s" s="17">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
@@ -48476,10 +48460,10 @@
     </row>
     <row r="75" ht="44.05" customHeight="1">
       <c r="A75" t="s" s="8">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="B75" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C75" s="16">
         <v>2000</v>
@@ -48491,7 +48475,7 @@
         <v>5</v>
       </c>
       <c r="H75" t="s" s="17">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
@@ -48504,10 +48488,10 @@
     </row>
     <row r="76" ht="44.05" customHeight="1">
       <c r="A76" t="s" s="8">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="B76" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C76" s="16">
         <v>2000</v>
@@ -48519,7 +48503,7 @@
         <v>5</v>
       </c>
       <c r="H76" t="s" s="17">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
@@ -48532,10 +48516,10 @@
     </row>
     <row r="77" ht="44.05" customHeight="1">
       <c r="A77" t="s" s="8">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="B77" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C77" s="16">
         <v>2000</v>
@@ -48547,7 +48531,7 @@
         <v>5</v>
       </c>
       <c r="H77" t="s" s="17">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
@@ -48560,10 +48544,10 @@
     </row>
     <row r="78" ht="44.05" customHeight="1">
       <c r="A78" t="s" s="8">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B78" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C78" s="16">
         <v>2000</v>
@@ -48575,7 +48559,7 @@
         <v>5</v>
       </c>
       <c r="H78" t="s" s="17">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
@@ -48588,10 +48572,10 @@
     </row>
     <row r="79" ht="44.05" customHeight="1">
       <c r="A79" t="s" s="8">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="B79" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C79" s="16">
         <v>2000</v>
@@ -48603,7 +48587,7 @@
         <v>5</v>
       </c>
       <c r="H79" t="s" s="17">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
@@ -48616,10 +48600,10 @@
     </row>
     <row r="80" ht="20.05" customHeight="1">
       <c r="A80" t="s" s="8">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="B80" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C80" s="16">
         <v>1200</v>
@@ -48631,7 +48615,7 @@
         <v>4</v>
       </c>
       <c r="H80" t="s" s="17">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
@@ -48644,10 +48628,10 @@
     </row>
     <row r="81" ht="56.05" customHeight="1">
       <c r="A81" t="s" s="8">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="B81" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C81" s="16">
         <v>2000</v>
@@ -48659,7 +48643,7 @@
         <v>3</v>
       </c>
       <c r="H81" t="s" s="17">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
@@ -48672,10 +48656,10 @@
     </row>
     <row r="82" ht="44.05" customHeight="1">
       <c r="A82" t="s" s="8">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="B82" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C82" s="16">
         <v>1000</v>
@@ -48687,7 +48671,7 @@
         <v>3</v>
       </c>
       <c r="H82" t="s" s="17">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
@@ -48698,12 +48682,12 @@
       <c r="O82" s="10"/>
       <c r="P82" s="10"/>
     </row>
-    <row r="83" ht="44.05" customHeight="1">
+    <row r="83" ht="32.05" customHeight="1">
       <c r="A83" t="s" s="8">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="B83" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C83" s="16">
         <v>500</v>
@@ -48715,7 +48699,7 @@
         <v>2</v>
       </c>
       <c r="H83" t="s" s="17">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
@@ -48726,12 +48710,12 @@
       <c r="O83" s="10"/>
       <c r="P83" s="10"/>
     </row>
-    <row r="84" ht="44.05" customHeight="1">
+    <row r="84" ht="32.05" customHeight="1">
       <c r="A84" t="s" s="8">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="B84" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C84" s="16">
         <v>250</v>
@@ -48743,7 +48727,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s" s="17">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
@@ -48756,10 +48740,10 @@
     </row>
     <row r="85" ht="80.05" customHeight="1">
       <c r="A85" t="s" s="8">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="B85" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C85" s="16">
         <v>1500</v>
@@ -48771,7 +48755,7 @@
         <v>4</v>
       </c>
       <c r="H85" t="s" s="17">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
@@ -48784,10 +48768,10 @@
     </row>
     <row r="86" ht="32.05" customHeight="1">
       <c r="A86" t="s" s="8">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="B86" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C86" s="16">
         <v>1000</v>
@@ -48799,7 +48783,7 @@
         <v>3</v>
       </c>
       <c r="H86" t="s" s="17">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="10"/>
@@ -48812,10 +48796,10 @@
     </row>
     <row r="87" ht="44.05" customHeight="1">
       <c r="A87" t="s" s="8">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="B87" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C87" s="16">
         <v>800</v>
@@ -48827,7 +48811,7 @@
         <v>2</v>
       </c>
       <c r="H87" t="s" s="17">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
@@ -48840,10 +48824,10 @@
     </row>
     <row r="88" ht="32.05" customHeight="1">
       <c r="A88" t="s" s="8">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="B88" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C88" s="16">
         <v>200</v>
@@ -48855,7 +48839,7 @@
         <v>2</v>
       </c>
       <c r="H88" t="s" s="17">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
@@ -48868,10 +48852,10 @@
     </row>
     <row r="89" ht="32.05" customHeight="1">
       <c r="A89" t="s" s="8">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="B89" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C89" s="16">
         <v>1500</v>
@@ -48883,7 +48867,7 @@
         <v>3</v>
       </c>
       <c r="H89" t="s" s="17">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="10"/>
@@ -48896,10 +48880,10 @@
     </row>
     <row r="90" ht="32.05" customHeight="1">
       <c r="A90" t="s" s="8">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="B90" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C90" s="16">
         <v>500</v>
@@ -48911,7 +48895,7 @@
         <v>5</v>
       </c>
       <c r="H90" t="s" s="17">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
@@ -48924,10 +48908,10 @@
     </row>
     <row r="91" ht="80.05" customHeight="1">
       <c r="A91" t="s" s="8">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="B91" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C91" s="16">
         <v>1000</v>
@@ -48939,11 +48923,11 @@
         <v>2</v>
       </c>
       <c r="H91" t="s" s="17">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" t="s" s="17">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="10"/>
@@ -48954,10 +48938,10 @@
     </row>
     <row r="92" ht="56.05" customHeight="1">
       <c r="A92" t="s" s="8">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="B92" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C92" s="16">
         <v>1500</v>
@@ -48969,7 +48953,7 @@
         <v>4</v>
       </c>
       <c r="H92" t="s" s="17">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
@@ -48980,12 +48964,12 @@
       <c r="O92" s="10"/>
       <c r="P92" s="10"/>
     </row>
-    <row r="93" ht="56.05" customHeight="1">
+    <row r="93" ht="44.05" customHeight="1">
       <c r="A93" t="s" s="8">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="B93" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C93" s="16">
         <v>300</v>
@@ -48997,7 +48981,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s" s="17">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
@@ -49010,10 +48994,10 @@
     </row>
     <row r="94" ht="68.05" customHeight="1">
       <c r="A94" t="s" s="8">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="B94" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C94" s="16">
         <v>200</v>
@@ -49025,7 +49009,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="s" s="17">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="10"/>
@@ -49038,10 +49022,10 @@
     </row>
     <row r="95" ht="68.05" customHeight="1">
       <c r="A95" t="s" s="8">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="B95" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C95" s="16">
         <v>0</v>
@@ -49053,7 +49037,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="s" s="17">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
@@ -49066,10 +49050,10 @@
     </row>
     <row r="96" ht="44.05" customHeight="1">
       <c r="A96" t="s" s="8">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="B96" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C96" s="16">
         <v>0</v>
@@ -49081,7 +49065,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="s" s="17">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10"/>
@@ -49092,12 +49076,12 @@
       <c r="O96" s="10"/>
       <c r="P96" s="10"/>
     </row>
-    <row r="97" ht="56.05" customHeight="1">
+    <row r="97" ht="44.05" customHeight="1">
       <c r="A97" t="s" s="8">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B97" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C97" s="16">
         <v>1000</v>
@@ -49109,7 +49093,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s" s="17">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
@@ -49122,10 +49106,10 @@
     </row>
     <row r="98" ht="32.05" customHeight="1">
       <c r="A98" t="s" s="8">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="B98" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C98" s="16">
         <v>0</v>
@@ -49137,7 +49121,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="s" s="17">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="10"/>
@@ -49150,10 +49134,10 @@
     </row>
     <row r="99" ht="44.05" customHeight="1">
       <c r="A99" t="s" s="8">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="B99" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C99" s="16">
         <v>0</v>
@@ -49165,7 +49149,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="s" s="17">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
@@ -49178,10 +49162,10 @@
     </row>
     <row r="100" ht="44.05" customHeight="1">
       <c r="A100" t="s" s="8">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B100" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C100" s="16">
         <v>500</v>
@@ -49193,7 +49177,7 @@
         <v>2</v>
       </c>
       <c r="H100" t="s" s="17">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="10"/>
@@ -49206,10 +49190,10 @@
     </row>
     <row r="101" ht="44.05" customHeight="1">
       <c r="A101" t="s" s="8">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="B101" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C101" s="16">
         <v>0</v>
@@ -49221,7 +49205,7 @@
         <v>2</v>
       </c>
       <c r="H101" t="s" s="17">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="10"/>
@@ -49234,10 +49218,10 @@
     </row>
     <row r="102" ht="44.05" customHeight="1">
       <c r="A102" t="s" s="8">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B102" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C102" s="16">
         <v>600</v>
@@ -49249,7 +49233,7 @@
         <v>2</v>
       </c>
       <c r="H102" t="s" s="17">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
@@ -49262,10 +49246,10 @@
     </row>
     <row r="103" ht="92.05" customHeight="1">
       <c r="A103" t="s" s="8">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="B103" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C103" s="16">
         <v>500</v>
@@ -49277,7 +49261,7 @@
         <v>2</v>
       </c>
       <c r="H103" t="s" s="17">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="10"/>
@@ -49288,12 +49272,12 @@
       <c r="O103" s="10"/>
       <c r="P103" s="10"/>
     </row>
-    <row r="104" ht="68.05" customHeight="1">
+    <row r="104" ht="56.05" customHeight="1">
       <c r="A104" t="s" s="8">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="B104" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C104" s="16">
         <v>2000</v>
@@ -49305,7 +49289,7 @@
         <v>4</v>
       </c>
       <c r="H104" t="s" s="17">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" t="s" s="17">
@@ -49320,10 +49304,10 @@
     </row>
     <row r="105" ht="32.05" customHeight="1">
       <c r="A105" t="s" s="8">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="B105" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C105" s="16">
         <v>1500</v>
@@ -49335,7 +49319,7 @@
         <v>4</v>
       </c>
       <c r="H105" t="s" s="17">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
@@ -49348,10 +49332,10 @@
     </row>
     <row r="106" ht="32.05" customHeight="1">
       <c r="A106" t="s" s="8">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="B106" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C106" s="16">
         <v>0</v>
@@ -49363,7 +49347,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s" s="17">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
@@ -49374,12 +49358,12 @@
       <c r="O106" s="10"/>
       <c r="P106" s="10"/>
     </row>
-    <row r="107" ht="80.05" customHeight="1">
+    <row r="107" ht="68.05" customHeight="1">
       <c r="A107" t="s" s="8">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="B107" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C107" s="16">
         <v>2000</v>
@@ -49391,7 +49375,7 @@
         <v>3</v>
       </c>
       <c r="H107" t="s" s="17">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="10"/>
@@ -49404,10 +49388,10 @@
     </row>
     <row r="108" ht="44.05" customHeight="1">
       <c r="A108" t="s" s="8">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="B108" t="s" s="9">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C108" s="16">
         <v>300</v>
@@ -49417,7 +49401,7 @@
       <c r="F108" s="10"/>
       <c r="G108" s="10"/>
       <c r="H108" t="s" s="17">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
@@ -49428,15 +49412,23 @@
       <c r="O108" s="10"/>
       <c r="P108" s="10"/>
     </row>
-    <row r="109" ht="20.05" customHeight="1">
-      <c r="A109" s="11"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="10"/>
+    <row r="109" ht="56.05" customHeight="1">
+      <c r="A109" t="s" s="8">
+        <v>1384</v>
+      </c>
+      <c r="B109" t="s" s="9">
+        <v>1171</v>
+      </c>
+      <c r="C109" s="16">
+        <v>800</v>
+      </c>
       <c r="D109" s="10"/>
       <c r="E109" s="10"/>
       <c r="F109" s="10"/>
       <c r="G109" s="10"/>
-      <c r="H109" s="10"/>
+      <c r="H109" t="s" s="17">
+        <v>1385</v>
+      </c>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
       <c r="K109" s="10"/>
@@ -49446,15 +49438,23 @@
       <c r="O109" s="10"/>
       <c r="P109" s="10"/>
     </row>
-    <row r="110" ht="20.05" customHeight="1">
-      <c r="A110" s="11"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="10"/>
+    <row r="110" ht="56.05" customHeight="1">
+      <c r="A110" t="s" s="8">
+        <v>1386</v>
+      </c>
+      <c r="B110" t="s" s="9">
+        <v>1171</v>
+      </c>
+      <c r="C110" s="16">
+        <v>600</v>
+      </c>
       <c r="D110" s="10"/>
       <c r="E110" s="10"/>
       <c r="F110" s="10"/>
       <c r="G110" s="10"/>
-      <c r="H110" s="10"/>
+      <c r="H110" t="s" s="17">
+        <v>1387</v>
+      </c>
       <c r="I110" s="10"/>
       <c r="J110" s="10"/>
       <c r="K110" s="10"/>
@@ -49464,15 +49464,23 @@
       <c r="O110" s="10"/>
       <c r="P110" s="10"/>
     </row>
-    <row r="111" ht="20.05" customHeight="1">
-      <c r="A111" s="11"/>
-      <c r="B111" s="12"/>
-      <c r="C111" s="10"/>
+    <row r="111" ht="56.05" customHeight="1">
+      <c r="A111" t="s" s="8">
+        <v>1388</v>
+      </c>
+      <c r="B111" t="s" s="9">
+        <v>1171</v>
+      </c>
+      <c r="C111" s="16">
+        <v>300</v>
+      </c>
       <c r="D111" s="10"/>
       <c r="E111" s="10"/>
       <c r="F111" s="10"/>
       <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
+      <c r="H111" t="s" s="17">
+        <v>1389</v>
+      </c>
       <c r="I111" s="10"/>
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
@@ -57531,21 +57539,21 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="22">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="C2" t="s" s="22">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="D2" t="s" s="22">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="E2" t="s" s="22">
-        <v>1383</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="3" ht="16.55" customHeight="1">
       <c r="A3" t="s" s="23">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="B3" s="24">
         <v>52</v>
@@ -57554,16 +57562,16 @@
         <v>0.347</v>
       </c>
       <c r="D3" t="s" s="26">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="E3" s="27">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,1)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,1)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,1)</f>
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" ht="16.35" customHeight="1">
       <c r="A4" t="s" s="28">
-        <v>1386</v>
+        <v>1396</v>
       </c>
       <c r="B4" s="29">
         <v>48</v>
@@ -57572,7 +57580,7 @@
         <v>0.337</v>
       </c>
       <c r="D4" t="s" s="31">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="E4" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,2)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,2)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,2)</f>
@@ -57581,7 +57589,7 @@
     </row>
     <row r="5" ht="16.35" customHeight="1">
       <c r="A5" t="s" s="28">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="B5" s="29">
         <v>27</v>
@@ -57590,7 +57598,7 @@
         <v>0.167</v>
       </c>
       <c r="D5" t="s" s="31">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="E5" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,3)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,3)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,3)</f>
@@ -57599,7 +57607,7 @@
     </row>
     <row r="6" ht="30.35" customHeight="1">
       <c r="A6" t="s" s="28">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="B6" s="29">
         <v>16</v>
@@ -57608,7 +57616,7 @@
         <v>0.1</v>
       </c>
       <c r="D6" t="s" s="31">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="E6" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,4)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,4)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,4)</f>
@@ -57617,7 +57625,7 @@
     </row>
     <row r="7" ht="16.35" customHeight="1">
       <c r="A7" t="s" s="33">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="B7" s="34">
         <v>9</v>
@@ -57626,7 +57634,7 @@
         <v>0.053</v>
       </c>
       <c r="D7" t="s" s="31">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="E7" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,5)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,5)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,5)</f>
@@ -57659,17 +57667,17 @@
         <v>22</v>
       </c>
       <c r="B11" t="s" s="41">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
       <c r="E11" t="s" s="43">
-        <v>1383</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="12" ht="16.35" customHeight="1">
       <c r="A12" t="s" s="28">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="B12" s="29">
         <v>60</v>
@@ -57683,7 +57691,7 @@
     </row>
     <row r="13" ht="16.35" customHeight="1">
       <c r="A13" t="s" s="28">
-        <v>1394</v>
+        <v>1404</v>
       </c>
       <c r="B13" s="29">
         <v>60</v>
@@ -57697,7 +57705,7 @@
     </row>
     <row r="14" ht="16.35" customHeight="1">
       <c r="A14" t="s" s="28">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="B14" s="29">
         <v>60</v>
@@ -57745,10 +57753,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" t="s" s="3">
-        <v>1396</v>
+        <v>1406</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -57758,10 +57766,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="C3" t="s" s="15">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -57771,10 +57779,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="C4" t="s" s="17">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -57784,10 +57792,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="C5" t="s" s="17">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -57797,10 +57805,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="C6" t="s" s="17">
-        <v>1405</v>
+        <v>1415</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -57810,10 +57818,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="C7" t="s" s="17">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -57823,10 +57831,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="C8" t="s" s="17">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -57836,10 +57844,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="C9" t="s" s="17">
-        <v>1411</v>
+        <v>1421</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>

--- a/context/card_data_demo.xlsx
+++ b/context/card_data_demo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1429">
   <si>
     <t>Table 1</t>
   </si>
@@ -247,7 +247,7 @@
     <t>Pit Lord</t>
   </si>
   <si>
-    <t>his card is destroyed if battle with Divine Unit. After this card attacked, halve its ATK&amp;DEF permanently</t>
+    <t>This card is destroyed if battle with Divine Unit. After this card attacked, halve its ATK&amp;DEF permanently</t>
   </si>
   <si>
     <t>Ancient Lich</t>
@@ -316,7 +316,7 @@
     <t>Leech Man</t>
   </si>
   <si>
-    <t>+20 DEF permanently each time it performed attack and survive. With mutagen flag : +45 ATK</t>
+    <t>+10 DEF permanently after it performed attack on unit. Also +10 ATK with mutagen flag</t>
   </si>
   <si>
     <t>Immortal Vampire</t>
@@ -403,7 +403,7 @@
     <t>Mafia Associates</t>
   </si>
   <si>
-    <t>If this card is exposed, its defense becomes 0</t>
+    <t>At the end of the turn that it’s been exposed, its defense becomes 0</t>
   </si>
   <si>
     <t>Silver Dragon</t>
@@ -535,7 +535,7 @@
     <t>Sniping Fairy</t>
   </si>
   <si>
-    <t>-20 ATK if exposed</t>
+    <t>At the end of the turn that it’s been exposed, -20 ATK</t>
   </si>
   <si>
     <t>Bomber Fairy</t>
@@ -664,7 +664,7 @@
     <t>Mephisto the Fallen</t>
   </si>
   <si>
-    <t>After this card attacked successfully, its ATK becomes 0 permanently</t>
+    <t>After this card attacked unit successfully, its ATK becomes 0 permanently</t>
   </si>
   <si>
     <t>Joseph the Battle Priest</t>
@@ -760,7 +760,7 @@
     <t>Cursed Well</t>
   </si>
   <si>
-    <t>+15 ATK if exposed</t>
+    <t>At the end of the turn that it’s been exposed, +15 ATK</t>
   </si>
   <si>
     <t>Shredder Doll</t>
@@ -1093,7 +1093,7 @@
     <t>Armored Monkey</t>
   </si>
   <si>
-    <t>+10 ATK if there is face-up Nature card</t>
+    <t>+10 ATK if there is another face-up Nature card</t>
   </si>
   <si>
     <t>Magical Butterfly</t>
@@ -1462,7 +1462,7 @@
     <t>Blue Mage</t>
   </si>
   <si>
-    <t>If this card battles non-Arcane card, flip a coins. If both are head, destroy it.</t>
+    <t>If this card battles non-Arcane card, flip two coins. If both are head, destroy it.</t>
   </si>
   <si>
     <t>Spell Sniper</t>
@@ -2321,10 +2321,10 @@
     <t>Diamond Unicorn</t>
   </si>
   <si>
-    <t>+15 ATK until ????</t>
-  </si>
-  <si>
-    <t>+15 ATK until the end of this turn, once.</t>
+    <t>Once Union, ??? until this turn’s end</t>
+  </si>
+  <si>
+    <t>Once Union, +15 ATK until this turn’s end</t>
   </si>
   <si>
     <t>1 ??? + 1 ??? + 500 cost</t>
@@ -3454,6 +3454,21 @@
     <t>Nanomites Dragon</t>
   </si>
   <si>
+    <t>Capnomancer</t>
+  </si>
+  <si>
+    <t>At the start of your turn, you can destroy this card to ???</t>
+  </si>
+  <si>
+    <t>At the start of your turn, you can destroy this card to revive Pyromancer</t>
+  </si>
+  <si>
+    <t>1 ???</t>
+  </si>
+  <si>
+    <t>1 Pyromancer + 1000 cost</t>
+  </si>
+  <si>
     <t>Booster Pack - Blightsilver / 9</t>
   </si>
   <si>
@@ -3788,7 +3803,7 @@
     <t>Alarm</t>
   </si>
   <si>
-    <t>Unil the end of this urn, All face-up Anima monster gain +10 DEF</t>
+    <t>Until the end of this urn, All face-up Anima monster gain +10 DEF</t>
   </si>
   <si>
     <t>Protective Instinct</t>
@@ -3819,6 +3834,12 @@
   </si>
   <si>
     <t>If you have 1500 or less crystal, drain crystal from foe until both players have same amount of crystals</t>
+  </si>
+  <si>
+    <t>Tripwire</t>
+  </si>
+  <si>
+    <t>Destroy the attacker with 20 or less ATK. Attacker side pay no cost.</t>
   </si>
   <si>
     <t>Illustration</t>
@@ -7683,7 +7704,7 @@
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
     </row>
-    <row r="38" ht="56.05" customHeight="1">
+    <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="8">
         <v>98</v>
       </c>
@@ -8392,7 +8413,7 @@
       <c r="O54" s="10"/>
       <c r="P54" s="10"/>
     </row>
-    <row r="55" ht="32.05" customHeight="1">
+    <row r="55" ht="44.05" customHeight="1">
       <c r="A55" t="s" s="8">
         <v>127</v>
       </c>
@@ -8461,7 +8482,9 @@
         <v>130</v>
       </c>
       <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
+      <c r="J56" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K56" s="16">
         <f>(D56*6)+(E56*4)</f>
         <v>1280</v>
@@ -8498,7 +8521,9 @@
         <v>39</v>
       </c>
       <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
+      <c r="J57" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K57" s="16">
         <f>(D57*6)+(E57*4)</f>
         <v>160</v>
@@ -8535,7 +8560,9 @@
         <v>39</v>
       </c>
       <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
+      <c r="J58" t="s" s="17">
+        <v>35</v>
+      </c>
       <c r="K58" s="16">
         <f>(D58*6)+(E58*4)</f>
         <v>140</v>
@@ -9506,7 +9533,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" ht="20.05" customHeight="1">
+    <row r="83" ht="32.05" customHeight="1">
       <c r="A83" t="s" s="8">
         <v>171</v>
       </c>
@@ -11095,7 +11122,7 @@
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
     </row>
-    <row r="124" ht="20.05" customHeight="1">
+    <row r="124" ht="32.05" customHeight="1">
       <c r="A124" t="s" s="8">
         <v>246</v>
       </c>
@@ -16596,10 +16623,10 @@
         <v>800</v>
       </c>
       <c r="D266" s="16">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E266" s="16">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F266" t="s" s="17">
         <v>7</v>
@@ -16616,7 +16643,7 @@
       </c>
       <c r="K266" s="16">
         <f>(D266*6)+(E266*4)</f>
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="L266" t="s" s="17">
         <v>35</v>
@@ -25213,7 +25240,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="16">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E19" s="16">
         <v>35</v>
@@ -26601,7 +26628,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="16">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E55" s="16">
         <v>40</v>
@@ -27655,19 +27682,41 @@
       <c r="N85" s="10"/>
       <c r="O85" s="10"/>
     </row>
-    <row r="86" ht="20.05" customHeight="1">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
+    <row r="86" ht="80.05" customHeight="1">
+      <c r="A86" t="s" s="8">
+        <v>1044</v>
+      </c>
+      <c r="B86" t="s" s="9">
+        <v>663</v>
+      </c>
+      <c r="C86" s="16">
+        <v>0</v>
+      </c>
+      <c r="D86" s="16">
+        <v>0</v>
+      </c>
+      <c r="E86" s="16">
+        <v>120</v>
+      </c>
+      <c r="F86" t="s" s="17">
+        <v>7</v>
+      </c>
       <c r="G86" s="10"/>
-      <c r="H86" s="10"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10"/>
+      <c r="H86" t="s" s="17">
+        <v>1045</v>
+      </c>
+      <c r="I86" t="s" s="17">
+        <v>1046</v>
+      </c>
+      <c r="J86" t="s" s="17">
+        <v>1047</v>
+      </c>
+      <c r="K86" t="s" s="17">
+        <v>1048</v>
+      </c>
+      <c r="L86" t="s" s="17">
+        <v>971</v>
+      </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10"/>
       <c r="O86" s="10"/>
@@ -35685,23 +35734,23 @@
       </c>
       <c r="N2" t="s" s="3">
         <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N545,"Yes")</f>
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="O2" t="s" s="3">
         <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O545,"Yes")</f>
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="P2" t="s" s="3">
         <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P545,"Yes")</f>
-        <v>1046</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="3" ht="44.25" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C3" s="14">
         <v>0</v>
@@ -35713,7 +35762,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" t="s" s="15">
@@ -35732,10 +35781,10 @@
     </row>
     <row r="4" ht="44.05" customHeight="1">
       <c r="A4" t="s" s="8">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C4" s="16">
         <v>200</v>
@@ -35747,7 +35796,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="s" s="17">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" t="s" s="17">
@@ -35766,10 +35815,10 @@
     </row>
     <row r="5" ht="44.05" customHeight="1">
       <c r="A5" t="s" s="8">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -35781,7 +35830,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s" s="17">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" t="s" s="17">
@@ -35800,10 +35849,10 @@
     </row>
     <row r="6" ht="44.05" customHeight="1">
       <c r="A6" t="s" s="8">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -35815,7 +35864,7 @@
         <v>2</v>
       </c>
       <c r="H6" t="s" s="17">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" t="s" s="17">
@@ -35834,10 +35883,10 @@
     </row>
     <row r="7" ht="32.05" customHeight="1">
       <c r="A7" t="s" s="8">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C7" s="16">
         <v>500</v>
@@ -35849,7 +35898,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s" s="17">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" t="s" s="17">
@@ -35868,10 +35917,10 @@
     </row>
     <row r="8" ht="44.05" customHeight="1">
       <c r="A8" t="s" s="8">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
@@ -35883,7 +35932,7 @@
         <v>5</v>
       </c>
       <c r="H8" t="s" s="17">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" t="s" s="17">
@@ -35902,10 +35951,10 @@
     </row>
     <row r="9" ht="32.05" customHeight="1">
       <c r="A9" t="s" s="8">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C9" s="16">
         <v>800</v>
@@ -35917,7 +35966,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="17">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" t="s" s="17">
@@ -35936,10 +35985,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="8">
-        <v>1062</v>
+        <v>1067</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C10" s="16">
         <v>250</v>
@@ -35951,7 +36000,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="17">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" t="s" s="17">
@@ -35970,10 +36019,10 @@
     </row>
     <row r="11" ht="32.05" customHeight="1">
       <c r="A11" t="s" s="8">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C11" s="16">
         <v>1000</v>
@@ -35985,7 +36034,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="17">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" t="s" s="17">
@@ -36004,10 +36053,10 @@
     </row>
     <row r="12" ht="44.05" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C12" s="16">
         <v>200</v>
@@ -36019,7 +36068,7 @@
         <v>2</v>
       </c>
       <c r="H12" t="s" s="17">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" t="s" s="17">
@@ -36034,10 +36083,10 @@
     </row>
     <row r="13" ht="32.05" customHeight="1">
       <c r="A13" t="s" s="8">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C13" s="16">
         <v>500</v>
@@ -36049,7 +36098,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="s" s="17">
-        <v>1069</v>
+        <v>1074</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" t="s" s="17">
@@ -36068,10 +36117,10 @@
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" t="s" s="8">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C14" s="16">
         <v>1500</v>
@@ -36083,7 +36132,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="17">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" t="s" s="17">
@@ -36102,10 +36151,10 @@
     </row>
     <row r="15" ht="32.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C15" s="16">
         <v>500</v>
@@ -36117,7 +36166,7 @@
         <v>4</v>
       </c>
       <c r="H15" t="s" s="17">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" t="s" s="17">
@@ -36136,10 +36185,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C16" s="16">
         <v>1500</v>
@@ -36151,7 +36200,7 @@
         <v>5</v>
       </c>
       <c r="H16" t="s" s="17">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" t="s" s="17">
@@ -36170,10 +36219,10 @@
     </row>
     <row r="17" ht="44.05" customHeight="1">
       <c r="A17" t="s" s="8">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C17" s="16">
         <v>900</v>
@@ -36185,7 +36234,7 @@
         <v>4</v>
       </c>
       <c r="H17" t="s" s="17">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" t="s" s="17">
@@ -36204,10 +36253,10 @@
     </row>
     <row r="18" ht="44.05" customHeight="1">
       <c r="A18" t="s" s="8">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
@@ -36219,7 +36268,7 @@
         <v>3</v>
       </c>
       <c r="H18" t="s" s="17">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" t="s" s="17">
@@ -36238,10 +36287,10 @@
     </row>
     <row r="19" ht="44.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C19" s="16">
         <v>800</v>
@@ -36253,7 +36302,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="17">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" t="s" s="17">
@@ -36268,10 +36317,10 @@
     </row>
     <row r="20" ht="44.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="B20" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C20" s="16">
         <v>600</v>
@@ -36283,7 +36332,7 @@
         <v>4</v>
       </c>
       <c r="H20" t="s" s="17">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" t="s" s="17">
@@ -36298,10 +36347,10 @@
     </row>
     <row r="21" ht="44.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="B21" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C21" s="16">
         <v>0</v>
@@ -36313,7 +36362,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s" s="17">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" t="s" s="17">
@@ -36332,10 +36381,10 @@
     </row>
     <row r="22" ht="44.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="B22" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C22" s="16">
         <v>50</v>
@@ -36347,7 +36396,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s" s="17">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" t="s" s="17">
@@ -36362,10 +36411,10 @@
     </row>
     <row r="23" ht="32.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="B23" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C23" s="16">
         <v>100</v>
@@ -36377,7 +36426,7 @@
         <v>3</v>
       </c>
       <c r="H23" t="s" s="17">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" t="s" s="17">
@@ -36392,10 +36441,10 @@
     </row>
     <row r="24" ht="44.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="B24" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C24" s="16">
         <v>1000</v>
@@ -36407,7 +36456,7 @@
         <v>5</v>
       </c>
       <c r="H24" t="s" s="17">
-        <v>1091</v>
+        <v>1096</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" t="s" s="17">
@@ -36422,10 +36471,10 @@
     </row>
     <row r="25" ht="44.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C25" s="16">
         <v>850</v>
@@ -36437,7 +36486,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s" s="17">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" t="s" s="17">
@@ -36452,10 +36501,10 @@
     </row>
     <row r="26" ht="32.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>1094</v>
+        <v>1099</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C26" s="16">
         <v>600</v>
@@ -36467,7 +36516,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s" s="17">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" t="s" s="17">
@@ -36482,10 +36531,10 @@
     </row>
     <row r="27" ht="44.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>1096</v>
+        <v>1101</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C27" s="16">
         <v>600</v>
@@ -36497,7 +36546,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="17">
-        <v>1097</v>
+        <v>1102</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" t="s" s="17">
@@ -36512,10 +36561,10 @@
     </row>
     <row r="28" ht="44.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C28" s="16">
         <v>600</v>
@@ -36527,7 +36576,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s" s="17">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" t="s" s="17">
@@ -36542,10 +36591,10 @@
     </row>
     <row r="29" ht="32.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C29" s="16">
         <v>600</v>
@@ -36557,7 +36606,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s" s="17">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" t="s" s="17">
@@ -36572,10 +36621,10 @@
     </row>
     <row r="30" ht="44.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C30" s="16">
         <v>600</v>
@@ -36587,7 +36636,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s" s="17">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" t="s" s="17">
@@ -36602,10 +36651,10 @@
     </row>
     <row r="31" ht="44.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C31" s="16">
         <v>600</v>
@@ -36617,7 +36666,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s" s="17">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" t="s" s="17">
@@ -36632,10 +36681,10 @@
     </row>
     <row r="32" ht="44.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C32" s="16">
         <v>600</v>
@@ -36647,7 +36696,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s" s="17">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" t="s" s="17">
@@ -36662,10 +36711,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C33" s="16">
         <v>300</v>
@@ -36677,7 +36726,7 @@
         <v>2</v>
       </c>
       <c r="H33" t="s" s="17">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" t="s" s="17">
@@ -36692,10 +36741,10 @@
     </row>
     <row r="34" ht="44.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C34" s="16">
         <v>800</v>
@@ -36707,7 +36756,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="17">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" t="s" s="17">
@@ -36722,10 +36771,10 @@
     </row>
     <row r="35" ht="56.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C35" s="16">
         <v>800</v>
@@ -36737,7 +36786,7 @@
         <v>3</v>
       </c>
       <c r="H35" t="s" s="17">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" t="s" s="17">
@@ -36752,10 +36801,10 @@
     </row>
     <row r="36" ht="44.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C36" s="16">
         <v>800</v>
@@ -36767,7 +36816,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="17">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" t="s" s="17">
@@ -36782,10 +36831,10 @@
     </row>
     <row r="37" ht="44.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="B37" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C37" s="16">
         <v>800</v>
@@ -36797,7 +36846,7 @@
         <v>3</v>
       </c>
       <c r="H37" t="s" s="17">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" t="s" s="17">
@@ -36812,10 +36861,10 @@
     </row>
     <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="B38" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C38" s="16">
         <v>800</v>
@@ -36827,7 +36876,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="17">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" t="s" s="17">
@@ -36842,10 +36891,10 @@
     </row>
     <row r="39" ht="56.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="B39" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C39" s="16">
         <v>800</v>
@@ -36857,7 +36906,7 @@
         <v>3</v>
       </c>
       <c r="H39" t="s" s="17">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" t="s" s="17">
@@ -36872,10 +36921,10 @@
     </row>
     <row r="40" ht="56.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="B40" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C40" s="16">
         <v>800</v>
@@ -36887,7 +36936,7 @@
         <v>3</v>
       </c>
       <c r="H40" t="s" s="17">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" t="s" s="17">
@@ -36902,10 +36951,10 @@
     </row>
     <row r="41" ht="44.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C41" s="16">
         <v>1200</v>
@@ -36917,7 +36966,7 @@
         <v>3</v>
       </c>
       <c r="H41" t="s" s="17">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" t="s" s="17">
@@ -36932,10 +36981,10 @@
     </row>
     <row r="42" ht="44.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C42" s="16">
         <v>1500</v>
@@ -36947,7 +36996,7 @@
         <v>4</v>
       </c>
       <c r="H42" t="s" s="17">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" t="s" s="17">
@@ -36962,10 +37011,10 @@
     </row>
     <row r="43" ht="44.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C43" s="16">
         <v>100</v>
@@ -36977,7 +37026,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="17">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" t="s" s="17">
@@ -36996,10 +37045,10 @@
     </row>
     <row r="44" ht="32.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C44" s="16">
         <v>700</v>
@@ -37011,7 +37060,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="17">
-        <v>1131</v>
+        <v>1136</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" t="s" s="17">
@@ -37030,10 +37079,10 @@
     </row>
     <row r="45" ht="32.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C45" s="16">
         <v>1200</v>
@@ -37045,7 +37094,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s" s="17">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -37058,10 +37107,10 @@
     </row>
     <row r="46" ht="32.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C46" s="16">
         <v>1500</v>
@@ -37073,7 +37122,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="17">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -37086,10 +37135,10 @@
     </row>
     <row r="47" ht="32.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C47" s="16">
         <v>950</v>
@@ -37101,7 +37150,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="17">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -37114,10 +37163,10 @@
     </row>
     <row r="48" ht="44.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C48" s="16">
         <v>0</v>
@@ -37129,7 +37178,7 @@
         <v>3</v>
       </c>
       <c r="H48" t="s" s="17">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -37142,10 +37191,10 @@
     </row>
     <row r="49" ht="68.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>1140</v>
+        <v>1145</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C49" s="16">
         <v>2000</v>
@@ -37157,7 +37206,7 @@
         <v>5</v>
       </c>
       <c r="H49" t="s" s="17">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
@@ -37170,10 +37219,10 @@
     </row>
     <row r="50" ht="44.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C50" s="16">
         <v>100</v>
@@ -37185,7 +37234,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="17">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
@@ -37198,7 +37247,7 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>1144</v>
+        <v>1149</v>
       </c>
       <c r="B51" s="12"/>
       <c r="C51" s="16">
@@ -37211,7 +37260,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="17">
-        <v>1145</v>
+        <v>1150</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
@@ -37224,10 +37273,10 @@
     </row>
     <row r="52" ht="32.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C52" s="16">
         <v>0</v>
@@ -37239,7 +37288,7 @@
         <v>2</v>
       </c>
       <c r="H52" t="s" s="17">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" t="s" s="17">
@@ -37258,7 +37307,7 @@
     </row>
     <row r="53" ht="32.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>1148</v>
+        <v>1153</v>
       </c>
       <c r="B53" s="12"/>
       <c r="C53" s="16">
@@ -37271,7 +37320,7 @@
         <v>2</v>
       </c>
       <c r="H53" t="s" s="17">
-        <v>1149</v>
+        <v>1154</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
@@ -37284,7 +37333,7 @@
     </row>
     <row r="54" ht="32.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="B54" s="12"/>
       <c r="C54" s="16">
@@ -37297,7 +37346,7 @@
         <v>3</v>
       </c>
       <c r="H54" t="s" s="17">
-        <v>1151</v>
+        <v>1156</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
@@ -37310,10 +37359,10 @@
     </row>
     <row r="55" ht="32.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="B55" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C55" s="16">
         <v>0</v>
@@ -37325,7 +37374,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="s" s="17">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" t="s" s="17">
@@ -37344,10 +37393,10 @@
     </row>
     <row r="56" ht="44.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C56" s="16">
         <v>0</v>
@@ -37359,7 +37408,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="s" s="17">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" t="s" s="17">
@@ -37378,7 +37427,7 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="B57" s="12"/>
       <c r="C57" s="16">
@@ -37391,7 +37440,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="s" s="17">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
@@ -37404,10 +37453,10 @@
     </row>
     <row r="58" ht="44.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C58" s="16">
         <v>0</v>
@@ -37419,7 +37468,7 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="17">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" t="s" s="17">
@@ -37438,7 +37487,7 @@
     </row>
     <row r="59" ht="44.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="16">
@@ -37451,7 +37500,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="17">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
@@ -37464,10 +37513,10 @@
     </row>
     <row r="60" ht="56.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="C60" s="16">
         <v>0</v>
@@ -37479,7 +37528,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="s" s="17">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" t="s" s="17">
@@ -37498,7 +37547,7 @@
     </row>
     <row r="61" ht="56.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="B61" s="12"/>
       <c r="C61" s="16">
@@ -37511,7 +37560,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="17">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -37522,15 +37571,21 @@
       <c r="O61" s="10"/>
       <c r="P61" s="10"/>
     </row>
-    <row r="62" ht="20.05" customHeight="1">
-      <c r="A62" s="11"/>
+    <row r="62" ht="44.05" customHeight="1">
+      <c r="A62" t="s" s="8">
+        <v>1171</v>
+      </c>
       <c r="B62" s="12"/>
-      <c r="C62" s="10"/>
+      <c r="C62" s="16">
+        <v>300</v>
+      </c>
       <c r="D62" s="10"/>
       <c r="E62" s="10"/>
       <c r="F62" s="10"/>
       <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
+      <c r="H62" t="s" s="17">
+        <v>1172</v>
+      </c>
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
@@ -46312,7 +46367,7 @@
         <v>24</v>
       </c>
       <c r="J2" t="s" s="3">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="K2" t="s" s="3">
         <v>26</v>
@@ -46325,23 +46380,23 @@
       </c>
       <c r="N2" t="s" s="3">
         <f>"Booster Pack - Blightsilver / "&amp;COUNTIF(N3:N556,"Yes")</f>
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="O2" t="s" s="3">
         <f>"Booster Pack - Unseen Presence / "&amp;COUNTIF(O3:O556,"Yes")</f>
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="P2" t="s" s="3">
         <f>"Booster Pack - Wind of Dominance / "&amp;COUNTIF(P3:P556,"Yes")</f>
-        <v>1169</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="3" ht="32.25" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C3" s="14">
         <v>0</v>
@@ -46353,7 +46408,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s" s="15">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" t="s" s="15">
@@ -46368,10 +46423,10 @@
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" t="s" s="8">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C4" s="16">
         <v>0</v>
@@ -46383,7 +46438,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s" s="17">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" t="s" s="17">
@@ -46402,10 +46457,10 @@
     </row>
     <row r="5" ht="32.05" customHeight="1">
       <c r="A5" t="s" s="8">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -46417,7 +46472,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="s" s="17">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" t="s" s="17">
@@ -46432,10 +46487,10 @@
     </row>
     <row r="6" ht="80.05" customHeight="1">
       <c r="A6" t="s" s="8">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C6" s="16">
         <v>0</v>
@@ -46447,7 +46502,7 @@
         <v>5</v>
       </c>
       <c r="H6" t="s" s="17">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" t="s" s="17">
@@ -46462,10 +46517,10 @@
     </row>
     <row r="7" ht="56.05" customHeight="1">
       <c r="A7" t="s" s="8">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C7" s="16">
         <v>0</v>
@@ -46477,7 +46532,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s" s="17">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" t="s" s="17">
@@ -46492,10 +46547,10 @@
     </row>
     <row r="8" ht="56.05" customHeight="1">
       <c r="A8" t="s" s="8">
-        <v>1181</v>
+        <v>1188</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
@@ -46507,7 +46562,7 @@
         <v>3</v>
       </c>
       <c r="H8" t="s" s="17">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" t="s" s="17">
@@ -46522,10 +46577,10 @@
     </row>
     <row r="9" ht="56.05" customHeight="1">
       <c r="A9" t="s" s="8">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C9" s="16">
         <v>0</v>
@@ -46537,7 +46592,7 @@
         <v>4</v>
       </c>
       <c r="H9" t="s" s="17">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" t="s" s="17">
@@ -46552,10 +46607,10 @@
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="A10" t="s" s="8">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C10" s="16">
         <v>0</v>
@@ -46567,7 +46622,7 @@
         <v>2</v>
       </c>
       <c r="H10" t="s" s="17">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" t="s" s="17">
@@ -46586,10 +46641,10 @@
     </row>
     <row r="11" ht="44.05" customHeight="1">
       <c r="A11" t="s" s="8">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C11" s="16">
         <v>0</v>
@@ -46601,7 +46656,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s" s="17">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" t="s" s="17">
@@ -46620,10 +46675,10 @@
     </row>
     <row r="12" ht="44.05" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C12" s="16">
         <v>0</v>
@@ -46635,7 +46690,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s" s="17">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" t="s" s="17">
@@ -46654,10 +46709,10 @@
     </row>
     <row r="13" ht="44.05" customHeight="1">
       <c r="A13" t="s" s="8">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C13" s="16">
         <v>0</v>
@@ -46669,7 +46724,7 @@
         <v>4</v>
       </c>
       <c r="H13" t="s" s="17">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" t="s" s="17">
@@ -46688,10 +46743,10 @@
     </row>
     <row r="14" ht="56.05" customHeight="1">
       <c r="A14" t="s" s="8">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C14" s="16">
         <v>3000</v>
@@ -46703,7 +46758,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s" s="17">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" t="s" s="17">
@@ -46718,10 +46773,10 @@
     </row>
     <row r="15" ht="56.05" customHeight="1">
       <c r="A15" t="s" s="8">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C15" s="16">
         <v>2000</v>
@@ -46733,7 +46788,7 @@
         <v>3</v>
       </c>
       <c r="H15" t="s" s="17">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" t="s" s="17">
@@ -46748,10 +46803,10 @@
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="A16" t="s" s="8">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C16" s="16">
         <v>1000</v>
@@ -46763,7 +46818,7 @@
         <v>4</v>
       </c>
       <c r="H16" t="s" s="17">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" t="s" s="17">
@@ -46782,10 +46837,10 @@
     </row>
     <row r="17" ht="32.05" customHeight="1">
       <c r="A17" t="s" s="8">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C17" s="16">
         <v>1000</v>
@@ -46797,7 +46852,7 @@
         <v>3</v>
       </c>
       <c r="H17" t="s" s="17">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" t="s" s="17">
@@ -46816,10 +46871,10 @@
     </row>
     <row r="18" ht="56.05" customHeight="1">
       <c r="A18" t="s" s="8">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C18" s="16">
         <v>500</v>
@@ -46831,7 +46886,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="s" s="17">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" t="s" s="17">
@@ -46846,10 +46901,10 @@
     </row>
     <row r="19" ht="32.05" customHeight="1">
       <c r="A19" t="s" s="8">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C19" s="16">
         <v>1000</v>
@@ -46861,7 +46916,7 @@
         <v>4</v>
       </c>
       <c r="H19" t="s" s="17">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" t="s" s="17">
@@ -46876,10 +46931,10 @@
     </row>
     <row r="20" ht="56.05" customHeight="1">
       <c r="A20" t="s" s="8">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="B20" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C20" s="16">
         <v>600</v>
@@ -46891,7 +46946,7 @@
         <v>3</v>
       </c>
       <c r="H20" t="s" s="17">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" t="s" s="17">
@@ -46906,10 +46961,10 @@
     </row>
     <row r="21" ht="32.05" customHeight="1">
       <c r="A21" t="s" s="8">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="B21" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C21" s="16">
         <v>1500</v>
@@ -46921,7 +46976,7 @@
         <v>4</v>
       </c>
       <c r="H21" t="s" s="17">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" t="s" s="17">
@@ -46936,10 +46991,10 @@
     </row>
     <row r="22" ht="44.05" customHeight="1">
       <c r="A22" t="s" s="8">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="B22" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C22" s="16">
         <v>850</v>
@@ -46951,7 +47006,7 @@
         <v>3</v>
       </c>
       <c r="H22" t="s" s="17">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" t="s" s="17">
@@ -46966,10 +47021,10 @@
     </row>
     <row r="23" ht="44.05" customHeight="1">
       <c r="A23" t="s" s="8">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="B23" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C23" s="16">
         <v>1000</v>
@@ -46981,7 +47036,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="s" s="17">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" t="s" s="17">
@@ -47000,10 +47055,10 @@
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" t="s" s="8">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="B24" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C24" s="16">
         <v>2000</v>
@@ -47015,7 +47070,7 @@
         <v>4</v>
       </c>
       <c r="H24" t="s" s="17">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" t="s" s="17">
@@ -47030,10 +47085,10 @@
     </row>
     <row r="25" ht="56.05" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="B25" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C25" s="16">
         <v>1000</v>
@@ -47045,7 +47100,7 @@
         <v>3</v>
       </c>
       <c r="H25" t="s" s="17">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" t="s" s="17">
@@ -47064,10 +47119,10 @@
     </row>
     <row r="26" ht="80.05" customHeight="1">
       <c r="A26" t="s" s="8">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="B26" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C26" s="16">
         <v>2000</v>
@@ -47079,7 +47134,7 @@
         <v>5</v>
       </c>
       <c r="H26" t="s" s="17">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" t="s" s="17">
@@ -47094,10 +47149,10 @@
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" t="s" s="8">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="B27" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C27" s="16">
         <v>600</v>
@@ -47109,7 +47164,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s" s="17">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" t="s" s="17">
@@ -47128,10 +47183,10 @@
     </row>
     <row r="28" ht="44.05" customHeight="1">
       <c r="A28" t="s" s="8">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="B28" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C28" s="16">
         <v>500</v>
@@ -47143,7 +47198,7 @@
         <v>2</v>
       </c>
       <c r="H28" t="s" s="17">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" t="s" s="17">
@@ -47158,10 +47213,10 @@
     </row>
     <row r="29" ht="80.05" customHeight="1">
       <c r="A29" t="s" s="8">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="B29" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C29" s="16">
         <v>700</v>
@@ -47173,7 +47228,7 @@
         <v>5</v>
       </c>
       <c r="H29" t="s" s="17">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" t="s" s="17">
@@ -47188,10 +47243,10 @@
     </row>
     <row r="30" ht="80.05" customHeight="1">
       <c r="A30" t="s" s="8">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="B30" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C30" s="16">
         <v>1200</v>
@@ -47203,7 +47258,7 @@
         <v>4</v>
       </c>
       <c r="H30" t="s" s="17">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" t="s" s="17">
@@ -47218,10 +47273,10 @@
     </row>
     <row r="31" ht="68.05" customHeight="1">
       <c r="A31" t="s" s="8">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="B31" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C31" s="16">
         <v>1000</v>
@@ -47233,7 +47288,7 @@
         <v>5</v>
       </c>
       <c r="H31" t="s" s="17">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" t="s" s="17">
@@ -47248,10 +47303,10 @@
     </row>
     <row r="32" ht="56.05" customHeight="1">
       <c r="A32" t="s" s="8">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="B32" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C32" s="16">
         <v>1800</v>
@@ -47263,7 +47318,7 @@
         <v>5</v>
       </c>
       <c r="H32" t="s" s="17">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" t="s" s="17">
@@ -47278,10 +47333,10 @@
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="A33" t="s" s="8">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="B33" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C33" s="16">
         <v>1500</v>
@@ -47293,7 +47348,7 @@
         <v>4</v>
       </c>
       <c r="H33" t="s" s="17">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" t="s" s="17">
@@ -47312,10 +47367,10 @@
     </row>
     <row r="34" ht="44.05" customHeight="1">
       <c r="A34" t="s" s="8">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="B34" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C34" s="16">
         <v>1000</v>
@@ -47327,7 +47382,7 @@
         <v>3</v>
       </c>
       <c r="H34" t="s" s="17">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
@@ -47340,10 +47395,10 @@
     </row>
     <row r="35" ht="44.05" customHeight="1">
       <c r="A35" t="s" s="8">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="B35" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C35" s="16">
         <v>600</v>
@@ -47355,7 +47410,7 @@
         <v>2</v>
       </c>
       <c r="H35" t="s" s="17">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
@@ -47368,10 +47423,10 @@
     </row>
     <row r="36" ht="56.05" customHeight="1">
       <c r="A36" t="s" s="8">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="B36" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C36" s="16">
         <v>250</v>
@@ -47383,7 +47438,7 @@
         <v>3</v>
       </c>
       <c r="H36" t="s" s="17">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
@@ -47396,10 +47451,10 @@
     </row>
     <row r="37" ht="32.05" customHeight="1">
       <c r="A37" t="s" s="8">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="B37" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C37" s="16">
         <v>300</v>
@@ -47411,7 +47466,7 @@
         <v>2</v>
       </c>
       <c r="H37" t="s" s="17">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -47424,10 +47479,10 @@
     </row>
     <row r="38" ht="44.05" customHeight="1">
       <c r="A38" t="s" s="8">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B38" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C38" s="16">
         <v>1000</v>
@@ -47439,7 +47494,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s" s="17">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -47452,10 +47507,10 @@
     </row>
     <row r="39" ht="32.05" customHeight="1">
       <c r="A39" t="s" s="8">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="B39" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C39" s="16">
         <v>1200</v>
@@ -47467,7 +47522,7 @@
         <v>4</v>
       </c>
       <c r="H39" t="s" s="17">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -47480,10 +47535,10 @@
     </row>
     <row r="40" ht="20.05" customHeight="1">
       <c r="A40" t="s" s="8">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B40" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C40" s="16">
         <v>0</v>
@@ -47495,7 +47550,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="s" s="17">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
@@ -47508,10 +47563,10 @@
     </row>
     <row r="41" ht="32.05" customHeight="1">
       <c r="A41" t="s" s="8">
-        <v>1247</v>
+        <v>1254</v>
       </c>
       <c r="B41" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C41" s="16">
         <v>0</v>
@@ -47523,7 +47578,7 @@
         <v>2</v>
       </c>
       <c r="H41" t="s" s="17">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
@@ -47536,10 +47591,10 @@
     </row>
     <row r="42" ht="32.05" customHeight="1">
       <c r="A42" t="s" s="8">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="B42" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C42" s="16">
         <v>0</v>
@@ -47551,7 +47606,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s" s="17">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -47564,10 +47619,10 @@
     </row>
     <row r="43" ht="32.05" customHeight="1">
       <c r="A43" t="s" s="8">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="B43" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C43" s="16">
         <v>0</v>
@@ -47579,7 +47634,7 @@
         <v>2</v>
       </c>
       <c r="H43" t="s" s="17">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
@@ -47592,10 +47647,10 @@
     </row>
     <row r="44" ht="20.05" customHeight="1">
       <c r="A44" t="s" s="8">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="B44" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C44" s="16">
         <v>0</v>
@@ -47607,7 +47662,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s" s="17">
-        <v>1254</v>
+        <v>1261</v>
       </c>
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
@@ -47620,10 +47675,10 @@
     </row>
     <row r="45" ht="56.05" customHeight="1">
       <c r="A45" t="s" s="8">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="B45" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C45" s="16">
         <v>0</v>
@@ -47635,7 +47690,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s" s="17">
-        <v>1256</v>
+        <v>1263</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
@@ -47648,10 +47703,10 @@
     </row>
     <row r="46" ht="44.05" customHeight="1">
       <c r="A46" t="s" s="8">
-        <v>1257</v>
+        <v>1264</v>
       </c>
       <c r="B46" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C46" s="16">
         <v>0</v>
@@ -47663,7 +47718,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s" s="17">
-        <v>1258</v>
+        <v>1265</v>
       </c>
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
@@ -47676,10 +47731,10 @@
     </row>
     <row r="47" ht="44.05" customHeight="1">
       <c r="A47" t="s" s="8">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="B47" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C47" s="16">
         <v>0</v>
@@ -47691,7 +47746,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s" s="17">
-        <v>1260</v>
+        <v>1267</v>
       </c>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
@@ -47704,10 +47759,10 @@
     </row>
     <row r="48" ht="56.05" customHeight="1">
       <c r="A48" t="s" s="8">
-        <v>1261</v>
+        <v>1268</v>
       </c>
       <c r="B48" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C48" s="16">
         <v>500</v>
@@ -47719,7 +47774,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="s" s="17">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
@@ -47732,10 +47787,10 @@
     </row>
     <row r="49" ht="32.05" customHeight="1">
       <c r="A49" t="s" s="8">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="B49" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C49" s="16">
         <v>0</v>
@@ -47747,7 +47802,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s" s="17">
-        <v>1264</v>
+        <v>1271</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
@@ -47760,10 +47815,10 @@
     </row>
     <row r="50" ht="32.05" customHeight="1">
       <c r="A50" t="s" s="8">
-        <v>1265</v>
+        <v>1272</v>
       </c>
       <c r="B50" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C50" s="16">
         <v>600</v>
@@ -47775,7 +47830,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s" s="17">
-        <v>1266</v>
+        <v>1273</v>
       </c>
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
@@ -47788,10 +47843,10 @@
     </row>
     <row r="51" ht="44.05" customHeight="1">
       <c r="A51" t="s" s="8">
-        <v>1267</v>
+        <v>1274</v>
       </c>
       <c r="B51" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C51" s="16">
         <v>0</v>
@@ -47803,7 +47858,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s" s="17">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
@@ -47816,10 +47871,10 @@
     </row>
     <row r="52" ht="68.05" customHeight="1">
       <c r="A52" t="s" s="8">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="B52" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C52" s="16">
         <v>200</v>
@@ -47831,7 +47886,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s" s="17">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
@@ -47844,10 +47899,10 @@
     </row>
     <row r="53" ht="68.05" customHeight="1">
       <c r="A53" t="s" s="8">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="B53" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C53" s="16">
         <v>200</v>
@@ -47859,7 +47914,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="s" s="17">
-        <v>1272</v>
+        <v>1279</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
@@ -47872,10 +47927,10 @@
     </row>
     <row r="54" ht="80.05" customHeight="1">
       <c r="A54" t="s" s="8">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="B54" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C54" s="16">
         <v>600</v>
@@ -47887,7 +47942,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s" s="17">
-        <v>1274</v>
+        <v>1281</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
@@ -47900,10 +47955,10 @@
     </row>
     <row r="55" ht="68.05" customHeight="1">
       <c r="A55" t="s" s="8">
-        <v>1275</v>
+        <v>1282</v>
       </c>
       <c r="B55" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C55" s="16">
         <v>500</v>
@@ -47915,7 +47970,7 @@
         <v>2</v>
       </c>
       <c r="H55" t="s" s="17">
-        <v>1276</v>
+        <v>1283</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
@@ -47928,10 +47983,10 @@
     </row>
     <row r="56" ht="44.05" customHeight="1">
       <c r="A56" t="s" s="8">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="B56" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C56" s="16">
         <v>900</v>
@@ -47943,7 +47998,7 @@
         <v>2</v>
       </c>
       <c r="H56" t="s" s="17">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
@@ -47956,10 +48011,10 @@
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="A57" t="s" s="8">
-        <v>1279</v>
+        <v>1286</v>
       </c>
       <c r="B57" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C57" s="16">
         <v>0</v>
@@ -47971,7 +48026,7 @@
         <v>2</v>
       </c>
       <c r="H57" t="s" s="17">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
@@ -47984,10 +48039,10 @@
     </row>
     <row r="58" ht="56.05" customHeight="1">
       <c r="A58" t="s" s="8">
-        <v>1281</v>
+        <v>1288</v>
       </c>
       <c r="B58" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C58" s="16">
         <v>450</v>
@@ -47999,7 +48054,7 @@
         <v>2</v>
       </c>
       <c r="H58" t="s" s="17">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
@@ -48012,10 +48067,10 @@
     </row>
     <row r="59" ht="68.05" customHeight="1">
       <c r="A59" t="s" s="8">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="B59" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C59" s="16">
         <v>450</v>
@@ -48027,7 +48082,7 @@
         <v>2</v>
       </c>
       <c r="H59" t="s" s="17">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
@@ -48040,10 +48095,10 @@
     </row>
     <row r="60" ht="44.05" customHeight="1">
       <c r="A60" t="s" s="8">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="B60" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C60" s="16">
         <v>200</v>
@@ -48055,7 +48110,7 @@
         <v>4</v>
       </c>
       <c r="H60" t="s" s="17">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
@@ -48068,10 +48123,10 @@
     </row>
     <row r="61" ht="32.05" customHeight="1">
       <c r="A61" t="s" s="8">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="B61" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C61" s="16">
         <v>1200</v>
@@ -48083,7 +48138,7 @@
         <v>5</v>
       </c>
       <c r="H61" t="s" s="17">
-        <v>1288</v>
+        <v>1295</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -48096,10 +48151,10 @@
     </row>
     <row r="62" ht="44.05" customHeight="1">
       <c r="A62" t="s" s="8">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="B62" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C62" s="16">
         <v>0</v>
@@ -48111,7 +48166,7 @@
         <v>2</v>
       </c>
       <c r="H62" t="s" s="17">
-        <v>1290</v>
+        <v>1297</v>
       </c>
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
@@ -48124,10 +48179,10 @@
     </row>
     <row r="63" ht="32.05" customHeight="1">
       <c r="A63" t="s" s="8">
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="B63" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C63" s="16">
         <v>0</v>
@@ -48139,7 +48194,7 @@
         <v>4</v>
       </c>
       <c r="H63" t="s" s="17">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
@@ -48152,10 +48207,10 @@
     </row>
     <row r="64" ht="32.05" customHeight="1">
       <c r="A64" t="s" s="8">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="B64" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C64" s="16">
         <v>0</v>
@@ -48167,7 +48222,7 @@
         <v>4</v>
       </c>
       <c r="H64" t="s" s="17">
-        <v>1294</v>
+        <v>1301</v>
       </c>
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
@@ -48180,10 +48235,10 @@
     </row>
     <row r="65" ht="80.05" customHeight="1">
       <c r="A65" t="s" s="8">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="B65" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C65" s="16">
         <v>800</v>
@@ -48195,7 +48250,7 @@
         <v>3</v>
       </c>
       <c r="H65" t="s" s="17">
-        <v>1296</v>
+        <v>1303</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
@@ -48208,10 +48263,10 @@
     </row>
     <row r="66" ht="80.05" customHeight="1">
       <c r="A66" t="s" s="8">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="B66" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C66" s="16">
         <v>800</v>
@@ -48223,7 +48278,7 @@
         <v>2</v>
       </c>
       <c r="H66" t="s" s="17">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
@@ -48236,10 +48291,10 @@
     </row>
     <row r="67" ht="68.05" customHeight="1">
       <c r="A67" t="s" s="8">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="B67" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C67" s="16">
         <v>1000</v>
@@ -48251,7 +48306,7 @@
         <v>5</v>
       </c>
       <c r="H67" t="s" s="17">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
@@ -48264,10 +48319,10 @@
     </row>
     <row r="68" ht="56.05" customHeight="1">
       <c r="A68" t="s" s="8">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="B68" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C68" s="16">
         <v>1500</v>
@@ -48279,7 +48334,7 @@
         <v>3</v>
       </c>
       <c r="H68" t="s" s="17">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
@@ -48292,10 +48347,10 @@
     </row>
     <row r="69" ht="44.05" customHeight="1">
       <c r="A69" t="s" s="8">
-        <v>1303</v>
+        <v>1310</v>
       </c>
       <c r="B69" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C69" s="16">
         <v>1200</v>
@@ -48307,7 +48362,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s" s="17">
-        <v>1304</v>
+        <v>1311</v>
       </c>
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
@@ -48320,10 +48375,10 @@
     </row>
     <row r="70" ht="56.05" customHeight="1">
       <c r="A70" t="s" s="8">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="B70" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C70" s="16">
         <v>300</v>
@@ -48335,7 +48390,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="s" s="17">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
@@ -48348,10 +48403,10 @@
     </row>
     <row r="71" ht="68.05" customHeight="1">
       <c r="A71" t="s" s="8">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="B71" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C71" s="16">
         <v>300</v>
@@ -48363,7 +48418,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="s" s="17">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
@@ -48376,10 +48431,10 @@
     </row>
     <row r="72" ht="68.05" customHeight="1">
       <c r="A72" t="s" s="8">
-        <v>1309</v>
+        <v>1316</v>
       </c>
       <c r="B72" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C72" s="16">
         <v>500</v>
@@ -48391,7 +48446,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s" s="17">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
@@ -48404,10 +48459,10 @@
     </row>
     <row r="73" ht="44.05" customHeight="1">
       <c r="A73" t="s" s="8">
-        <v>1311</v>
+        <v>1318</v>
       </c>
       <c r="B73" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C73" s="16">
         <v>2000</v>
@@ -48419,7 +48474,7 @@
         <v>4</v>
       </c>
       <c r="H73" t="s" s="17">
-        <v>1312</v>
+        <v>1319</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
@@ -48432,10 +48487,10 @@
     </row>
     <row r="74" ht="44.05" customHeight="1">
       <c r="A74" t="s" s="8">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="B74" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C74" s="16">
         <v>2000</v>
@@ -48447,7 +48502,7 @@
         <v>5</v>
       </c>
       <c r="H74" t="s" s="17">
-        <v>1314</v>
+        <v>1321</v>
       </c>
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
@@ -48460,10 +48515,10 @@
     </row>
     <row r="75" ht="44.05" customHeight="1">
       <c r="A75" t="s" s="8">
-        <v>1315</v>
+        <v>1322</v>
       </c>
       <c r="B75" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C75" s="16">
         <v>2000</v>
@@ -48475,7 +48530,7 @@
         <v>5</v>
       </c>
       <c r="H75" t="s" s="17">
-        <v>1316</v>
+        <v>1323</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
@@ -48488,10 +48543,10 @@
     </row>
     <row r="76" ht="44.05" customHeight="1">
       <c r="A76" t="s" s="8">
-        <v>1317</v>
+        <v>1324</v>
       </c>
       <c r="B76" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C76" s="16">
         <v>2000</v>
@@ -48503,7 +48558,7 @@
         <v>5</v>
       </c>
       <c r="H76" t="s" s="17">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
@@ -48516,10 +48571,10 @@
     </row>
     <row r="77" ht="44.05" customHeight="1">
       <c r="A77" t="s" s="8">
-        <v>1319</v>
+        <v>1326</v>
       </c>
       <c r="B77" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C77" s="16">
         <v>2000</v>
@@ -48531,7 +48586,7 @@
         <v>5</v>
       </c>
       <c r="H77" t="s" s="17">
-        <v>1320</v>
+        <v>1327</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
@@ -48544,10 +48599,10 @@
     </row>
     <row r="78" ht="44.05" customHeight="1">
       <c r="A78" t="s" s="8">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="B78" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C78" s="16">
         <v>2000</v>
@@ -48559,7 +48614,7 @@
         <v>5</v>
       </c>
       <c r="H78" t="s" s="17">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
@@ -48572,10 +48627,10 @@
     </row>
     <row r="79" ht="44.05" customHeight="1">
       <c r="A79" t="s" s="8">
-        <v>1323</v>
+        <v>1330</v>
       </c>
       <c r="B79" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C79" s="16">
         <v>2000</v>
@@ -48587,7 +48642,7 @@
         <v>5</v>
       </c>
       <c r="H79" t="s" s="17">
-        <v>1324</v>
+        <v>1331</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
@@ -48600,10 +48655,10 @@
     </row>
     <row r="80" ht="20.05" customHeight="1">
       <c r="A80" t="s" s="8">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="B80" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C80" s="16">
         <v>1200</v>
@@ -48615,7 +48670,7 @@
         <v>4</v>
       </c>
       <c r="H80" t="s" s="17">
-        <v>1326</v>
+        <v>1333</v>
       </c>
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
@@ -48628,10 +48683,10 @@
     </row>
     <row r="81" ht="56.05" customHeight="1">
       <c r="A81" t="s" s="8">
-        <v>1327</v>
+        <v>1334</v>
       </c>
       <c r="B81" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C81" s="16">
         <v>2000</v>
@@ -48643,7 +48698,7 @@
         <v>3</v>
       </c>
       <c r="H81" t="s" s="17">
-        <v>1328</v>
+        <v>1335</v>
       </c>
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
@@ -48656,10 +48711,10 @@
     </row>
     <row r="82" ht="44.05" customHeight="1">
       <c r="A82" t="s" s="8">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="B82" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C82" s="16">
         <v>1000</v>
@@ -48671,7 +48726,7 @@
         <v>3</v>
       </c>
       <c r="H82" t="s" s="17">
-        <v>1330</v>
+        <v>1337</v>
       </c>
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
@@ -48684,10 +48739,10 @@
     </row>
     <row r="83" ht="32.05" customHeight="1">
       <c r="A83" t="s" s="8">
-        <v>1331</v>
+        <v>1338</v>
       </c>
       <c r="B83" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C83" s="16">
         <v>500</v>
@@ -48699,7 +48754,7 @@
         <v>2</v>
       </c>
       <c r="H83" t="s" s="17">
-        <v>1332</v>
+        <v>1339</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
@@ -48712,10 +48767,10 @@
     </row>
     <row r="84" ht="32.05" customHeight="1">
       <c r="A84" t="s" s="8">
-        <v>1333</v>
+        <v>1340</v>
       </c>
       <c r="B84" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C84" s="16">
         <v>250</v>
@@ -48727,7 +48782,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s" s="17">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
@@ -48740,10 +48795,10 @@
     </row>
     <row r="85" ht="80.05" customHeight="1">
       <c r="A85" t="s" s="8">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="B85" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C85" s="16">
         <v>1500</v>
@@ -48755,7 +48810,7 @@
         <v>4</v>
       </c>
       <c r="H85" t="s" s="17">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="10"/>
@@ -48768,10 +48823,10 @@
     </row>
     <row r="86" ht="32.05" customHeight="1">
       <c r="A86" t="s" s="8">
-        <v>1337</v>
+        <v>1344</v>
       </c>
       <c r="B86" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C86" s="16">
         <v>1000</v>
@@ -48783,7 +48838,7 @@
         <v>3</v>
       </c>
       <c r="H86" t="s" s="17">
-        <v>1338</v>
+        <v>1345</v>
       </c>
       <c r="I86" s="10"/>
       <c r="J86" s="10"/>
@@ -48796,10 +48851,10 @@
     </row>
     <row r="87" ht="44.05" customHeight="1">
       <c r="A87" t="s" s="8">
-        <v>1339</v>
+        <v>1346</v>
       </c>
       <c r="B87" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C87" s="16">
         <v>800</v>
@@ -48811,7 +48866,7 @@
         <v>2</v>
       </c>
       <c r="H87" t="s" s="17">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
@@ -48824,10 +48879,10 @@
     </row>
     <row r="88" ht="32.05" customHeight="1">
       <c r="A88" t="s" s="8">
-        <v>1341</v>
+        <v>1348</v>
       </c>
       <c r="B88" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C88" s="16">
         <v>200</v>
@@ -48839,7 +48894,7 @@
         <v>2</v>
       </c>
       <c r="H88" t="s" s="17">
-        <v>1342</v>
+        <v>1349</v>
       </c>
       <c r="I88" s="10"/>
       <c r="J88" s="10"/>
@@ -48852,10 +48907,10 @@
     </row>
     <row r="89" ht="32.05" customHeight="1">
       <c r="A89" t="s" s="8">
-        <v>1343</v>
+        <v>1350</v>
       </c>
       <c r="B89" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C89" s="16">
         <v>1500</v>
@@ -48867,7 +48922,7 @@
         <v>3</v>
       </c>
       <c r="H89" t="s" s="17">
-        <v>1344</v>
+        <v>1351</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="10"/>
@@ -48880,10 +48935,10 @@
     </row>
     <row r="90" ht="32.05" customHeight="1">
       <c r="A90" t="s" s="8">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="B90" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C90" s="16">
         <v>500</v>
@@ -48895,7 +48950,7 @@
         <v>5</v>
       </c>
       <c r="H90" t="s" s="17">
-        <v>1346</v>
+        <v>1353</v>
       </c>
       <c r="I90" s="10"/>
       <c r="J90" s="10"/>
@@ -48908,10 +48963,10 @@
     </row>
     <row r="91" ht="80.05" customHeight="1">
       <c r="A91" t="s" s="8">
-        <v>1347</v>
+        <v>1354</v>
       </c>
       <c r="B91" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C91" s="16">
         <v>1000</v>
@@ -48923,11 +48978,11 @@
         <v>2</v>
       </c>
       <c r="H91" t="s" s="17">
-        <v>1348</v>
+        <v>1355</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" t="s" s="17">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="K91" s="10"/>
       <c r="L91" s="10"/>
@@ -48938,10 +48993,10 @@
     </row>
     <row r="92" ht="56.05" customHeight="1">
       <c r="A92" t="s" s="8">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="B92" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C92" s="16">
         <v>1500</v>
@@ -48953,7 +49008,7 @@
         <v>4</v>
       </c>
       <c r="H92" t="s" s="17">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="I92" s="10"/>
       <c r="J92" s="10"/>
@@ -48966,10 +49021,10 @@
     </row>
     <row r="93" ht="44.05" customHeight="1">
       <c r="A93" t="s" s="8">
-        <v>1352</v>
+        <v>1359</v>
       </c>
       <c r="B93" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C93" s="16">
         <v>300</v>
@@ -48981,7 +49036,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s" s="17">
-        <v>1353</v>
+        <v>1360</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="10"/>
@@ -48994,10 +49049,10 @@
     </row>
     <row r="94" ht="68.05" customHeight="1">
       <c r="A94" t="s" s="8">
-        <v>1354</v>
+        <v>1361</v>
       </c>
       <c r="B94" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C94" s="16">
         <v>200</v>
@@ -49009,7 +49064,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="s" s="17">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="I94" s="10"/>
       <c r="J94" s="10"/>
@@ -49022,10 +49077,10 @@
     </row>
     <row r="95" ht="68.05" customHeight="1">
       <c r="A95" t="s" s="8">
-        <v>1356</v>
+        <v>1363</v>
       </c>
       <c r="B95" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C95" s="16">
         <v>0</v>
@@ -49037,7 +49092,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="s" s="17">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
@@ -49050,10 +49105,10 @@
     </row>
     <row r="96" ht="44.05" customHeight="1">
       <c r="A96" t="s" s="8">
-        <v>1358</v>
+        <v>1365</v>
       </c>
       <c r="B96" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C96" s="16">
         <v>0</v>
@@ -49065,7 +49120,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="s" s="17">
-        <v>1359</v>
+        <v>1366</v>
       </c>
       <c r="I96" s="10"/>
       <c r="J96" s="10"/>
@@ -49078,10 +49133,10 @@
     </row>
     <row r="97" ht="44.05" customHeight="1">
       <c r="A97" t="s" s="8">
-        <v>1360</v>
+        <v>1367</v>
       </c>
       <c r="B97" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C97" s="16">
         <v>1000</v>
@@ -49093,7 +49148,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s" s="17">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
@@ -49106,10 +49161,10 @@
     </row>
     <row r="98" ht="32.05" customHeight="1">
       <c r="A98" t="s" s="8">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="B98" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C98" s="16">
         <v>0</v>
@@ -49121,7 +49176,7 @@
         <v>1</v>
       </c>
       <c r="H98" t="s" s="17">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="I98" s="10"/>
       <c r="J98" s="10"/>
@@ -49134,10 +49189,10 @@
     </row>
     <row r="99" ht="44.05" customHeight="1">
       <c r="A99" t="s" s="8">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="B99" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C99" s="16">
         <v>0</v>
@@ -49149,7 +49204,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="s" s="17">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="10"/>
@@ -49162,10 +49217,10 @@
     </row>
     <row r="100" ht="44.05" customHeight="1">
       <c r="A100" t="s" s="8">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="B100" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C100" s="16">
         <v>500</v>
@@ -49177,7 +49232,7 @@
         <v>2</v>
       </c>
       <c r="H100" t="s" s="17">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="I100" s="10"/>
       <c r="J100" s="10"/>
@@ -49190,10 +49245,10 @@
     </row>
     <row r="101" ht="44.05" customHeight="1">
       <c r="A101" t="s" s="8">
-        <v>1368</v>
+        <v>1375</v>
       </c>
       <c r="B101" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C101" s="16">
         <v>0</v>
@@ -49205,7 +49260,7 @@
         <v>2</v>
       </c>
       <c r="H101" t="s" s="17">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="10"/>
@@ -49218,10 +49273,10 @@
     </row>
     <row r="102" ht="44.05" customHeight="1">
       <c r="A102" t="s" s="8">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="B102" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C102" s="16">
         <v>600</v>
@@ -49233,7 +49288,7 @@
         <v>2</v>
       </c>
       <c r="H102" t="s" s="17">
-        <v>1371</v>
+        <v>1378</v>
       </c>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
@@ -49246,10 +49301,10 @@
     </row>
     <row r="103" ht="92.05" customHeight="1">
       <c r="A103" t="s" s="8">
-        <v>1372</v>
+        <v>1379</v>
       </c>
       <c r="B103" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C103" s="16">
         <v>500</v>
@@ -49261,7 +49316,7 @@
         <v>2</v>
       </c>
       <c r="H103" t="s" s="17">
-        <v>1373</v>
+        <v>1380</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="10"/>
@@ -49274,10 +49329,10 @@
     </row>
     <row r="104" ht="56.05" customHeight="1">
       <c r="A104" t="s" s="8">
-        <v>1374</v>
+        <v>1381</v>
       </c>
       <c r="B104" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C104" s="16">
         <v>2000</v>
@@ -49289,7 +49344,7 @@
         <v>4</v>
       </c>
       <c r="H104" t="s" s="17">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" t="s" s="17">
@@ -49304,10 +49359,10 @@
     </row>
     <row r="105" ht="32.05" customHeight="1">
       <c r="A105" t="s" s="8">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="B105" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C105" s="16">
         <v>1500</v>
@@ -49319,7 +49374,7 @@
         <v>4</v>
       </c>
       <c r="H105" t="s" s="17">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
@@ -49332,10 +49387,10 @@
     </row>
     <row r="106" ht="32.05" customHeight="1">
       <c r="A106" t="s" s="8">
-        <v>1378</v>
+        <v>1385</v>
       </c>
       <c r="B106" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C106" s="16">
         <v>0</v>
@@ -49347,7 +49402,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s" s="17">
-        <v>1379</v>
+        <v>1386</v>
       </c>
       <c r="I106" s="10"/>
       <c r="J106" s="10"/>
@@ -49360,10 +49415,10 @@
     </row>
     <row r="107" ht="68.05" customHeight="1">
       <c r="A107" t="s" s="8">
-        <v>1380</v>
+        <v>1387</v>
       </c>
       <c r="B107" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C107" s="16">
         <v>2000</v>
@@ -49375,7 +49430,7 @@
         <v>3</v>
       </c>
       <c r="H107" t="s" s="17">
-        <v>1381</v>
+        <v>1388</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="10"/>
@@ -49388,10 +49443,10 @@
     </row>
     <row r="108" ht="44.05" customHeight="1">
       <c r="A108" t="s" s="8">
-        <v>1382</v>
+        <v>1389</v>
       </c>
       <c r="B108" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C108" s="16">
         <v>300</v>
@@ -49401,7 +49456,7 @@
       <c r="F108" s="10"/>
       <c r="G108" s="10"/>
       <c r="H108" t="s" s="17">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
@@ -49414,10 +49469,10 @@
     </row>
     <row r="109" ht="56.05" customHeight="1">
       <c r="A109" t="s" s="8">
-        <v>1384</v>
+        <v>1391</v>
       </c>
       <c r="B109" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C109" s="16">
         <v>800</v>
@@ -49427,7 +49482,7 @@
       <c r="F109" s="10"/>
       <c r="G109" s="10"/>
       <c r="H109" t="s" s="17">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
@@ -49440,10 +49495,10 @@
     </row>
     <row r="110" ht="56.05" customHeight="1">
       <c r="A110" t="s" s="8">
-        <v>1386</v>
+        <v>1393</v>
       </c>
       <c r="B110" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C110" s="16">
         <v>600</v>
@@ -49453,7 +49508,7 @@
       <c r="F110" s="10"/>
       <c r="G110" s="10"/>
       <c r="H110" t="s" s="17">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="I110" s="10"/>
       <c r="J110" s="10"/>
@@ -49466,10 +49521,10 @@
     </row>
     <row r="111" ht="56.05" customHeight="1">
       <c r="A111" t="s" s="8">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="B111" t="s" s="9">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="C111" s="16">
         <v>300</v>
@@ -49479,7 +49534,7 @@
       <c r="F111" s="10"/>
       <c r="G111" s="10"/>
       <c r="H111" t="s" s="17">
-        <v>1389</v>
+        <v>1396</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="10"/>
@@ -57539,21 +57594,21 @@
         <v>22</v>
       </c>
       <c r="B2" t="s" s="22">
-        <v>1390</v>
+        <v>1397</v>
       </c>
       <c r="C2" t="s" s="22">
-        <v>1391</v>
+        <v>1398</v>
       </c>
       <c r="D2" t="s" s="22">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="E2" t="s" s="22">
-        <v>1393</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="3" ht="16.55" customHeight="1">
       <c r="A3" t="s" s="23">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="B3" s="24">
         <v>52</v>
@@ -57562,7 +57617,7 @@
         <v>0.347</v>
       </c>
       <c r="D3" t="s" s="26">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="E3" s="27">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,1)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,1)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,1)</f>
@@ -57571,7 +57626,7 @@
     </row>
     <row r="4" ht="16.35" customHeight="1">
       <c r="A4" t="s" s="28">
-        <v>1396</v>
+        <v>1403</v>
       </c>
       <c r="B4" s="29">
         <v>48</v>
@@ -57580,7 +57635,7 @@
         <v>0.337</v>
       </c>
       <c r="D4" t="s" s="31">
-        <v>1397</v>
+        <v>1404</v>
       </c>
       <c r="E4" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,2)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,2)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,2)</f>
@@ -57589,7 +57644,7 @@
     </row>
     <row r="5" ht="16.35" customHeight="1">
       <c r="A5" t="s" s="28">
-        <v>1398</v>
+        <v>1405</v>
       </c>
       <c r="B5" s="29">
         <v>27</v>
@@ -57598,7 +57653,7 @@
         <v>0.167</v>
       </c>
       <c r="D5" t="s" s="31">
-        <v>1397</v>
+        <v>1404</v>
       </c>
       <c r="E5" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,3)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,3)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,3)</f>
@@ -57607,7 +57662,7 @@
     </row>
     <row r="6" ht="30.35" customHeight="1">
       <c r="A6" t="s" s="28">
-        <v>1399</v>
+        <v>1406</v>
       </c>
       <c r="B6" s="29">
         <v>16</v>
@@ -57616,7 +57671,7 @@
         <v>0.1</v>
       </c>
       <c r="D6" t="s" s="31">
-        <v>1400</v>
+        <v>1407</v>
       </c>
       <c r="E6" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,4)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,4)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,4)</f>
@@ -57625,7 +57680,7 @@
     </row>
     <row r="7" ht="16.35" customHeight="1">
       <c r="A7" t="s" s="33">
-        <v>1401</v>
+        <v>1408</v>
       </c>
       <c r="B7" s="34">
         <v>9</v>
@@ -57634,7 +57689,7 @@
         <v>0.053</v>
       </c>
       <c r="D7" t="s" s="31">
-        <v>1402</v>
+        <v>1409</v>
       </c>
       <c r="E7" s="32">
         <f>_xlfn.COUNTIFS('Unit'!$L$3:$L$568,"Yes",'Unit'!$G$3:$G$568,5)+_xlfn.COUNTIFS('Trap'!$L$3:$L$545,"Yes",'Trap'!$G$3:$G$545,5)+_xlfn.COUNTIFS('Tech'!$L$3:$L$556,"Yes",'Tech'!$G$3:$G$556,5)</f>
@@ -57667,17 +57722,17 @@
         <v>22</v>
       </c>
       <c r="B11" t="s" s="41">
-        <v>1390</v>
+        <v>1397</v>
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
       <c r="E11" t="s" s="43">
-        <v>1393</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="12" ht="16.35" customHeight="1">
       <c r="A12" t="s" s="28">
-        <v>1403</v>
+        <v>1410</v>
       </c>
       <c r="B12" s="29">
         <v>60</v>
@@ -57691,7 +57746,7 @@
     </row>
     <row r="13" ht="16.35" customHeight="1">
       <c r="A13" t="s" s="28">
-        <v>1404</v>
+        <v>1411</v>
       </c>
       <c r="B13" s="29">
         <v>60</v>
@@ -57705,7 +57760,7 @@
     </row>
     <row r="14" ht="16.35" customHeight="1">
       <c r="A14" t="s" s="28">
-        <v>1405</v>
+        <v>1412</v>
       </c>
       <c r="B14" s="29">
         <v>60</v>
@@ -57753,10 +57808,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4"/>
       <c r="B2" t="s" s="3">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -57766,10 +57821,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>1408</v>
+        <v>1415</v>
       </c>
       <c r="C3" t="s" s="15">
-        <v>1409</v>
+        <v>1416</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -57779,10 +57834,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>1410</v>
+        <v>1417</v>
       </c>
       <c r="C4" t="s" s="17">
-        <v>1411</v>
+        <v>1418</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -57792,10 +57847,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>1412</v>
+        <v>1419</v>
       </c>
       <c r="C5" t="s" s="17">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -57805,10 +57860,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="C6" t="s" s="17">
-        <v>1415</v>
+        <v>1422</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -57818,10 +57873,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="C7" t="s" s="17">
-        <v>1417</v>
+        <v>1424</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -57831,10 +57886,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="C8" t="s" s="17">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -57844,10 +57899,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>1420</v>
+        <v>1427</v>
       </c>
       <c r="C9" t="s" s="17">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
